--- a/data/raw/문제_SAFE.xlsx
+++ b/data/raw/문제_SAFE.xlsx
@@ -739,10 +739,14 @@
       <c r="N2" s="3" t="n"/>
       <c r="O2" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P2" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P2" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q2" s="3" t="inlineStr">
         <is>
           <t>AI 초안(2026-10-19) · 근거 확인 ×: 일반 교통안전 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>
@@ -814,10 +818,14 @@
       <c r="N3" s="3" t="n"/>
       <c r="O3" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P3" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P3" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q3" s="3" t="inlineStr">
         <is>
           <t>AI 초안(2026-10-19) · 근거 확인 ×: 일반 교통안전 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>
@@ -889,10 +897,14 @@
       <c r="N4" s="3" t="n"/>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P4" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
           <t>AI 초안(2026-10-19) · 근거 확인 ×: 일반 교통안전 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>
@@ -964,10 +976,14 @@
       <c r="N5" s="3" t="n"/>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P5" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
           <t>AI 초안(2026-10-19) · 근거 확인 ×: 일반 교통안전 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>
@@ -1039,10 +1055,14 @@
       <c r="N6" s="3" t="n"/>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P6" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
           <t>AI 초안(2026-10-19) · 근거 확인 ×: 일반 교통안전 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>
@@ -1114,10 +1134,14 @@
       <c r="N7" s="3" t="n"/>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P7" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P7" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
           <t>AI 초안(2026-10-19) · 근거 확인 ×: 일반 교통안전 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>
@@ -1189,10 +1213,14 @@
       <c r="N8" s="3" t="n"/>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P8" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
           <t>AI 초안(2026-10-19) · 근거 확인 ×: 일반 교통안전 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>
@@ -1264,10 +1292,14 @@
       <c r="N9" s="3" t="n"/>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P9" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P9" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
           <t>AI 초안(2026-10-19) · 근거 확인 ×: 일반 교통안전 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>
@@ -1339,10 +1371,14 @@
       <c r="N10" s="3" t="n"/>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P10" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P10" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
           <t>AI 초안(2026-10-19) · 근거 확인 ×: 일반 교통안전 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>
@@ -1414,10 +1450,14 @@
       <c r="N11" s="3" t="n"/>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P11" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P11" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
           <t>AI 초안(2026-10-19) · 근거 확인 ×: 일반 교통안전 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>
@@ -1489,10 +1529,14 @@
       <c r="N12" s="3" t="n"/>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P12" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P12" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
           <t>AI 초안(2026-10-19) · 근거 확인 ×: 일반 교통안전 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>
@@ -1564,10 +1608,14 @@
       <c r="N13" s="3" t="n"/>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P13" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P13" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
           <t>AI 초안(2026-10-19) · 근거 확인 ×: 일반 교통안전 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>
@@ -1639,10 +1687,14 @@
       <c r="N14" s="3" t="n"/>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P14" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P14" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q14" s="3" t="inlineStr">
         <is>
           <t>AI 초안(2026-10-19) · 근거 확인 ○: 법제처 찾기쉬운 생활법령정보(도로교통법)에서 확인 – 원문 대조 권장</t>
@@ -1714,10 +1766,14 @@
       <c r="N15" s="3" t="n"/>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P15" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P15" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
           <t>AI 초안(2026-10-19) · 근거 확인 ○: 법제처 찾기쉬운 생활법령정보(도로교통법)에서 확인 – 원문 대조 권장</t>
@@ -1789,10 +1845,14 @@
       <c r="N16" s="3" t="n"/>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P16" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P16" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
           <t>AI 초안(2026-10-19) · 근거 확인 ×: 일반 교통안전 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>
@@ -1864,10 +1924,14 @@
       <c r="N17" s="3" t="n"/>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P17" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P17" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
           <t>AI 초안(2026-10-19) · 근거 확인 ×: 일반 교통안전 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>
@@ -1939,10 +2003,14 @@
       <c r="N18" s="3" t="n"/>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P18" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P18" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q18" s="3" t="inlineStr">
         <is>
           <t>AI 초안(2026-10-19) · 근거 확인 ×: 일반 교통안전 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>
@@ -2014,10 +2082,14 @@
       <c r="N19" s="3" t="n"/>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P19" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P19" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
           <t>AI 초안(2026-10-19) · 근거 확인 ×: 일반 교통안전 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>
@@ -2089,10 +2161,14 @@
       <c r="N20" s="3" t="n"/>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P20" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P20" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
           <t>AI 초안(2026-10-19) · 근거 확인 ×: 일반 교통안전 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>
@@ -2164,10 +2240,14 @@
       <c r="N21" s="3" t="n"/>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P21" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P21" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q21" s="3" t="inlineStr">
         <is>
           <t>AI 초안(2026-10-19) · 근거 확인 ×: 일반 교통안전 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>
@@ -2239,10 +2319,14 @@
       <c r="N22" s="3" t="n"/>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P22" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P22" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q22" s="3" t="inlineStr">
         <is>
           <t>AI 초안(2026-10-19) · 근거 확인 ×: 일반 교통안전 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>
@@ -2314,10 +2398,14 @@
       <c r="N23" s="3" t="n"/>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P23" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P23" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
           <t>AI 초안(2026-10-19) · 근거 확인 ×: 일반 교통안전 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>
@@ -2389,10 +2477,14 @@
       <c r="N24" s="3" t="n"/>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P24" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P24" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q24" s="3" t="inlineStr">
         <is>
           <t>AI 초안(2026-10-19) · 근거 확인 ×: 일반 교통안전 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>
@@ -2464,10 +2556,14 @@
       <c r="N25" s="3" t="n"/>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P25" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P25" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q25" s="3" t="inlineStr">
         <is>
           <t>AI 초안(2026-10-19) · 근거 확인 ×: 일반 교통안전 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>
@@ -2539,10 +2635,14 @@
       <c r="N26" s="3" t="n"/>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P26" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P26" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q26" s="3" t="inlineStr">
         <is>
           <t>AI 초안(2026-10-19) · 근거 확인 ×: 일반 교통안전 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>
@@ -2614,10 +2714,14 @@
       <c r="N27" s="3" t="n"/>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P27" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P27" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q27" s="3" t="inlineStr">
         <is>
           <t>AI 초안(2026-10-19) · 근거 확인 ×: 일반 교통안전 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>
@@ -2689,10 +2793,14 @@
       <c r="N28" s="3" t="n"/>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P28" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P28" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q28" s="3" t="inlineStr">
         <is>
           <t>AI 초안(2026-10-19) · 근거 확인 ×: 일반 교통안전 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>
@@ -2764,10 +2872,14 @@
       <c r="N29" s="3" t="n"/>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P29" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P29" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q29" s="3" t="inlineStr">
         <is>
           <t>AI 초안(2026-10-19) · 근거 확인 ×: 일반 교통안전 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>
@@ -2839,10 +2951,14 @@
       <c r="N30" s="3" t="n"/>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P30" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P30" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
           <t>AI 초안(2026-10-19) · 근거 확인 ×: 일반 교통안전 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>
@@ -2914,10 +3030,14 @@
       <c r="N31" s="3" t="n"/>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P31" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P31" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q31" s="3" t="inlineStr">
         <is>
           <t>AI 초안(2026-10-19) · 근거 확인 ×: 일반 교통안전 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>
@@ -2989,10 +3109,14 @@
       <c r="N32" s="3" t="n"/>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P32" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P32" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q32" s="3" t="inlineStr">
         <is>
           <t>AI 초안(2026-10-19) · 근거 확인 ×: 일반 교통안전 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>
@@ -3064,10 +3188,14 @@
       <c r="N33" s="3" t="n"/>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P33" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P33" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q33" s="3" t="inlineStr">
         <is>
           <t>AI 초안(2026-10-19) · 근거 확인 ×: 일반 교통안전 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>
@@ -3139,10 +3267,14 @@
       <c r="N34" s="3" t="n"/>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P34" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P34" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q34" s="3" t="inlineStr">
         <is>
           <t>AI 초안(2026-10-19) · 근거 확인 ×: 일반 교통안전 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>
@@ -3214,10 +3346,14 @@
       <c r="N35" s="3" t="n"/>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P35" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P35" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q35" s="3" t="inlineStr">
         <is>
           <t>AI 초안(2026-10-19) · 근거 확인 ×: 일반 교통안전 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>
@@ -3289,10 +3425,14 @@
       <c r="N36" s="3" t="n"/>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P36" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P36" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q36" s="3" t="inlineStr">
         <is>
           <t>AI 초안(2026-10-19) · 근거 확인 ×: 일반 교통안전 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>
@@ -3364,10 +3504,14 @@
       <c r="N37" s="3" t="n"/>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P37" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P37" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
           <t>AI 초안(2026-10-19) · 근거 확인 ×: 일반 교통안전 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>
@@ -3439,10 +3583,14 @@
       <c r="N38" s="3" t="n"/>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P38" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P38" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q38" s="3" t="inlineStr">
         <is>
           <t>AI 초안(2026-10-19) · 근거 확인 ×: 법령 원문 미확인(작성자 지식) – 원문 대조 필수</t>
@@ -3514,10 +3662,14 @@
       <c r="N39" s="3" t="n"/>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P39" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P39" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q39" s="3" t="inlineStr">
         <is>
           <t>AI 초안(2026-10-19) · 근거 확인 ×: 법령 원문 미확인(작성자 지식) – 원문 대조 필수</t>
@@ -3589,10 +3741,14 @@
       <c r="N40" s="3" t="n"/>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P40" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P40" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q40" s="3" t="inlineStr">
         <is>
           <t>AI 초안(2026-10-19) · 근거 확인 ×: 법령 원문 미확인(작성자 지식) – 원문 대조 필수</t>
@@ -3664,10 +3820,14 @@
       <c r="N41" s="3" t="n"/>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P41" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P41" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q41" s="3" t="inlineStr">
         <is>
           <t>AI 초안(2026-10-19) · 근거 확인 ×: 일반 교통안전 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>
@@ -3739,10 +3899,14 @@
       <c r="N42" s="3" t="n"/>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P42" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P42" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q42" s="3" t="inlineStr">
         <is>
           <t>AI 초안(2026-10-19) · 근거 확인 ×: 법령 원문 미확인(작성자 지식) – 원문 대조 필수</t>
@@ -3814,10 +3978,14 @@
       <c r="N43" s="3" t="n"/>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P43" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P43" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q43" s="3" t="inlineStr">
         <is>
           <t>AI 초안(2026-10-19) · 근거 확인 ×: 일반 교통안전 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>
@@ -3889,10 +4057,14 @@
       <c r="N44" s="3" t="n"/>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P44" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P44" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q44" s="3" t="inlineStr">
         <is>
           <t>AI 초안(2026-10-19) · 근거 확인 ○: 법제처 찾기쉬운 생활법령정보(도로교통법)에서 확인 – 원문 대조 권장</t>
@@ -3964,10 +4136,14 @@
       <c r="N45" s="3" t="n"/>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P45" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P45" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
           <t>AI 초안(2026-10-19) · 근거 확인 ○: 법제처 찾기쉬운 생활법령정보(도로교통법)에서 확인 – 원문 대조 권장</t>
@@ -4039,10 +4215,14 @@
       <c r="N46" s="3" t="n"/>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P46" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P46" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q46" s="3" t="inlineStr">
         <is>
           <t>AI 초안(2026-10-19) · 근거 확인 ○: 법제처 찾기쉬운 생활법령정보(도로교통법)에서 확인 – 원문 대조 권장</t>
@@ -4114,10 +4294,14 @@
       <c r="N47" s="3" t="n"/>
       <c r="O47" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P47" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P47" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q47" s="3" t="inlineStr">
         <is>
           <t>AI 초안(2026-10-19) · 근거 확인 ×: 일반 교통안전 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>
@@ -4189,10 +4373,14 @@
       <c r="N48" s="3" t="n"/>
       <c r="O48" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P48" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P48" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q48" s="3" t="inlineStr">
         <is>
           <t>AI 초안(2026-10-19) · 근거 확인 ×: 일반 교통안전 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>
@@ -4264,10 +4452,14 @@
       <c r="N49" s="3" t="n"/>
       <c r="O49" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P49" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P49" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q49" s="3" t="inlineStr">
         <is>
           <t>AI 초안(2026-10-19) · 근거 확인 ×: 일반 교통안전 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>
@@ -4339,10 +4531,14 @@
       <c r="N50" s="3" t="n"/>
       <c r="O50" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P50" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P50" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q50" s="3" t="inlineStr">
         <is>
           <t>AI 초안(2026-10-19) · 근거 확인 ○: 법제처 찾기쉬운 생활법령정보(도로교통법)에서 확인 – 원문 대조 권장</t>
@@ -4414,10 +4610,14 @@
       <c r="N51" s="3" t="n"/>
       <c r="O51" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P51" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P51" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q51" s="3" t="inlineStr">
         <is>
           <t>AI 초안(2026-10-19) · 근거 확인 ×: 일반 교통안전 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>
@@ -4489,10 +4689,14 @@
       <c r="N52" s="3" t="n"/>
       <c r="O52" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P52" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P52" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q52" s="3" t="inlineStr">
         <is>
           <t>AI 초안(2026-10-19) · 근거 확인 ×: 일반 교통안전 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>
@@ -4564,10 +4768,14 @@
       <c r="N53" s="3" t="n"/>
       <c r="O53" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P53" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P53" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q53" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 일반 자동차 구조·점검 지식(작성자 지식) – 공단 교재 내용과 대조 필요</t>
@@ -4639,10 +4847,14 @@
       <c r="N54" s="3" t="n"/>
       <c r="O54" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P54" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P54" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q54" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 일반 자동차 구조·점검 지식(작성자 지식) – 공단 교재 내용과 대조 필요</t>
@@ -4714,10 +4926,14 @@
       <c r="N55" s="3" t="n"/>
       <c r="O55" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P55" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P55" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q55" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 일반 지식(수치 포함) – 공단 교재 수치와 대조 필수</t>
@@ -4789,10 +5005,14 @@
       <c r="N56" s="3" t="n"/>
       <c r="O56" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P56" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P56" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q56" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 일반 자동차 구조·점검 지식(작성자 지식) – 공단 교재 내용과 대조 필요</t>
@@ -4864,10 +5084,14 @@
       <c r="N57" s="3" t="n"/>
       <c r="O57" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P57" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P57" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q57" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 일반 자동차 구조·점검 지식(작성자 지식) – 공단 교재 내용과 대조 필요</t>
@@ -4939,10 +5163,14 @@
       <c r="N58" s="3" t="n"/>
       <c r="O58" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P58" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P58" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q58" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 일반 자동차 구조·점검 지식(작성자 지식) – 공단 교재 내용과 대조 필요</t>
@@ -5014,10 +5242,14 @@
       <c r="N59" s="3" t="n"/>
       <c r="O59" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P59" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P59" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q59" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 일반 자동차 구조·점검 지식(작성자 지식) – 공단 교재 내용과 대조 필요</t>
@@ -5089,10 +5321,14 @@
       <c r="N60" s="3" t="n"/>
       <c r="O60" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P60" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P60" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q60" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 일반 자동차 구조·점검 지식(작성자 지식) – 공단 교재 내용과 대조 필요</t>
@@ -5164,10 +5400,14 @@
       <c r="N61" s="3" t="n"/>
       <c r="O61" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P61" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P61" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q61" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 일반 자동차 구조·점검 지식(작성자 지식) – 공단 교재 내용과 대조 필요</t>
@@ -5239,10 +5479,14 @@
       <c r="N62" s="3" t="n"/>
       <c r="O62" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P62" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P62" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q62" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 일반 자동차 구조·점검 지식(작성자 지식) – 공단 교재 내용과 대조 필요</t>
@@ -5314,10 +5558,14 @@
       <c r="N63" s="3" t="n"/>
       <c r="O63" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P63" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P63" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q63" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 일반 자동차 구조·점검 지식(작성자 지식) – 공단 교재 내용과 대조 필요</t>
@@ -5389,10 +5637,14 @@
       <c r="N64" s="3" t="n"/>
       <c r="O64" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P64" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P64" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q64" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 일반 자동차 구조·점검 지식(작성자 지식) – 공단 교재 내용과 대조 필요</t>
@@ -5464,10 +5716,14 @@
       <c r="N65" s="3" t="n"/>
       <c r="O65" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P65" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P65" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q65" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 일반 자동차 구조·점검 지식(작성자 지식) – 공단 교재 내용과 대조 필요</t>
@@ -5539,10 +5795,14 @@
       <c r="N66" s="3" t="n"/>
       <c r="O66" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P66" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P66" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q66" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 일반 자동차 구조·점검 지식(작성자 지식) – 공단 교재 내용과 대조 필요</t>
@@ -5614,10 +5874,14 @@
       <c r="N67" s="3" t="n"/>
       <c r="O67" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P67" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P67" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q67" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 일반 자동차 구조·점검 지식(작성자 지식) – 공단 교재 내용과 대조 필요</t>
@@ -5689,10 +5953,14 @@
       <c r="N68" s="3" t="n"/>
       <c r="O68" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P68" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P68" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q68" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 일반 자동차 구조·점검 지식(작성자 지식) – 공단 교재 내용과 대조 필요</t>
@@ -5764,10 +6032,14 @@
       <c r="N69" s="3" t="n"/>
       <c r="O69" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P69" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P69" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q69" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 일반 자동차 구조·점검 지식(작성자 지식) – 공단 교재 내용과 대조 필요</t>
@@ -5839,10 +6111,14 @@
       <c r="N70" s="3" t="n"/>
       <c r="O70" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P70" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P70" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q70" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 일반 자동차 구조·점검 지식(작성자 지식) – 공단 교재 내용과 대조 필요</t>
@@ -5914,10 +6190,14 @@
       <c r="N71" s="3" t="n"/>
       <c r="O71" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P71" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P71" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q71" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 일반 자동차 구조·점검 지식(작성자 지식) – 공단 교재 내용과 대조 필요</t>
@@ -5989,10 +6269,14 @@
       <c r="N72" s="3" t="n"/>
       <c r="O72" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P72" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P72" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q72" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 일반 자동차 구조·점검 지식(작성자 지식) – 공단 교재 내용과 대조 필요</t>
@@ -6064,10 +6348,14 @@
       <c r="N73" s="3" t="n"/>
       <c r="O73" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P73" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P73" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q73" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 일반 자동차 구조·점검 지식(작성자 지식) – 공단 교재 내용과 대조 필요</t>
@@ -6139,10 +6427,14 @@
       <c r="N74" s="3" t="n"/>
       <c r="O74" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P74" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P74" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q74" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 일반 자동차 구조·점검 지식(작성자 지식) – 공단 교재 내용과 대조 필요</t>
@@ -6214,10 +6506,14 @@
       <c r="N75" s="3" t="n"/>
       <c r="O75" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P75" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P75" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q75" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 일반 자동차 구조·점검 지식(작성자 지식) – 공단 교재 내용과 대조 필요</t>
@@ -6289,10 +6585,14 @@
       <c r="N76" s="3" t="n"/>
       <c r="O76" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P76" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P76" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q76" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 일반 자동차 구조·점검 지식(작성자 지식) – 공단 교재 내용과 대조 필요</t>
@@ -6364,10 +6664,14 @@
       <c r="N77" s="3" t="n"/>
       <c r="O77" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P77" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P77" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q77" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 일반 자동차 구조·점검 지식(작성자 지식) – 공단 교재 내용과 대조 필요</t>
@@ -6439,10 +6743,14 @@
       <c r="N78" s="3" t="n"/>
       <c r="O78" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P78" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P78" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q78" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 일반 자동차 구조·점검 지식(작성자 지식) – 공단 교재 내용과 대조 필요</t>
@@ -6514,10 +6822,14 @@
       <c r="N79" s="3" t="n"/>
       <c r="O79" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P79" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P79" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q79" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 일반 자동차 구조·점검 지식(작성자 지식) – 공단 교재 내용과 대조 필요</t>
@@ -6589,10 +6901,14 @@
       <c r="N80" s="3" t="n"/>
       <c r="O80" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P80" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P80" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q80" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 일반 자동차 구조·점검 지식(작성자 지식) – 공단 교재 내용과 대조 필요</t>
@@ -6664,10 +6980,14 @@
       <c r="N81" s="3" t="n"/>
       <c r="O81" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P81" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P81" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q81" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 일반 자동차 구조·점검 지식(작성자 지식) – 공단 교재 내용과 대조 필요</t>
@@ -6739,10 +7059,14 @@
       <c r="N82" s="3" t="n"/>
       <c r="O82" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P82" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P82" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q82" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 일반 교통안전 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>
@@ -6814,10 +7138,14 @@
       <c r="N83" s="3" t="n"/>
       <c r="O83" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P83" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P83" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q83" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 일반 자동차 구조·점검 지식(작성자 지식) – 공단 교재 내용과 대조 필요</t>
@@ -6889,10 +7217,14 @@
       <c r="N84" s="3" t="n"/>
       <c r="O84" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P84" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P84" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q84" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 일반 교통안전 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>
@@ -6964,10 +7296,14 @@
       <c r="N85" s="3" t="n"/>
       <c r="O85" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P85" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P85" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q85" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 일반 자동차 구조·점검 지식(작성자 지식) – 공단 교재 내용과 대조 필요</t>
@@ -7039,10 +7375,14 @@
       <c r="N86" s="3" t="n"/>
       <c r="O86" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P86" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P86" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q86" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 일반 자동차 구조·점검 지식(작성자 지식) – 공단 교재 내용과 대조 필요</t>
@@ -7114,10 +7454,14 @@
       <c r="N87" s="3" t="n"/>
       <c r="O87" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P87" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P87" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q87" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 일반 자동차 구조·점검 지식(작성자 지식) – 공단 교재 내용과 대조 필요</t>
@@ -7189,10 +7533,14 @@
       <c r="N88" s="3" t="n"/>
       <c r="O88" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P88" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P88" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q88" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 일반 교통안전 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>
@@ -7264,10 +7612,14 @@
       <c r="N89" s="3" t="n"/>
       <c r="O89" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P89" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P89" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q89" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 일반 교통안전 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>
@@ -7339,10 +7691,14 @@
       <c r="N90" s="3" t="n"/>
       <c r="O90" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P90" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P90" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q90" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 일반 교통안전 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>
@@ -7414,10 +7770,14 @@
       <c r="N91" s="3" t="n"/>
       <c r="O91" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P91" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P91" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q91" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 일반 지식(수치 포함) – 공단 교재 수치와 대조 필수</t>
@@ -7489,10 +7849,14 @@
       <c r="N92" s="3" t="n"/>
       <c r="O92" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P92" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P92" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q92" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 일반 교통안전 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>
@@ -7564,10 +7928,14 @@
       <c r="N93" s="3" t="n"/>
       <c r="O93" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P93" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P93" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q93" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 일반 교통안전 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>
@@ -7639,10 +8007,14 @@
       <c r="N94" s="3" t="n"/>
       <c r="O94" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P94" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P94" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q94" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 일반 교통안전 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>
@@ -7714,10 +8086,14 @@
       <c r="N95" s="3" t="n"/>
       <c r="O95" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P95" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P95" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q95" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 일반 교통안전 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>
@@ -7789,10 +8165,14 @@
       <c r="N96" s="3" t="n"/>
       <c r="O96" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P96" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P96" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q96" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 일반 교통안전 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>
@@ -7864,10 +8244,14 @@
       <c r="N97" s="3" t="n"/>
       <c r="O97" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P97" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P97" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q97" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 일반 교통안전 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>
@@ -7939,10 +8323,14 @@
       <c r="N98" s="3" t="n"/>
       <c r="O98" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P98" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P98" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q98" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 일반 교통안전 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>
@@ -8014,10 +8402,14 @@
       <c r="N99" s="3" t="n"/>
       <c r="O99" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P99" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P99" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q99" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 일반 교통안전 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>
@@ -8089,10 +8481,14 @@
       <c r="N100" s="3" t="n"/>
       <c r="O100" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P100" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P100" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q100" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 일반 교통안전 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>
@@ -8164,10 +8560,14 @@
       <c r="N101" s="3" t="n"/>
       <c r="O101" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P101" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P101" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q101" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 일반 교통안전 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>
@@ -8239,10 +8639,14 @@
       <c r="N102" s="3" t="n"/>
       <c r="O102" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P102" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P102" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q102" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 일반 교통안전 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>
@@ -8314,10 +8718,14 @@
       <c r="N103" s="3" t="n"/>
       <c r="O103" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P103" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P103" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q103" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 일반 교통안전 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>
@@ -8389,10 +8797,14 @@
       <c r="N104" s="3" t="n"/>
       <c r="O104" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P104" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P104" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q104" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 일반 교통안전 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>
@@ -8464,10 +8876,14 @@
       <c r="N105" s="3" t="n"/>
       <c r="O105" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P105" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P105" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q105" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 일반 교통안전 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>
@@ -8539,10 +8955,14 @@
       <c r="N106" s="3" t="n"/>
       <c r="O106" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P106" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P106" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q106" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 일반 교통안전 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>
@@ -8614,10 +9034,14 @@
       <c r="N107" s="3" t="n"/>
       <c r="O107" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P107" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P107" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q107" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 일반 교통안전 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>
@@ -8689,10 +9113,14 @@
       <c r="N108" s="3" t="n"/>
       <c r="O108" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P108" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P108" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q108" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 일반 교통안전 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>
@@ -8764,10 +9192,14 @@
       <c r="N109" s="3" t="n"/>
       <c r="O109" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P109" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P109" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q109" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 일반 교통안전 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>
@@ -8839,10 +9271,14 @@
       <c r="N110" s="3" t="n"/>
       <c r="O110" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P110" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P110" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q110" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 일반 교통안전 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>
@@ -8914,10 +9350,14 @@
       <c r="N111" s="3" t="n"/>
       <c r="O111" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P111" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P111" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q111" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 일반 교통안전 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>
@@ -8989,10 +9429,14 @@
       <c r="N112" s="3" t="n"/>
       <c r="O112" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P112" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P112" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q112" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 일반 교통안전 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>
@@ -9064,10 +9508,14 @@
       <c r="N113" s="3" t="n"/>
       <c r="O113" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P113" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P113" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q113" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 일반 교통안전 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>
@@ -9139,10 +9587,14 @@
       <c r="N114" s="3" t="n"/>
       <c r="O114" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P114" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P114" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q114" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 일반 교통안전 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>
@@ -9214,10 +9666,14 @@
       <c r="N115" s="3" t="n"/>
       <c r="O115" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P115" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P115" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q115" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 일반 교통안전 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>
@@ -9289,10 +9745,14 @@
       <c r="N116" s="3" t="n"/>
       <c r="O116" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P116" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P116" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q116" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 일반 교통안전 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>
@@ -9364,10 +9824,14 @@
       <c r="N117" s="3" t="n"/>
       <c r="O117" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P117" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P117" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q117" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 일반 교통안전 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>
@@ -9439,10 +9903,14 @@
       <c r="N118" s="3" t="n"/>
       <c r="O118" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P118" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P118" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q118" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 일반 자동차 구조·점검 지식(작성자 지식) – 공단 교재 내용과 대조 필요</t>
@@ -9514,10 +9982,14 @@
       <c r="N119" s="3" t="n"/>
       <c r="O119" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P119" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P119" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q119" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 일반 자동차 구조·점검 지식(작성자 지식) – 공단 교재 내용과 대조 필요</t>
@@ -9589,10 +10061,14 @@
       <c r="N120" s="3" t="n"/>
       <c r="O120" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P120" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P120" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q120" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 일반 교통안전 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>
@@ -9664,10 +10140,14 @@
       <c r="N121" s="3" t="n"/>
       <c r="O121" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P121" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P121" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q121" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 일반 자동차 구조·점검 지식(작성자 지식) – 공단 교재 내용과 대조 필요</t>
@@ -9739,10 +10219,14 @@
       <c r="N122" s="3" t="n"/>
       <c r="O122" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P122" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P122" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q122" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 일반 교통안전 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>
@@ -9814,10 +10298,14 @@
       <c r="N123" s="3" t="n"/>
       <c r="O123" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P123" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P123" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q123" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 일반 교통안전 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>
@@ -9889,10 +10377,14 @@
       <c r="N124" s="3" t="n"/>
       <c r="O124" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P124" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P124" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q124" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 일반 교통안전 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>
@@ -9964,10 +10456,14 @@
       <c r="N125" s="3" t="n"/>
       <c r="O125" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P125" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P125" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q125" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 일반 교통안전 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>
@@ -10039,10 +10535,14 @@
       <c r="N126" s="3" t="n"/>
       <c r="O126" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P126" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P126" s="3" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-20</t>
+        </is>
+      </c>
       <c r="Q126" s="3" t="inlineStr">
         <is>
           <t>AI 2차 초안(2026-10-20) · 근거 확인 ×: 일반 교통안전 이론(작성자 지식) – 공단 출제 기준·교재 내용과 대조 필요</t>

--- a/data/raw/문제_SAFE.xlsx
+++ b/data/raw/문제_SAFE.xlsx
@@ -10614,10 +10614,14 @@
       <c r="N127" s="3" t="n"/>
       <c r="O127" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P127" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P127" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q127" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교재 운전자 요인-시각 특성(심시력). 교재(안전운행) 일반 내용, 원문 미확인 · 교차 점검 반영</t>
@@ -10689,10 +10693,14 @@
       <c r="N128" s="3" t="n"/>
       <c r="O128" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P128" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P128" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q128" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교재 운전자 요인-심시력. 교재(안전운행) 일반 내용, 원문 미확인</t>
@@ -10764,10 +10772,14 @@
       <c r="N129" s="3" t="n"/>
       <c r="O129" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P129" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P129" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q129" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교재 운전자 요인-명순응·암순응. 교재(안전운행) 일반 내용, 원문 미확인</t>
@@ -10839,10 +10851,14 @@
       <c r="N130" s="3" t="n"/>
       <c r="O130" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P130" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P130" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q130" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교재 야간운전-현혹현상. 교재(안전운행) 일반 내용, 원문 미확인</t>
@@ -10914,10 +10930,14 @@
       <c r="N131" s="3" t="n"/>
       <c r="O131" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P131" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P131" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q131" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교재 운전자 요인-야간 시력과 옷 색깔. 교재(안전운행) 일반 내용, 원문 미확인</t>
@@ -10989,10 +11009,14 @@
       <c r="N132" s="3" t="n"/>
       <c r="O132" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P132" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P132" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q132" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교재 운전자 요인-속도와 시야(40km 100°, 70km 65°, 100km 40°). WebSearch로 원문 확인 못함 · 교차 점검 반영</t>
@@ -11064,10 +11088,14 @@
       <c r="N133" s="3" t="n"/>
       <c r="O133" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P133" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P133" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q133" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교재 운전자 요인-시야와 시축(3° 80%, 6° 90%, 12° 99%). WebSearch로 원문 확인 못함</t>
@@ -11139,10 +11167,14 @@
       <c r="N134" s="3" t="n"/>
       <c r="O134" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P134" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P134" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q134" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교재 운전자 요인-시야 고정. 교재(안전운행) 일반 내용, 원문 미확인</t>
@@ -11214,10 +11246,14 @@
       <c r="N135" s="3" t="n"/>
       <c r="O135" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P135" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P135" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q135" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교재 운전자 요인-동체시력 특성. 교재(안전운행) 일반 내용, 원문 미확인</t>
@@ -11289,10 +11325,14 @@
       <c r="N136" s="3" t="n"/>
       <c r="O136" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P136" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P136" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q136" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교재 운전자 요인-착각(경사의 착각). 교재(안전운행) 일반 내용, 원문 미확인 · 교차 점검 반영</t>
@@ -11364,10 +11404,14 @@
       <c r="N137" s="3" t="n"/>
       <c r="O137" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P137" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P137" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q137" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교재 운전자 요인-착각(속도의 착각). 교재(안전운행) 일반 내용, 원문 미확인</t>
@@ -11439,10 +11483,14 @@
       <c r="N138" s="3" t="n"/>
       <c r="O138" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P138" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P138" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q138" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교재 운전자 요인-착각(상반의 착각). 교재(안전운행) 일반 내용, 원문 미확인 · 교차 점검 반영</t>
@@ -11514,10 +11562,14 @@
       <c r="N139" s="3" t="n"/>
       <c r="O139" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P139" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P139" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q139" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교재 운전자 요인-운전 특성(인지&gt;판단&gt;조작). 교재(안전운행) 일반 내용, 원문 미확인</t>
@@ -11589,10 +11641,14 @@
       <c r="N140" s="3" t="n"/>
       <c r="O140" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P140" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P140" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q140" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교재 교통사고의 원인 요인(간접·중간·직접). 교재(안전운행) 일반 내용, 원문 미확인</t>
@@ -11664,10 +11720,14 @@
       <c r="N141" s="3" t="n"/>
       <c r="O141" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P141" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P141" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q141" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교재 교통사고의 원인 요인(중간적 요인). 교재(안전운행) 일반 내용, 원문 미확인</t>
@@ -11739,10 +11799,14 @@
       <c r="N142" s="3" t="n"/>
       <c r="O142" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P142" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P142" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q142" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교재 사고의 심리적 요인-예측의 실수. 교재(안전운행) 일반 내용, 원문 미확인</t>
@@ -11814,10 +11878,14 @@
       <c r="N143" s="3" t="n"/>
       <c r="O143" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P143" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P143" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q143" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교재 사고의 심리적 요인-사고 다발 운전자 특성. 교재(안전운행) 일반 내용, 원문 미확인</t>
@@ -11889,10 +11957,14 @@
       <c r="N144" s="3" t="n"/>
       <c r="O144" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P144" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P144" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q144" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교재 운전자 요인-운전피로의 요인 구분. 교재(안전운행) 일반 내용, 원문 미확인</t>
@@ -11964,10 +12036,14 @@
       <c r="N145" s="3" t="n"/>
       <c r="O145" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P145" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P145" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q145" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교재 운전자 요인-피로와 운전 착오. 교재(안전운행) 일반 내용, 원문 미확인</t>
@@ -12039,10 +12115,14 @@
       <c r="N146" s="3" t="n"/>
       <c r="O146" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P146" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P146" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q146" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교재 운전자 요인-운전피로의 특징. 교재(안전운행) 일반 내용, 원문 미확인</t>
@@ -12114,10 +12194,14 @@
       <c r="N147" s="3" t="n"/>
       <c r="O147" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P147" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P147" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q147" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교재 운전자 요인-음주운전 사고 특징. 교재(안전운행) 일반 내용, 원문 미확인</t>
@@ -12189,10 +12273,14 @@
       <c r="N148" s="3" t="n"/>
       <c r="O148" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P148" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P148" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q148" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 도로교통법 제45조(과로한 때 등의 운전 금지) - 조문 내용 기억 기준, 원문 미확인</t>
@@ -12264,10 +12352,14 @@
       <c r="N149" s="3" t="n"/>
       <c r="O149" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P149" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P149" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q149" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교재 보행자-어린이 인지발달 단계(피아제). 교재(안전운행) 일반 내용, 원문 미확인</t>
@@ -12339,10 +12431,14 @@
       <c r="N150" s="3" t="n"/>
       <c r="O150" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P150" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P150" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q150" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교재 보행자-어린이 교통사고 유형. 교재(안전운행) 일반 내용, 원문 미확인</t>
@@ -12414,10 +12510,14 @@
       <c r="N151" s="3" t="n"/>
       <c r="O151" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P151" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P151" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q151" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교재 보행자-어린이 승차 시 주의. 교재(안전운행) 일반 내용, 원문 미확인</t>
@@ -12489,10 +12589,14 @@
       <c r="N152" s="3" t="n"/>
       <c r="O152" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P152" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P152" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q152" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교재 고령자 교통안전-시각 특성. 교재(안전운행) 일반 내용, 원문 미확인</t>
@@ -12564,10 +12668,14 @@
       <c r="N153" s="3" t="n"/>
       <c r="O153" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P153" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P153" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q153" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교재 고령자 교통안전-고령 보행자 특성. 교재(안전운행) 일반 내용, 원문 미확인</t>
@@ -12639,10 +12747,14 @@
       <c r="N154" s="3" t="n"/>
       <c r="O154" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P154" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P154" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q154" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교재 운전 행동-주의 분산. 교재(안전운행) 일반 내용, 원문 미확인</t>
@@ -12714,10 +12826,14 @@
       <c r="N155" s="3" t="n"/>
       <c r="O155" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P155" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P155" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q155" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교재 자동차 주요 장치-주행장치(휠). 교재(안전운행) 일반 내용, 원문 미확인</t>
@@ -12789,10 +12905,14 @@
       <c r="N156" s="3" t="n"/>
       <c r="O156" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P156" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P156" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q156" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교재 자동차 주요 장치-조향장치(앞바퀴 정렬). 교재(안전운행) 일반 내용, 원문 미확인</t>
@@ -12864,10 +12984,14 @@
       <c r="N157" s="3" t="n"/>
       <c r="O157" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P157" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P157" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q157" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교재 자동차 주요 장치-조향장치(캐스터). 교재(안전운행) 일반 내용, 원문 미확인</t>
@@ -12939,10 +13063,14 @@
       <c r="N158" s="3" t="n"/>
       <c r="O158" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P158" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P158" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q158" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교재 자동차 주요 장치-현가장치(공기 스프링). 교재(안전운행) 일반 내용, 원문 미확인</t>
@@ -13014,10 +13142,14 @@
       <c r="N159" s="3" t="n"/>
       <c r="O159" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P159" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P159" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q159" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교재 고장 징후-현가장치 이상. 교재(안전운행) 일반 내용, 원문 미확인</t>
@@ -13089,10 +13221,14 @@
       <c r="N160" s="3" t="n"/>
       <c r="O160" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P160" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P160" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q160" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교재 고장 징후-이상음(팬벨트). 교재(안전운행) 일반 내용, 원문 미확인</t>
@@ -13164,10 +13300,14 @@
       <c r="N161" s="3" t="n"/>
       <c r="O161" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P161" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P161" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q161" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교재 고장 징후-이상음(클러치). 교재(안전운행) 일반 내용, 원문 미확인</t>
@@ -13239,10 +13379,14 @@
       <c r="N162" s="3" t="n"/>
       <c r="O162" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P162" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P162" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q162" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교재 고장 징후-이상음(브레이크). 교재(안전운행) 일반 내용, 원문 미확인</t>
@@ -13314,10 +13458,14 @@
       <c r="N163" s="3" t="n"/>
       <c r="O163" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P163" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P163" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q163" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교재 고장 징후-배출가스 색(백색). 교재(안전운행) 일반 내용, 원문 미확인</t>
@@ -13389,10 +13537,14 @@
       <c r="N164" s="3" t="n"/>
       <c r="O164" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P164" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P164" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q164" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교재 고장 징후-냄새(전기장치). 교재(안전운행) 일반 내용, 원문 미확인</t>
@@ -13464,10 +13616,14 @@
       <c r="N165" s="3" t="n"/>
       <c r="O165" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P165" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P165" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q165" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교재 차량 점검-오감에 의한 판별. 교재(안전운행) 일반 내용, 원문 미확인</t>
@@ -13539,10 +13695,14 @@
       <c r="N166" s="3" t="n"/>
       <c r="O166" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P166" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P166" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q166" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교재 차량 점검-브레이크 이상. 교재(안전운행) 일반 내용, 원문 미확인</t>
@@ -13614,10 +13774,14 @@
       <c r="N167" s="3" t="n"/>
       <c r="O167" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P167" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P167" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q167" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교재 자동차 주요 장치-제동장치(주차 브레이크). 교재(안전운행) 일반 내용, 원문 미확인</t>
@@ -13689,10 +13853,14 @@
       <c r="N168" s="3" t="n"/>
       <c r="O168" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P168" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P168" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q168" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교재 자동차 주요 장치-제동장치(엔진 브레이크). 교재(안전운행) 일반 내용, 원문 미확인</t>
@@ -13764,10 +13932,14 @@
       <c r="N169" s="3" t="n"/>
       <c r="O169" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P169" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P169" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q169" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교재 물리적 현상-워터 페이드. 교재(안전운행) 일반 내용, 원문 미확인 · 교차 점검 반영</t>
@@ -13839,10 +14011,14 @@
       <c r="N170" s="3" t="n"/>
       <c r="O170" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P170" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P170" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q170" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교재 물리적 현상-베이퍼 록 원인. 교재(안전운행) 일반 내용, 원문 미확인</t>
@@ -13914,10 +14090,14 @@
       <c r="N171" s="3" t="n"/>
       <c r="O171" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P171" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P171" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q171" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교재 물리적 현상-스탠딩 웨이브 예방. 교재(안전운행) 일반 내용, 원문 미확인</t>
@@ -13989,10 +14169,14 @@
       <c r="N172" s="3" t="n"/>
       <c r="O172" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P172" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P172" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q172" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교재 물리적 현상-모닝 록 조치. 교재(안전운행) 일반 내용, 원문 미확인</t>
@@ -14064,10 +14248,14 @@
       <c r="N173" s="3" t="n"/>
       <c r="O173" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P173" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P173" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q173" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교재 물리적 현상-내륜차·외륜차. 교재(안전운행) 일반 내용, 원문 미확인</t>
@@ -14139,10 +14327,14 @@
       <c r="N174" s="3" t="n"/>
       <c r="O174" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P174" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P174" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q174" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교재 물리적 현상-내륜차·외륜차. 교재(안전운행) 일반 내용, 원문 미확인</t>
@@ -14214,10 +14406,14 @@
       <c r="N175" s="3" t="n"/>
       <c r="O175" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P175" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P175" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q175" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교재 물리적 현상-원심력. 교재(안전운행) 일반 내용, 원문 미확인</t>
@@ -14289,10 +14485,14 @@
       <c r="N176" s="3" t="n"/>
       <c r="O176" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P176" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P176" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q176" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교재 차량 거동-오버스티어. 교재(안전운행) 일반 내용, 원문 미확인 · 교차 점검 반영</t>
@@ -14364,10 +14564,14 @@
       <c r="N177" s="3" t="n"/>
       <c r="O177" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P177" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P177" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q177" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교재 차량 거동-진동(요잉). 교재(안전운행) 일반 내용, 원문 미확인</t>
@@ -14439,10 +14643,14 @@
       <c r="N178" s="3" t="n"/>
       <c r="O178" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P178" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P178" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q178" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교재 차량 거동-노즈 업. 교재(안전운행) 일반 내용, 원문 미확인</t>
@@ -14514,10 +14722,14 @@
       <c r="N179" s="3" t="n"/>
       <c r="O179" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P179" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P179" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q179" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교재 정지거리·공주거리·제동거리. 교재(안전운행) 일반 내용, 원문 미확인</t>
@@ -14589,10 +14801,14 @@
       <c r="N180" s="3" t="n"/>
       <c r="O180" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P180" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P180" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q180" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교재 정지거리 영향 요인. 교재(안전운행) 일반 내용, 원문 미확인</t>
@@ -14664,10 +14880,14 @@
       <c r="N181" s="3" t="n"/>
       <c r="O181" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P181" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P181" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q181" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 ○: 계산: 90km/h = 25m/s, 25×0.8 = 20m (단위 환산으로 확인)</t>
@@ -14739,10 +14959,14 @@
       <c r="N182" s="3" t="n"/>
       <c r="O182" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P182" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P182" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q182" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교재 타이어 마모 요인. 교재(안전운행) 일반 내용, 원문 미확인</t>
@@ -14814,10 +15038,14 @@
       <c r="N183" s="3" t="n"/>
       <c r="O183" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P183" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P183" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q183" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교재 타이어의 종류-튜브리스. 교재(안전운행) 일반 내용, 원문 미확인</t>
@@ -14889,10 +15117,14 @@
       <c r="N184" s="3" t="n"/>
       <c r="O184" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P184" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P184" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q184" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교재 차량 점검 시 주의사항. 교재(안전운행) 일반 내용, 원문 미확인</t>
@@ -14964,10 +15196,14 @@
       <c r="N185" s="3" t="n"/>
       <c r="O185" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P185" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P185" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q185" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교재 차량 점검·운행 주의사항(트랙터 차량). 교재(안전운행) 일반 내용, 원문 미확인</t>
@@ -15039,10 +15275,14 @@
       <c r="N186" s="3" t="n"/>
       <c r="O186" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P186" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P186" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q186" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교재 운행 전 점검(운전석·엔진 점검 구분). 교재(안전운행) 일반 내용, 원문 미확인</t>
@@ -15114,10 +15354,14 @@
       <c r="N187" s="3" t="n"/>
       <c r="O187" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P187" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P187" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q187" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교재 차량 점검-조향장치. 교재(안전운행) 일반 내용, 원문 미확인</t>
@@ -15189,10 +15433,14 @@
       <c r="N188" s="3" t="n"/>
       <c r="O188" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P188" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P188" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q188" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교재 제동장치-ABS 사용. 교재(안전운행) 일반 내용, 원문 미확인</t>
@@ -15264,10 +15512,14 @@
       <c r="N189" s="3" t="n"/>
       <c r="O189" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P189" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P189" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q189" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교재 안전운행 단원(도로요인·안전운전) 일반 내용, 원문 미대조</t>
@@ -15339,10 +15591,14 @@
       <c r="N190" s="3" t="n"/>
       <c r="O190" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P190" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P190" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q190" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교재 안전운행 단원(도로요인·안전운전) 일반 내용, 원문 미대조</t>
@@ -15414,10 +15670,14 @@
       <c r="N191" s="3" t="n"/>
       <c r="O191" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P191" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P191" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q191" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 ○: 도로의 구조·시설 기준에 관한 규칙 제2조(용어 정의) 편경사; 교재 도로요인 용어 정의 · 교차 점검 반영</t>
@@ -15489,10 +15749,14 @@
       <c r="N192" s="3" t="n"/>
       <c r="O192" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P192" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P192" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q192" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 ○: 도로의 구조·시설 기준에 관한 규칙 제2조 횡단경사 정의(배수 목적)</t>
@@ -15564,10 +15828,14 @@
       <c r="N193" s="3" t="n"/>
       <c r="O193" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P193" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P193" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q193" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교재 안전운행 단원(도로요인·안전운전) 일반 내용, 원문 미대조</t>
@@ -15639,10 +15907,14 @@
       <c r="N194" s="3" t="n"/>
       <c r="O194" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P194" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P194" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q194" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교재 도로요인-방호울타리 구분(노측용·중앙분리대용·보도용·교량용), 원문 미대조</t>
@@ -15714,10 +15986,14 @@
       <c r="N195" s="3" t="n"/>
       <c r="O195" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P195" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P195" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q195" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교재 안전운행 단원(도로요인·안전운전) 일반 내용, 원문 미대조</t>
@@ -15789,10 +16065,14 @@
       <c r="N196" s="3" t="n"/>
       <c r="O196" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P196" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P196" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q196" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교재 중앙분리대 종류(방호울타리형·연석형·광폭) 설명, 원문 미대조</t>
@@ -15864,10 +16144,14 @@
       <c r="N197" s="3" t="n"/>
       <c r="O197" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P197" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P197" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q197" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교재 안전운행 단원(도로요인·안전운전) 일반 내용, 원문 미대조</t>
@@ -15939,10 +16223,14 @@
       <c r="N198" s="3" t="n"/>
       <c r="O198" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P198" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P198" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q198" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교재 안전운행 단원(도로요인·안전운전) 일반 내용, 원문 미대조</t>
@@ -16014,10 +16302,14 @@
       <c r="N199" s="3" t="n"/>
       <c r="O199" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P199" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P199" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q199" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교재 안전운행 단원(도로요인·안전운전) 일반 내용, 원문 미대조</t>
@@ -16089,10 +16381,14 @@
       <c r="N200" s="3" t="n"/>
       <c r="O200" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P200" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P200" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q200" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 ○: 도로의 구조·시설 기준에 관한 규칙 제2조 오르막차로 정의 · 교차 점검 반영</t>
@@ -16164,10 +16460,14 @@
       <c r="N201" s="3" t="n"/>
       <c r="O201" s="3" t="inlineStr">
         <is>
-          <t>draft</t>
-        </is>
-      </c>
-      <c r="P201" s="3" t="n"/>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P201" s="3" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
+        </is>
+      </c>
       <c r="Q201" s="3" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 ○: 도로의 구조·시설 기준에 관한 규칙 제2조 정지시거 정의 · 교차 점검 반영</t>
@@ -16238,7 +16538,12 @@
       </c>
       <c r="O202" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P202" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
         </is>
       </c>
       <c r="Q202" t="inlineStr">
@@ -16311,7 +16616,12 @@
       </c>
       <c r="O203" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P203" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
         </is>
       </c>
       <c r="Q203" t="inlineStr">
@@ -16384,7 +16694,12 @@
       </c>
       <c r="O204" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P204" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
         </is>
       </c>
       <c r="Q204" t="inlineStr">
@@ -16457,7 +16772,12 @@
       </c>
       <c r="O205" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P205" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
         </is>
       </c>
       <c r="Q205" t="inlineStr">
@@ -16530,7 +16850,12 @@
       </c>
       <c r="O206" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P206" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
         </is>
       </c>
       <c r="Q206" t="inlineStr">
@@ -16603,7 +16928,12 @@
       </c>
       <c r="O207" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P207" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
         </is>
       </c>
       <c r="Q207" t="inlineStr">
@@ -16676,7 +17006,12 @@
       </c>
       <c r="O208" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P208" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
         </is>
       </c>
       <c r="Q208" t="inlineStr">
@@ -16749,7 +17084,12 @@
       </c>
       <c r="O209" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P209" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
         </is>
       </c>
       <c r="Q209" t="inlineStr">
@@ -16822,7 +17162,12 @@
       </c>
       <c r="O210" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P210" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
         </is>
       </c>
       <c r="Q210" t="inlineStr">
@@ -16895,7 +17240,12 @@
       </c>
       <c r="O211" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P211" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
         </is>
       </c>
       <c r="Q211" t="inlineStr">
@@ -16968,7 +17318,12 @@
       </c>
       <c r="O212" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P212" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
         </is>
       </c>
       <c r="Q212" t="inlineStr">
@@ -17041,7 +17396,12 @@
       </c>
       <c r="O213" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P213" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
         </is>
       </c>
       <c r="Q213" t="inlineStr">
@@ -17114,7 +17474,12 @@
       </c>
       <c r="O214" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P214" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
         </is>
       </c>
       <c r="Q214" t="inlineStr">
@@ -17187,7 +17552,12 @@
       </c>
       <c r="O215" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P215" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
         </is>
       </c>
       <c r="Q215" t="inlineStr">
@@ -17260,7 +17630,12 @@
       </c>
       <c r="O216" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P216" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
         </is>
       </c>
       <c r="Q216" t="inlineStr">
@@ -17333,7 +17708,12 @@
       </c>
       <c r="O217" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P217" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
         </is>
       </c>
       <c r="Q217" t="inlineStr">
@@ -17406,7 +17786,12 @@
       </c>
       <c r="O218" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P218" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
         </is>
       </c>
       <c r="Q218" t="inlineStr">
@@ -17479,7 +17864,12 @@
       </c>
       <c r="O219" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P219" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
         </is>
       </c>
       <c r="Q219" t="inlineStr">
@@ -17552,7 +17942,12 @@
       </c>
       <c r="O220" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P220" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
         </is>
       </c>
       <c r="Q220" t="inlineStr">
@@ -17625,7 +18020,12 @@
       </c>
       <c r="O221" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P221" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
         </is>
       </c>
       <c r="Q221" t="inlineStr">
@@ -17698,7 +18098,12 @@
       </c>
       <c r="O222" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P222" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
         </is>
       </c>
       <c r="Q222" t="inlineStr">
@@ -17771,7 +18176,12 @@
       </c>
       <c r="O223" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P223" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
         </is>
       </c>
       <c r="Q223" t="inlineStr">
@@ -17844,7 +18254,12 @@
       </c>
       <c r="O224" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P224" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
         </is>
       </c>
       <c r="Q224" t="inlineStr">
@@ -17917,7 +18332,12 @@
       </c>
       <c r="O225" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P225" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
         </is>
       </c>
       <c r="Q225" t="inlineStr">
@@ -17990,7 +18410,12 @@
       </c>
       <c r="O226" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P226" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
         </is>
       </c>
       <c r="Q226" t="inlineStr">
@@ -18063,7 +18488,12 @@
       </c>
       <c r="O227" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P227" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
         </is>
       </c>
       <c r="Q227" t="inlineStr">
@@ -18136,7 +18566,12 @@
       </c>
       <c r="O228" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P228" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
         </is>
       </c>
       <c r="Q228" t="inlineStr">
@@ -18209,7 +18644,12 @@
       </c>
       <c r="O229" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P229" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
         </is>
       </c>
       <c r="Q229" t="inlineStr">
@@ -18282,7 +18722,12 @@
       </c>
       <c r="O230" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P230" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
         </is>
       </c>
       <c r="Q230" t="inlineStr">
@@ -18355,7 +18800,12 @@
       </c>
       <c r="O231" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P231" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
         </is>
       </c>
       <c r="Q231" t="inlineStr">
@@ -18428,7 +18878,12 @@
       </c>
       <c r="O232" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P232" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
         </is>
       </c>
       <c r="Q232" t="inlineStr">
@@ -18501,7 +18956,12 @@
       </c>
       <c r="O233" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P233" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
         </is>
       </c>
       <c r="Q233" t="inlineStr">
@@ -18574,7 +19034,12 @@
       </c>
       <c r="O234" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P234" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
         </is>
       </c>
       <c r="Q234" t="inlineStr">
@@ -18647,7 +19112,12 @@
       </c>
       <c r="O235" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P235" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
         </is>
       </c>
       <c r="Q235" t="inlineStr">
@@ -18720,7 +19190,12 @@
       </c>
       <c r="O236" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P236" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
         </is>
       </c>
       <c r="Q236" t="inlineStr">
@@ -18793,7 +19268,12 @@
       </c>
       <c r="O237" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P237" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
         </is>
       </c>
       <c r="Q237" t="inlineStr">
@@ -18866,7 +19346,12 @@
       </c>
       <c r="O238" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P238" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
         </is>
       </c>
       <c r="Q238" t="inlineStr">
@@ -18939,7 +19424,12 @@
       </c>
       <c r="O239" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P239" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
         </is>
       </c>
       <c r="Q239" t="inlineStr">
@@ -19012,7 +19502,12 @@
       </c>
       <c r="O240" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P240" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
         </is>
       </c>
       <c r="Q240" t="inlineStr">
@@ -19085,7 +19580,12 @@
       </c>
       <c r="O241" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P241" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
         </is>
       </c>
       <c r="Q241" t="inlineStr">
@@ -19158,7 +19658,12 @@
       </c>
       <c r="O242" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P242" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
         </is>
       </c>
       <c r="Q242" t="inlineStr">
@@ -19231,7 +19736,12 @@
       </c>
       <c r="O243" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P243" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
         </is>
       </c>
       <c r="Q243" t="inlineStr">
@@ -19304,7 +19814,12 @@
       </c>
       <c r="O244" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P244" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
         </is>
       </c>
       <c r="Q244" t="inlineStr">
@@ -19377,7 +19892,12 @@
       </c>
       <c r="O245" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P245" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
         </is>
       </c>
       <c r="Q245" t="inlineStr">
@@ -19450,7 +19970,12 @@
       </c>
       <c r="O246" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P246" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
         </is>
       </c>
       <c r="Q246" t="inlineStr">
@@ -19523,7 +20048,12 @@
       </c>
       <c r="O247" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P247" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
         </is>
       </c>
       <c r="Q247" t="inlineStr">
@@ -19596,7 +20126,12 @@
       </c>
       <c r="O248" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P248" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
         </is>
       </c>
       <c r="Q248" t="inlineStr">
@@ -19669,7 +20204,12 @@
       </c>
       <c r="O249" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P249" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
         </is>
       </c>
       <c r="Q249" t="inlineStr">
@@ -19742,7 +20282,12 @@
       </c>
       <c r="O250" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P250" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
         </is>
       </c>
       <c r="Q250" t="inlineStr">
@@ -19815,7 +20360,12 @@
       </c>
       <c r="O251" t="inlineStr">
         <is>
-          <t>draft</t>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P251" t="inlineStr">
+        <is>
+          <t>개발자 / 2026-10-21</t>
         </is>
       </c>
       <c r="Q251" t="inlineStr">

--- a/data/raw/문제_SAFE.xlsx
+++ b/data/raw/문제_SAFE.xlsx
@@ -565,7 +565,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q251"/>
+  <dimension ref="A1:Q376"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -20371,6 +20371,9756 @@
       <c r="Q251" t="inlineStr">
         <is>
           <t>AI 3차 초안(2026-10-21) · 근거 확인 △: 교재 '주의 분산(인지적·시각적·신체적)' 일반 내용 및 교통안전 연구 결과. 원문 미확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>SAFE-0251</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>운전면허 적성검사에서 구별할 수 있어야 하는 색으로 도로교통법 시행령에 정해진 것은?</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>붉은색·녹색·노란색</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>붉은색·파란색·흰색</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t>녹색·파란색·검은색</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>노란색·흰색·주황색</t>
+        </is>
+      </c>
+      <c r="G252" t="n">
+        <v>1</v>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>도로교통법 시행령 제45조제1항제2호는 붉은색·녹색 및 노란색을 구별할 수 있을 것을 적성 기준으로 정한다. 신호등에 쓰이는 색과 같다.</t>
+        </is>
+      </c>
+      <c r="I252" t="inlineStr">
+        <is>
+          <t>교차로 신호등에 켜지는 등화의 색을 떠올려 보세요.</t>
+        </is>
+      </c>
+      <c r="J252" t="inlineStr">
+        <is>
+          <t>도로교통법 시행령 제45조</t>
+        </is>
+      </c>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L252" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M252" t="n">
+        <v>1</v>
+      </c>
+      <c r="O252" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P252" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q252" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 도로교통법 시행령 제45조제1항(국가법령정보센터 law.go.kr 현행 조문 확인, 2026-10-21) 제2호</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>SAFE-0252</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>제1종 대형면허나 특수면허를 받으려는 사람(보청기를 쓰지 않음)이 들을 수 있어야 하는 소리의 크기 기준은?</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>25데시벨</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>40데시벨</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>55데시벨</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>70데시벨</t>
+        </is>
+      </c>
+      <c r="G253" t="n">
+        <v>3</v>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>시행령 제45조제1항제3호에 따라 55데시벨(보청기 사용자는 40데시벨)의 소리를 들을 수 있어야 하며, 이 기준은 제1종 대형·특수면허에만 적용된다.</t>
+        </is>
+      </c>
+      <c r="I253" t="inlineStr">
+        <is>
+          <t>보청기를 쓰는 사람에게는 더 작은 소리 기준이 따로 있습니다. 보기 중 그 값은 보청기 사용자용입니다.</t>
+        </is>
+      </c>
+      <c r="J253" t="inlineStr">
+        <is>
+          <t>도로교통법 시행령 제45조</t>
+        </is>
+      </c>
+      <c r="K253" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L253" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M253" t="n">
+        <v>3</v>
+      </c>
+      <c r="O253" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P253" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q253" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 도로교통법 시행령 제45조제1항(국가법령정보센터 law.go.kr 현행 조문 확인, 2026-10-21) 제3호 및 각 호 외 부분 단서</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>SAFE-0253</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>운전면허 적성 기준 중 '일정 크기의 소리를 들을 수 있을 것'이라는 청력 기준이 적용되는 경우는?</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>제2종 보통면허를 받으려는 경우</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>제1종 보통면허를 받으려는 경우</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>원동기장치자전거면허를 받으려는 경우</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>제1종 대형면허나 특수면허를 받으려는 경우</t>
+        </is>
+      </c>
+      <c r="G254" t="n">
+        <v>4</v>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>시행령 제45조제1항 단서는 청력 기준(제3호)을 제1종 운전면허 중 대형면허 또는 특수면허를 취득하려는 경우에만 적용한다고 정한다.</t>
+        </is>
+      </c>
+      <c r="I254" t="inlineStr">
+        <is>
+          <t>큰 차나 특수한 차를 몰 때 경음기·경보음을 듣는 능력이 더 중요해집니다.</t>
+        </is>
+      </c>
+      <c r="J254" t="inlineStr">
+        <is>
+          <t>도로교통법 시행령 제45조</t>
+        </is>
+      </c>
+      <c r="K254" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L254" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M254" t="n">
+        <v>2</v>
+      </c>
+      <c r="O254" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P254" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q254" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 도로교통법 시행령 제45조제1항(국가법령정보센터 law.go.kr 현행 조문 확인, 2026-10-21) 각 호 외 부분 단서</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>SAFE-0254</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>제2종 운전면허에 필요한 시력 기준(교정시력 포함, 두 눈을 모두 볼 수 있는 사람)으로 옳은 것은?</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>두 눈을 동시에 뜨고 잰 시력 0.3 이상</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>두 눈의 시력이 각각 1.0 이상</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>두 눈을 동시에 뜨고 잰 시력 0.8 이상</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>두 눈을 동시에 뜨고 잰 시력 0.5 이상</t>
+        </is>
+      </c>
+      <c r="G255" t="n">
+        <v>4</v>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>시행령 제45조제1항제1호나목은 제2종 운전면허의 시력 기준을 두 눈을 동시에 뜨고 잰 시력 0.5 이상으로 정한다. 0.8 이상은 제1종 기준이다.</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr">
+        <is>
+          <t>제2종은 제1종처럼 두 눈을 따로 재지 않고, 두 눈을 함께 뜨고 잰 값만 봅니다.</t>
+        </is>
+      </c>
+      <c r="J255" t="inlineStr">
+        <is>
+          <t>도로교통법 시행령 제45조</t>
+        </is>
+      </c>
+      <c r="K255" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L255" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M255" t="n">
+        <v>2</v>
+      </c>
+      <c r="O255" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P255" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q255" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 도로교통법 시행령 제45조제1항(국가법령정보센터 law.go.kr 현행 조문 확인, 2026-10-21) 제1호나목 · 교차 점검 반영</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>SAFE-0255</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>한쪽 눈을 보지 못하는 사람이 제2종 운전면허를 받으려 할 때 다른 쪽 눈에 필요한 시력은?</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>0.4 이상</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>0.5 이상</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>0.6 이상</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>1.0 이상</t>
+        </is>
+      </c>
+      <c r="G256" t="n">
+        <v>3</v>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>시행령 제45조제1항제1호나목 단서에 따라 한쪽 눈을 보지 못하는 사람은 다른 쪽 눈의 시력이 0.6 이상이어야 제2종 면허를 받을 수 있다.</t>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr">
+        <is>
+          <t>한 눈만으로 보는 만큼, 두 눈을 함께 뜨고 잴 때보다 기준이 엄격해집니다.</t>
+        </is>
+      </c>
+      <c r="J256" t="inlineStr">
+        <is>
+          <t>도로교통법 시행령 제45조</t>
+        </is>
+      </c>
+      <c r="K256" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L256" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M256" t="n">
+        <v>3</v>
+      </c>
+      <c r="O256" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P256" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q256" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 도로교통법 시행령 제45조제1항(국가법령정보센터 law.go.kr 현행 조문 확인, 2026-10-21) 제1호나목 단서 · 교차 점검 반영</t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>SAFE-0256</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>한쪽 눈을 보지 못하는 사람이 제1종 보통면허를 받으려 할 때 갖추어야 할 기준으로 옳은 것은?</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>다른 쪽 눈의 시력 0.5 이상만 갖추면 된다</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>다른 쪽 눈의 시력 0.8 이상이고 수평시야가 120도 이상이어야 한다</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>제1종 보통면허는 받을 수 없다</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>다른 쪽 눈의 시력 0.6 이상이고 색 구별 검사는 면제된다</t>
+        </is>
+      </c>
+      <c r="G257" t="n">
+        <v>2</v>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>시행령 제45조제1항제1호가목 단서는 이 경우 다른 쪽 눈 시력 0.8 이상, 수평시야 120도 이상, 수직시야 20도 이상, 중심시야 20도 내 암점·반맹이 없을 것을 요구한다.</t>
+        </is>
+      </c>
+      <c r="I257" t="inlineStr">
+        <is>
+          <t>한쪽 눈만으로 운전하면 시력뿐 아니라 좌우로 볼 수 있는 범위도 함께 따집니다.</t>
+        </is>
+      </c>
+      <c r="J257" t="inlineStr">
+        <is>
+          <t>도로교통법 시행령 제45조</t>
+        </is>
+      </c>
+      <c r="K257" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L257" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M257" t="n">
+        <v>3</v>
+      </c>
+      <c r="O257" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P257" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q257" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 도로교통법 시행령 제45조제1항(국가법령정보센터 law.go.kr 현행 조문 확인, 2026-10-21) 제1호가목 단서</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>SAFE-0257</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>정면을 보고 있을 때 시야 가장자리에서 물체의 움직임을 알아차리게 해 주는 시각 기능에 대한 설명으로 옳은 것은?</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>주변시로, 세밀한 모양은 잘 못 보지만 움직임을 감지해 위험 방향으로 눈을 돌리게 한다</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>중심시로, 색과 글자를 가장 정확하게 구별한다</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>심시력으로, 물체까지의 거리를 정확히 잰다</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>명순응으로, 밝은 빛에 눈을 적응시킨다</t>
+        </is>
+      </c>
+      <c r="G258" t="n">
+        <v>1</v>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>주변시는 시야 바깥쪽 영역의 시각으로 해상도는 낮지만 움직임에 민감해, 옆에서 다가오는 차·보행자를 먼저 알아차리게 한다. 정확한 식별은 중심시가 맡는다.</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr">
+        <is>
+          <t>눈동자 정면이 아닌 가장자리 영역이 하는 일을 생각해 보세요.</t>
+        </is>
+      </c>
+      <c r="J258" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K258" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L258" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M258" t="n">
+        <v>2</v>
+      </c>
+      <c r="O258" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P258" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q258" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 시각 일반 이론(중심시·주변시). 교재 시야 단원과 일치하는 일반 지식, 원문 미확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>SAFE-0258</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>야간에 도로 위에 '무엇인가 있다'는 것을 가장 먼저 알아차리기 쉬운 보행자의 옷 색깔로 교재에 제시된 것은?</t>
+        </is>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>흑색</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>흰색</t>
+        </is>
+      </c>
+      <c r="E259" t="inlineStr">
+        <is>
+          <t>청색</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>적색</t>
+        </is>
+      </c>
+      <c r="G259" t="n">
+        <v>2</v>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>교재는 무엇인가 있다는 것을 인지하는 데는 흰색, 엷은 황색 순으로 좋고 흑색이 가장 어렵다고 설명한다. 적색은 움직이는 방향을 알아맞히기 쉬운 색이다.</t>
+        </is>
+      </c>
+      <c r="I259" t="inlineStr">
+        <is>
+          <t>어둠 속에서 밝게 보이는 정도가 '존재 인지'를 좌우합니다. 흑색은 가장 늦게 보이는 색으로 알려져 있습니다.</t>
+        </is>
+      </c>
+      <c r="J259" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K259" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L259" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M259" t="n">
+        <v>2</v>
+      </c>
+      <c r="O259" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P259" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q259" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 교재 일반 내용(안전운행 - 운전자 요인, 야간시력). 기존 SAFE-0008(흑색 가장 늦음)·0130(방향=적색)과 다른 항목. 원문 미확인 · 교차 점검 반영</t>
+        </is>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>SAFE-0259</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>운전 중 일어나는 '원근의 착각'에 대한 설명으로 옳은 것은?</t>
+        </is>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>큰 물체는 실제보다 멀리 있는 것처럼 보인다</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>오르막은 실제보다 완만하게 보인다</t>
+        </is>
+      </c>
+      <c r="E260" t="inlineStr">
+        <is>
+          <t>작은 물체나 덜 밝은 물체는 실제보다 멀리 있는 것처럼 느껴진다</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>빠른 차는 실제보다 느리게 느껴진다</t>
+        </is>
+      </c>
+      <c r="G260" t="n">
+        <v>3</v>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>원근의 착각은 작은 것은 멀리, 덜 밝은 것은 멀리 있는 것처럼 느끼는 현상이다. 그래서 작은 이륜차나 어두운 물체와의 거리를 실제보다 길게 판단하기 쉽다.</t>
+        </is>
+      </c>
+      <c r="I260" t="inlineStr">
+        <is>
+          <t>크기와 밝기가 거리 판단에 어떤 단서로 쓰이는지 생각해 보세요.</t>
+        </is>
+      </c>
+      <c r="J260" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K260" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L260" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M260" t="n">
+        <v>2</v>
+      </c>
+      <c r="O260" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P260" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q260" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 교재 일반 내용(안전운행 - 사고의 심리, 착각의 종류). 기존 경사·속도·상반의 착각과 다른 항목, 원문 미확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>SAFE-0260</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>운전자의 반응시간에 대한 설명으로 옳은 것은?</t>
+        </is>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>경험이 많으면 상황과 관계없이 반응시간이 일정하다</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>나이가 들수록 반응시간이 짧아진다</t>
+        </is>
+      </c>
+      <c r="E261" t="inlineStr">
+        <is>
+          <t>선택해야 할 대상이나 행동이 많을수록 반응시간이 길어진다</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>예상하고 있던 위험일수록 반응시간이 길어진다</t>
+        </is>
+      </c>
+      <c r="G261" t="n">
+        <v>3</v>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>여러 가능성 가운데 하나를 골라 반응해야 하는 선택반응은 단순반응보다 오래 걸리며, 고를 대상이 많을수록 더 길어진다. 예상한 위험에는 오히려 빨리 반응한다.</t>
+        </is>
+      </c>
+      <c r="I261" t="inlineStr">
+        <is>
+          <t>복잡한 교차로와 한적한 직선도로에서 판단에 걸리는 시간을 비교해 보세요.</t>
+        </is>
+      </c>
+      <c r="J261" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K261" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L261" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M261" t="n">
+        <v>2</v>
+      </c>
+      <c r="O261" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P261" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q261" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 인간공학 일반 이론(단순반응·선택반응, 힉의 법칙). 교재 반응시간 단원과 맞는 일반 지식</t>
+        </is>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>SAFE-0261</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>운전 피로의 요인을 생활 요인, 운전작업 중의 요인, 운전자 요인으로 나눌 때 '운전자 요인'에 해당하는 것은?</t>
+        </is>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>수면 부족과 불규칙한 생활</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>운전석의 소음과 진동</t>
+        </is>
+      </c>
+      <c r="E262" t="inlineStr">
+        <is>
+          <t>교통 정체와 도로 조건</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>운전자의 신체 조건·경험·연령·성격</t>
+        </is>
+      </c>
+      <c r="G262" t="n">
+        <v>4</v>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>교재는 운전자 자신의 신체 조건, 경험, 연령, 성별, 성격, 질병 등을 운전자 요인으로 분류한다. 수면·생활환경은 생활 요인, 차내 환경·운전 조건은 운전작업 중의 요인이다.</t>
+        </is>
+      </c>
+      <c r="I262" t="inlineStr">
+        <is>
+          <t>사람마다 타고나거나 쌓아 온 개인적 특성을 떠올려 보세요.</t>
+        </is>
+      </c>
+      <c r="J262" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K262" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L262" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M262" t="n">
+        <v>2</v>
+      </c>
+      <c r="O262" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P262" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q262" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 교재 일반 내용(안전운행 - 운전 피로의 요인). 기존 SAFE-0143은 운전작업 중 요인을 물음, 원문 미확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>SAFE-0262</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>운전 피로를 회복하는 방법으로 가장 근본적이고 효과적인 것은?</t>
+        </is>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>진한 커피나 에너지 음료를 연달아 마신다</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>창문을 열고 음악 소리를 크게 높인다</t>
+        </is>
+      </c>
+      <c r="E263" t="inlineStr">
+        <is>
+          <t>충분한 수면과 휴식을 취한다</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>껌을 씹으며 계속 운전한다</t>
+        </is>
+      </c>
+      <c r="G263" t="n">
+        <v>3</v>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>피로 회복에는 충분한 수면이 가장 효과적이다. 카페인·찬 바람·음악은 잠깐 졸음을 늦출 뿐 쌓인 피로를 없애지 못한다.</t>
+        </is>
+      </c>
+      <c r="I263" t="inlineStr">
+        <is>
+          <t>잠깐 정신을 깨우는 방법과 몸을 실제로 회복시키는 방법을 구분해 보세요.</t>
+        </is>
+      </c>
+      <c r="J263" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K263" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L263" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M263" t="n">
+        <v>1</v>
+      </c>
+      <c r="O263" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P263" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q263" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 교재 일반 내용(안전운행 - 운전 피로). 일반적인 피로 회복 원칙</t>
+        </is>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>SAFE-0263</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>졸린 상태로 운전할 때 운전자가 스스로 알아차리지 못한 채 몇 초 동안 잠에 빠지는 현상을 무엇이라 하는가?</t>
+        </is>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>미세수면</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>명순응</t>
+        </is>
+      </c>
+      <c r="E264" t="inlineStr">
+        <is>
+          <t>현혹현상</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>시야 협착</t>
+        </is>
+      </c>
+      <c r="G264" t="n">
+        <v>1</v>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>미세수면은 1~수 초 동안 의식이 끊기는 짧은 잠으로, 시속 100킬로미터라면 그 사이 수십 미터를 무방비로 달리게 된다.</t>
+        </is>
+      </c>
+      <c r="I264" t="inlineStr">
+        <is>
+          <t>의식이 끊긴 순간을 운전자 자신이 기억하지 못한다는 점이 특징입니다.</t>
+        </is>
+      </c>
+      <c r="J264" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K264" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L264" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M264" t="n">
+        <v>1</v>
+      </c>
+      <c r="O264" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P264" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q264" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 수면의학·교통안전 일반 개념(micro-sleep). 교재 졸음운전 단원 관련 · 교차 점검 반영</t>
+        </is>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>SAFE-0264</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>밤에 잠을 자도 낮에 심한 졸음이 계속되는 운전자에게 의심할 수 있고, 졸음운전 위험을 높이는 질환은?</t>
+        </is>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>근시</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>수면무호흡증</t>
+        </is>
+      </c>
+      <c r="E265" t="inlineStr">
+        <is>
+          <t>평발</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>충치</t>
+        </is>
+      </c>
+      <c r="G265" t="n">
+        <v>2</v>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>수면무호흡증은 잠자는 동안 호흡이 반복해서 멈춰 깊은 잠을 못 자게 하므로 낮 동안 졸음이 심해진다. 직업 운전자라면 진료와 치료를 받는 것이 좋다.</t>
+        </is>
+      </c>
+      <c r="I265" t="inlineStr">
+        <is>
+          <t>밤새 깊은 잠을 방해받아 낮에 졸리게 되는 질환입니다. 코골이가 심한 사람에게 흔합니다.</t>
+        </is>
+      </c>
+      <c r="J265" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K265" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L265" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M265" t="n">
+        <v>2</v>
+      </c>
+      <c r="O265" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P265" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q265" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 의학 일반 지식(폐쇄성 수면무호흡과 주간 졸림). 교통안전공단 졸음운전 예방 자료 취지 · 교차 점검 반영</t>
+        </is>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>SAFE-0265</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>당뇨병 치료 중인 운전자가 운전 중 식은땀이 나고 손이 떨리며 어지러워졌다. 알맞은 대처는?</t>
+        </is>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>목적지까지 속도를 높여 빨리 간다</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>창문을 열고 계속 운전한다</t>
+        </is>
+      </c>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>안전한 곳에 차를 세우고 사탕·주스 등으로 당분을 보충한 뒤 회복될 때까지 쉰다</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>인슐린을 한 번 더 투여하고 운전을 계속한다</t>
+        </is>
+      </c>
+      <c r="G266" t="n">
+        <v>3</v>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>식은땀·떨림·어지러움은 저혈당 증상일 수 있으며 의식 저하로 이어질 수 있다. 즉시 차를 세우고 당분을 섭취하며 회복될 때까지 운전하지 않아야 한다.</t>
+        </is>
+      </c>
+      <c r="I266" t="inlineStr">
+        <is>
+          <t>혈액 속 어떤 성분이 부족할 때 나타나는 증상인지 생각해 보세요.</t>
+        </is>
+      </c>
+      <c r="J266" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K266" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L266" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M266" t="n">
+        <v>2</v>
+      </c>
+      <c r="O266" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P266" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q266" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 의학 일반 지식(저혈당 증상과 응급 대처)</t>
+        </is>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>SAFE-0266</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>겨울철 창문을 모두 닫고 시동을 켠 채 히터를 틀어 놓고 차 안에서 잠을 잘 때 가장 우려되는 위험은?</t>
+        </is>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>타이어 공기압 상승</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>브레이크 페이드</t>
+        </is>
+      </c>
+      <c r="E267" t="inlineStr">
+        <is>
+          <t>배터리 과충전</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>배기가스 속 일산화탄소에 의한 중독</t>
+        </is>
+      </c>
+      <c r="G267" t="n">
+        <v>4</v>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>배기관 주변이 막히거나 차체 틈으로 배기가스가 들어오면 무색·무취의 일산화탄소에 중독될 수 있다. 공회전 상태로 밀폐된 차 안에서 자지 않고 수시로 환기한다.</t>
+        </is>
+      </c>
+      <c r="I267" t="inlineStr">
+        <is>
+          <t>색도 냄새도 없는 가스가 문제입니다.</t>
+        </is>
+      </c>
+      <c r="J267" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K267" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L267" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M267" t="n">
+        <v>1</v>
+      </c>
+      <c r="O267" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P267" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q267" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 안전 일반 지식(공회전 차내 일산화탄소 중독 사고). 교재 겨울철 운전 주의 취지</t>
+        </is>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>SAFE-0267</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>직업 운전자의 스트레스 관리 방법으로 바람직하지 않은 것은?</t>
+        </is>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>규칙적으로 운동하고 충분히 잠을 잔다</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>운행 계획을 여유 있게 세워 시간에 쫓기지 않는다</t>
+        </is>
+      </c>
+      <c r="E268" t="inlineStr">
+        <is>
+          <t>운행이 끝나면 매일 술을 마셔 긴장을 푼다</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>동료나 가족과 고민을 나누고 취미 활동을 한다</t>
+        </is>
+      </c>
+      <c r="G268" t="n">
+        <v>3</v>
+      </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>습관적인 음주는 수면의 질을 떨어뜨리고 다음 날 숙취 운전으로 이어질 수 있어 바람직하지 않다. 운동·수면·여유 있는 일정·대화는 좋은 관리 방법이다.</t>
+        </is>
+      </c>
+      <c r="I268" t="inlineStr">
+        <is>
+          <t>잠깐 긴장을 풀어 주는 듯해도 다음 날 운전에 해가 되는 것을 고르세요.</t>
+        </is>
+      </c>
+      <c r="J268" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K268" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L268" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M268" t="n">
+        <v>1</v>
+      </c>
+      <c r="O268" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P268" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q268" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 건강관리 일반 지식. 기존 SAFE-0094(운전 중 감정)와 다른 각도</t>
+        </is>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>SAFE-0268</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>고속도로처럼 단조로운 길을 오래 달릴 때 의식이 흐려지고 멍해져 반응이 둔해지는 현상과 그 예방법을 바르게 짝지은 것은?</t>
+        </is>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>수막현상 – 타이어 공기압을 낮춘다</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>고속도로 최면 – 시선을 자주 옮기고 정기적으로 휴식한다</t>
+        </is>
+      </c>
+      <c r="E269" t="inlineStr">
+        <is>
+          <t>증발현상 – 상향등을 계속 켠다</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>페이드 현상 – 엔진 브레이크를 쓴다</t>
+        </is>
+      </c>
+      <c r="G269" t="n">
+        <v>2</v>
+      </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>고속도로 최면은 변화 없는 풍경과 일정한 소음·진동 속에서 의식 수준이 떨어지는 현상이다. 시선을 계속 움직이고, 계기와 후사경을 살피며, 쉬어 가는 것이 예방법이다.</t>
+        </is>
+      </c>
+      <c r="I269" t="inlineStr">
+        <is>
+          <t>단조로운 자극이 사람을 몽롱하게 만드는 상태를 가리키는 말입니다.</t>
+        </is>
+      </c>
+      <c r="J269" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K269" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L269" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M269" t="n">
+        <v>2</v>
+      </c>
+      <c r="O269" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P269" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q269" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 교통심리 일반 개념(highway hypnosis). 교재 고속도로 운전 단원 취지</t>
+        </is>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>SAFE-0269</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>보행자가 횡단보도가 아닌 곳으로 길을 건너는 심리로 보기 어려운 것은?</t>
+        </is>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>횡단보도까지 가는 거리가 멀어서</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>바쁘고 급한 마음에 빨리 건너려고</t>
+        </is>
+      </c>
+      <c r="E270" t="inlineStr">
+        <is>
+          <t>차가 오고 있지만 충분히 건널 수 있다고 판단해서</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>차량 운전자가 반드시 정지해 줄 것이 법으로 보장되어 있어서</t>
+        </is>
+      </c>
+      <c r="G270" t="n">
+        <v>4</v>
+      </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>교재는 횡단거리를 줄이려는 마음, 평소 습관, 바쁨, 차가 와도 건널 수 있다는 판단 등을 무단횡단 심리로 든다. 횡단보도 외 장소에서 차가 반드시 멈춘다는 법적 보장은 없다.</t>
+        </is>
+      </c>
+      <c r="I270" t="inlineStr">
+        <is>
+          <t>보행자 자신의 편의나 착각과 관계없는, 사실과 다른 보기를 고르세요.</t>
+        </is>
+      </c>
+      <c r="J270" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K270" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L270" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M270" t="n">
+        <v>2</v>
+      </c>
+      <c r="O270" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P270" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q270" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 교재 일반 내용(안전운행 - 보행자 요인). 원문 미확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>SAFE-0270</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>보행자의 교통 행동 특성으로 운전자가 알아 두어야 할 것은?</t>
+        </is>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>보행자는 차를 보면 운전자도 자기를 보았을 것이라고 여기기 쉽다</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>보행자는 항상 차의 속도와 거리를 정확히 판단한다</t>
+        </is>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>보행자는 경음기를 울리면 언제나 즉시 멈춘다</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>보행자는 야간에 자신이 운전자에게 잘 보이지 않는다는 것을 늘 알고 있다</t>
+        </is>
+      </c>
+      <c r="G271" t="n">
+        <v>1</v>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>보행자는 차의 전조등을 보면 운전자도 자신을 보았다고 생각하기 쉽지만, 운전자는 보행자를 못 본 경우가 많다. 그래서 운전자가 먼저 보행자를 예상하고 대비해야 한다.</t>
+        </is>
+      </c>
+      <c r="I271" t="inlineStr">
+        <is>
+          <t>보행자 입장에서 '내가 보이니 상대도 나를 보겠지'라는 생각을 떠올려 보세요.</t>
+        </is>
+      </c>
+      <c r="J271" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K271" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L271" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M271" t="n">
+        <v>2</v>
+      </c>
+      <c r="O271" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P271" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q271" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 교통심리 일반 지식(보행자의 가시성 과대평가). 교재 보행자 단원 취지</t>
+        </is>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>SAFE-0271</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>도로 가장자리를 달리는 자전거를 뒤따라갈 때 특히 예상해야 할 행동은?</t>
+        </is>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>자전거는 항상 일정한 속도로 직진만 한다</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>자전거는 차보다 빨라 곧 멀어진다</t>
+        </is>
+      </c>
+      <c r="E272" t="inlineStr">
+        <is>
+          <t>맨홀·웅덩이·주차된 차를 피하려고 갑자기 차로 안쪽으로 들어올 수 있다</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>자전거는 뒤쪽 소리를 잘 들으므로 경음기로 비키게 하면 된다</t>
+        </is>
+      </c>
+      <c r="G272" t="n">
+        <v>3</v>
+      </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>자전거는 노면 장애물이나 주차 차량을 피하려고 예고 없이 진로를 바꿀 수 있고 바람에도 흔들린다. 충분한 간격을 두고 서행하며 예상 운전을 해야 한다.</t>
+        </is>
+      </c>
+      <c r="I272" t="inlineStr">
+        <is>
+          <t>도로 가장자리에는 자전거가 피해 가야 할 것들이 많습니다.</t>
+        </is>
+      </c>
+      <c r="J272" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K272" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L272" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M272" t="n">
+        <v>1</v>
+      </c>
+      <c r="O272" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P272" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q272" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 교통안전 일반 지식. 기존 SAFE-0101(옆 간격)과 다른 각도</t>
+        </is>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>SAFE-0272</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>이륜자동차를 뒤따라갈 때 승용차를 뒤따를 때보다 차간거리를 더 두어야 하는 이유로 옳은 것은?</t>
+        </is>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>이륜차는 제동등이 없기 때문에</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>노면 상태에 따라 넘어지거나 갑자기 진로를 바꿀 수 있기 때문에</t>
+        </is>
+      </c>
+      <c r="E273" t="inlineStr">
+        <is>
+          <t>이륜차는 항상 차보다 늦게 멈추기 때문에</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>이륜차는 후사경이 없기 때문에</t>
+        </is>
+      </c>
+      <c r="G273" t="n">
+        <v>2</v>
+      </c>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>이륜차는 바퀴가 둘이라 모래·물·노면 패임에 쉽게 균형을 잃고 넘어지거나 피하려고 진로를 바꾼다. 넘어진 운전자를 치지 않도록 넉넉히 거리를 둔다.</t>
+        </is>
+      </c>
+      <c r="I273" t="inlineStr">
+        <is>
+          <t>바퀴가 두 개인 차의 균형 문제를 생각해 보세요.</t>
+        </is>
+      </c>
+      <c r="J273" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K273" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L273" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M273" t="n">
+        <v>1</v>
+      </c>
+      <c r="O273" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P273" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q273" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 교통안전 일반 지식. 기존 SAFE-0100(작아 멀어 보임)과 다른 각도</t>
+        </is>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>SAFE-0273</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>대형 화물자동차 운전석에서 볼 때 사각지대가 가장 넓어 차로 변경·우회전 시 특히 주의해야 하는 쪽은?</t>
+        </is>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>운전석 쪽(왼쪽) 뒤</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>차 바로 뒤 중앙 위쪽</t>
+        </is>
+      </c>
+      <c r="E274" t="inlineStr">
+        <is>
+          <t>적재함 지붕 위</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>조수석 쪽(오른쪽) 옆과 앞 아래</t>
+        </is>
+      </c>
+      <c r="G274" t="n">
+        <v>4</v>
+      </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>운전석이 왼쪽에 있어 반대편인 오른쪽 옆과 앞 아래가 가장 보기 어렵다. 우측 보조 거울을 살피고 오른쪽 차로 변경·우회전은 특히 천천히 한다.</t>
+        </is>
+      </c>
+      <c r="I274" t="inlineStr">
+        <is>
+          <t>운전자가 앉은 자리에서 가장 먼 쪽이 어디인지 생각해 보세요.</t>
+        </is>
+      </c>
+      <c r="J274" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K274" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L274" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M274" t="n">
+        <v>2</v>
+      </c>
+      <c r="O274" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P274" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q274" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 교통안전공단 대형차 사각지대 안내 취지(일반 지식). 기존 SAFE-0093(일반)·0249(앞쪽)과 다른 방향</t>
+        </is>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>SAFE-0274</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>짐을 가득 실은 대형 화물자동차가 앞지르기를 할 때 주의할 점으로 옳은 것은?</t>
+        </is>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>가속 능력이 낮아 앞지르기에 걸리는 시간과 거리가 길므로 충분한 여유가 있을 때만 한다</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>차체가 커서 상대 차가 피해 주므로 짧은 거리에서도 할 수 있다</t>
+        </is>
+      </c>
+      <c r="E275" t="inlineStr">
+        <is>
+          <t>무게 때문에 가속이 빠르므로 오르막에서 하는 것이 좋다</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>앞지르기 후 곧바로 앞지른 차 앞으로 바짝 들어간다</t>
+        </is>
+      </c>
+      <c r="G275" t="n">
+        <v>1</v>
+      </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>무거운 대형차는 출력에 비해 가속이 느리고 차체가 길어 반대 차로나 옆 차로에 머무는 시간이 길다. 앞쪽 여유가 충분할 때만 하고, 마친 뒤에는 넉넉한 간격을 두고 복귀한다.</t>
+        </is>
+      </c>
+      <c r="I275" t="inlineStr">
+        <is>
+          <t>무게가 늘면 속도를 올리는 데 어떤 영향이 있는지 생각해 보세요.</t>
+        </is>
+      </c>
+      <c r="J275" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K275" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L275" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M275" t="n">
+        <v>1</v>
+      </c>
+      <c r="O275" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P275" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q275" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 차량 동역학 일반 지식</t>
+        </is>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>SAFE-0275</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>트랙터와 트레일러를 연결한 차가 미끄러운 길에서 급제동할 때 트레일러가 트랙터를 밀어 연결 부위가 'ㄱ'자로 꺾이는 현상은?</t>
+        </is>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>스탠딩 웨이브 현상</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>모닝 록 현상</t>
+        </is>
+      </c>
+      <c r="E276" t="inlineStr">
+        <is>
+          <t>하이드로플레이닝</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>잭나이프 현상</t>
+        </is>
+      </c>
+      <c r="G276" t="n">
+        <v>4</v>
+      </c>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>잭나이프 현상은 트랙터 바퀴가 먼저 잠기거나 미끄러질 때 관성으로 밀고 들어오는 트레일러 때문에 연결부가 접이식 칼처럼 꺾이는 현상이다. 급제동·급핸들을 피하는 것이 예방법이다.</t>
+        </is>
+      </c>
+      <c r="I276" t="inlineStr">
+        <is>
+          <t>트레일러가 트랙터보다 덜 감속되며 관성으로 밀고 들어올 때 생기는 현상입니다.</t>
+        </is>
+      </c>
+      <c r="J276" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K276" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L276" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M276" t="n">
+        <v>2</v>
+      </c>
+      <c r="O276" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P276" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q276" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 연결차량 일반 이론(jackknife). 교재 트레일러 운행 주의 취지 · 교차 점검 반영</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>SAFE-0276</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>화물을 싣지 않은 빈 화물자동차로 급제동할 때 특히 생기기 쉬운 현상은?</t>
+        </is>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>앞바퀴 공기압이 급격히 오른다</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>제동거리가 적재 때보다 몇 배로 늘어난다</t>
+        </is>
+      </c>
+      <c r="E277" t="inlineStr">
+        <is>
+          <t>뒷바퀴에 걸리는 하중이 작아 뒷바퀴가 쉽게 잠겨 미끄러진다</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>엔진 과열이 일어난다</t>
+        </is>
+      </c>
+      <c r="G277" t="n">
+        <v>3</v>
+      </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>빈 차는 뒤쪽 하중이 작아 뒷바퀴의 접지력이 약하므로 급제동 때 뒷바퀴가 먼저 잠기고 차 뒤가 흔들리기 쉽다. 빈 차라도 브레이크는 미리 나누어 밟는다.</t>
+        </is>
+      </c>
+      <c r="I277" t="inlineStr">
+        <is>
+          <t>적재함 아래 바퀴를 노면에 눌러 주는 무게가 사라진 상태를 생각해 보세요.</t>
+        </is>
+      </c>
+      <c r="J277" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L277" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M277" t="n">
+        <v>3</v>
+      </c>
+      <c r="O277" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P277" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q277" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 차량 동역학 일반 지식(공차 시 후륜 하중 감소와 후륜 록)</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>SAFE-0277</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>유압 브레이크에 쓰이는 진공 배력장치(하이드로 백 등)의 원리로 옳은 것은?</t>
+        </is>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>엔진 흡기 쪽의 진공(부압)과 대기압의 차이를 이용해 페달 밟는 힘을 키운다</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>배기가스 압력으로 브레이크 라이닝을 밀어 준다</t>
+        </is>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>전동기로 바퀴를 거꾸로 돌려 감속한다</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>타이어 공기압을 이용해 제동한다</t>
+        </is>
+      </c>
+      <c r="G278" t="n">
+        <v>1</v>
+      </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>진공 배력장치는 엔진 흡기다기관 등의 부압과 대기압의 차이로 생기는 힘을 더해 적은 페달 힘으로도 큰 제동력을 얻게 한다. 그래서 엔진이 꺼지면 페달이 무거워진다.</t>
+        </is>
+      </c>
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>엔진이 공기를 빨아들일 때 생기는 낮은 압력을 떠올려 보세요.</t>
+        </is>
+      </c>
+      <c r="J278" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L278" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M278" t="n">
+        <v>3</v>
+      </c>
+      <c r="O278" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P278" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q278" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 자동차 구조 일반 이론(진공 배력식 브레이크). 기존 SAFE-0082는 시동 꺼짐 조치만 물음</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>SAFE-0278</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>공기 브레이크 장치에서 엔진의 힘으로 압축공기를 만들어 공기탱크로 보내는 장치는?</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>브레이크 챔버</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>릴레이 밸브</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>공기압축기</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>쇽업소버</t>
+        </is>
+      </c>
+      <c r="G279" t="n">
+        <v>3</v>
+      </c>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>공기압축기가 만든 압축공기는 공기탱크에 저장되었다가, 브레이크 밸브를 거쳐 각 바퀴의 브레이크 챔버로 보내져 제동이 이루어진다.</t>
+        </is>
+      </c>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>공기를 눌러 압력을 높이는 장치를 고르세요.</t>
+        </is>
+      </c>
+      <c r="J279" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L279" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M279" t="n">
+        <v>1</v>
+      </c>
+      <c r="O279" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P279" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q279" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 자동차 구조 일반 이론(공기식 브레이크 구성)</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>SAFE-0279</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>공기 브레이크의 특징으로 옳지 않은 것은?</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>차량 중량에 크게 제한받지 않아 대형차에 적합하다</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>공기가 조금 새더라도 제동 성능이 크게 떨어지지 않는다</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
+          <t>페달을 밟는 양에 따라 제동력이 조절된다</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>구조가 간단하고 값이 싸서 소형 승용차에 주로 쓰인다</t>
+        </is>
+      </c>
+      <c r="G280" t="n">
+        <v>4</v>
+      </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>공기 브레이크는 큰 제동력을 얻을 수 있어 대형차에 쓰이지만, 압축기·탱크·밸브 등이 필요해 구조가 복잡하고 값이 비싸다. 나머지 보기는 공기 브레이크의 장점이다.</t>
+        </is>
+      </c>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>이 장치가 주로 어떤 크기의 차에 쓰이는지, 부품이 얼마나 많은지 떠올려 보세요.</t>
+        </is>
+      </c>
+      <c r="J280" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L280" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M280" t="n">
+        <v>2</v>
+      </c>
+      <c r="O280" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P280" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q280" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 교재 일반 내용(안전운행 - 제동장치) 공기식 브레이크 장단점 내용 기억. 기존 SAFE-0068은 공기압 확인만 물음</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>SAFE-0280</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>공기 브레이크를 쓰는 차량의 공기탱크에 고인 물을 정기적으로 빼내야 하는 이유로 옳은 것은?</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>엔진 출력을 높이기 위해</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>연료 소비를 늘리기 위해</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>타이어 공기압을 맞추기 위해</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>압축공기 속 수분이 고이면 탱크 부식과 겨울철 동결로 제동 계통에 고장이 생길 수 있기 때문에</t>
+        </is>
+      </c>
+      <c r="G281" t="n">
+        <v>4</v>
+      </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>압축 과정에서 생긴 수분이 탱크 바닥에 고이면 녹이 슬고, 겨울에는 얼어 밸브·배관을 막을 수 있다. 드레인 밸브를 열어 고인 물을 빼 준다.</t>
+        </is>
+      </c>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>공기를 압축하면 그 속의 수증기가 어떻게 되는지 생각해 보세요.</t>
+        </is>
+      </c>
+      <c r="J281" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L281" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M281" t="n">
+        <v>2</v>
+      </c>
+      <c r="O281" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P281" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q281" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 대형차 정비 일반 지식(공기탱크 드레인)</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>SAFE-0281</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>대형차의 스프링 브레이크(스프링 챔버)에 대한 설명으로 옳은 것은?</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>공기압이 높아질수록 브레이크가 강하게 걸린다</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>전자석으로 추진축 회전을 막는다</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>배기관을 막아 엔진 저항을 크게 한다</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>공기압이 일정 수준 아래로 떨어지면 스프링 힘으로 브레이크가 자동으로 걸린다</t>
+        </is>
+      </c>
+      <c r="G282" t="n">
+        <v>4</v>
+      </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>스프링 브레이크는 평소 공기압으로 스프링을 눌러 풀어 두고, 공기압이 빠지면 스프링이 브레이크를 걸어 주는 장치로 주차 브레이크와 비상 브레이크 역할을 한다.</t>
+        </is>
+      </c>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>공기압이 사라졌을 때도 차가 멈출 수 있게 하려면 어떤 힘을 써야 할지 생각해 보세요.</t>
+        </is>
+      </c>
+      <c r="J282" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L282" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M282" t="n">
+        <v>3</v>
+      </c>
+      <c r="O282" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P282" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q282" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 대형차 제동장치 일반 이론(spring brake chamber)</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>SAFE-0282</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>추진축에 붙은 원판이 전자석 사이에서 회전할 때 생기는 맴돌이 전류의 저항으로 감속하는 보조 제동장치는?</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>와전류 리타더</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>배기 브레이크</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>ABS</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>주차 브레이크</t>
+        </is>
+      </c>
+      <c r="G283" t="n">
+        <v>1</v>
+      </c>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>와전류 리타더는 전자석의 자기장 속에서 회전하는 원판에 생기는 와전류의 저항을 이용해 마찰 없이 감속하는 보조 브레이크로, 긴 내리막에서 풋 브레이크 부담을 줄인다.</t>
+        </is>
+      </c>
+      <c r="I283" t="inlineStr">
+        <is>
+          <t>전기와 자석을 이용하며, 보조 제동장치를 가리키는 외래어가 붙은 이름입니다.</t>
+        </is>
+      </c>
+      <c r="J283" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L283" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M283" t="n">
+        <v>2</v>
+      </c>
+      <c r="O283" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P283" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q283" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 대형차 보조제동장치 일반 이론(eddy current retarder). 기존 SAFE-0066은 배기 브레이크</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>SAFE-0283</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>드럼 브레이크와 비교한 디스크 브레이크의 장점으로 옳은 것은?</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>마찰 면적이 넓어 작은 힘으로도 제동력이 크다</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>주차 브레이크 기능을 따로 둘 필요가 전혀 없다</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
+          <t>디스크가 밖으로 드러나 열이 잘 식으므로 페이드 현상이 적다</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>물이 묻어도 마찰재가 전혀 젖지 않는다</t>
+        </is>
+      </c>
+      <c r="G284" t="n">
+        <v>3</v>
+      </c>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>디스크 브레이크는 회전하는 원판이 바깥 공기에 드러나 있어 방열이 잘 되므로 연속 제동에도 페이드가 적다. 반면 큰 힘이 필요해 배력장치를 함께 쓰는 경우가 많다.</t>
+        </is>
+      </c>
+      <c r="I284" t="inlineStr">
+        <is>
+          <t>원판이 공기에 직접 닿는 구조가 어떤 이점을 주는지 생각해 보세요.</t>
+        </is>
+      </c>
+      <c r="J284" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L284" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M284" t="n">
+        <v>2</v>
+      </c>
+      <c r="O284" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P284" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q284" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 자동차 구조 일반 이론(디스크·드럼 브레이크 비교)</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>SAFE-0284</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>주차 브레이크를 완전히 풀었는데도 계기판의 브레이크 경고등이 꺼지지 않는다. 먼저 점검할 사항은?</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>엔진오일 색깔</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>타이어 트레드 깊이</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>냉각수 부동액 농도</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>브레이크액 양(또는 공기 브레이크의 공기압)</t>
+        </is>
+      </c>
+      <c r="G285" t="n">
+        <v>4</v>
+      </c>
+      <c r="H285" t="inlineStr">
+        <is>
+          <t>브레이크 경고등은 주차 브레이크 작동뿐 아니라 브레이크액 부족이나 공기압 저하 때도 켜진다. 주차 브레이크를 풀었는데도 켜져 있다면 제동 계통을 즉시 점검한다.</t>
+        </is>
+      </c>
+      <c r="I285" t="inlineStr">
+        <is>
+          <t>이 경고등이 알려 주는 계통이 무엇인지 생각해 보세요.</t>
+        </is>
+      </c>
+      <c r="J285" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L285" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M285" t="n">
+        <v>2</v>
+      </c>
+      <c r="O285" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P285" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q285" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 차량 취급설명서 일반 내용(브레이크 경고등 점등 조건)</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>SAFE-0285</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>동력 조향장치(파워 스티어링)의 장점으로 옳지 않은 것은?</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>작은 힘으로 핸들을 돌릴 수 있다</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>노면의 충격이 핸들에 덜 전달된다</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>타이어가 펑크 나도 직진을 자동으로 유지한다</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>무거운 앞바퀴 하중에도 조향 조작이 쉽다</t>
+        </is>
+      </c>
+      <c r="G286" t="n">
+        <v>3</v>
+      </c>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>동력 조향장치는 유압이나 전동기의 힘을 보태 조향을 가볍게 하고 노면 충격이 핸들로 오는 것을 줄인다. 타이어 파손 시 직진을 자동으로 유지해 주지는 않는다.</t>
+        </is>
+      </c>
+      <c r="I286" t="inlineStr">
+        <is>
+          <t>이 장치는 '돕는 힘'을 보태는 것일 뿐 사고 상황을 스스로 제어하지는 않습니다.</t>
+        </is>
+      </c>
+      <c r="J286" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L286" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M286" t="n">
+        <v>1</v>
+      </c>
+      <c r="O286" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P286" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q286" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 자동차 구조 일반 이론(동력 조향장치)</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>SAFE-0286</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>유압식 동력 조향장치의 오일이 부족할 때 나타날 수 있는 증상으로 옳은 것은?</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>핸들이 무거워지고 돌릴 때 '웅' 하는 소음이 난다</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>브레이크 페달이 바닥까지 들어간다</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>배기가스가 검게 나온다</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>방향지시등이 빠르게 깜빡인다</t>
+        </is>
+      </c>
+      <c r="G287" t="n">
+        <v>1</v>
+      </c>
+      <c r="H287" t="inlineStr">
+        <is>
+          <t>동력 조향 오일이 부족하면 펌프가 공기를 빨아들여 보조 힘이 줄어 핸들이 무거워지고 펌프 소음이 커진다. 오일 양과 누유를 점검한다.</t>
+        </is>
+      </c>
+      <c r="I287" t="inlineStr">
+        <is>
+          <t>핸들 조작을 도와주는 유압이 약해지면 어떻게 될지 생각해 보세요.</t>
+        </is>
+      </c>
+      <c r="J287" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L287" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M287" t="n">
+        <v>2</v>
+      </c>
+      <c r="O287" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P287" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q287" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 정비 일반 지식. 기존 SAFE-0059(공기압 부족)와 다른 원인</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>SAFE-0287</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>앞바퀴 정렬 중 토인(toe-in)의 역할로 옳은 것은?</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>핸들을 돌린 뒤 저절로 직진 상태로 되돌아오게 한다</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>주행 중 앞바퀴가 바깥쪽으로 벌어지는 것을 막아 타이어가 옆으로 끌리며 닳는 것을 줄인다</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>차체가 좌우로 기우는 것을 막는다</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>엔진의 진동을 줄인다</t>
+        </is>
+      </c>
+      <c r="G288" t="n">
+        <v>2</v>
+      </c>
+      <c r="H288" t="inlineStr">
+        <is>
+          <t>토인은 주행 중 앞바퀴가 바깥으로 벌어지려는 경향(캠버 영향 등)을 상쇄해 바퀴가 평행하게 구르게 하고, 타이어 편마모를 막는다. 복원력은 주로 캐스터의 역할이다.</t>
+        </is>
+      </c>
+      <c r="I288" t="inlineStr">
+        <is>
+          <t>앞쪽을 살짝 오므려 둔 이유를 바퀴가 굴러갈 때 벌어지려는 성질과 연결해 보세요.</t>
+        </is>
+      </c>
+      <c r="J288" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L288" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M288" t="n">
+        <v>3</v>
+      </c>
+      <c r="O288" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P288" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q288" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 교재 일반 내용(안전운행 - 조향장치) 앞바퀴 정렬 기능. 기존 SAFE-0058은 정의만 물음</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>SAFE-0288</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>과속방지턱을 넘은 뒤 차체가 위아래로 여러 번 계속 출렁인다. 가장 먼저 의심할 수 있는 고장은?</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>쇽업소버의 성능 저하나 오일 누설</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>냉각수 부족</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>배터리 방전</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>연료 필터 막힘</t>
+        </is>
+      </c>
+      <c r="G289" t="n">
+        <v>1</v>
+      </c>
+      <c r="H289" t="inlineStr">
+        <is>
+          <t>쇽업소버는 스프링의 진동을 흡수해 빨리 가라앉히는 장치이므로, 성능이 떨어지면 한 번의 충격에도 출렁임이 오래 이어진다. 오일이 새는지도 함께 확인한다.</t>
+        </is>
+      </c>
+      <c r="I289" t="inlineStr">
+        <is>
+          <t>스프링이 튕기는 것을 붙잡아 주는 부품이 무엇인지 떠올려 보세요.</t>
+        </is>
+      </c>
+      <c r="J289" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L289" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M289" t="n">
+        <v>1</v>
+      </c>
+      <c r="O289" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P289" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q289" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 정비 일반 지식. 기존 SAFE-0063은 역할(정의)만 물음</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>SAFE-0289</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>코일 스프링에 대한 설명으로 옳은 것은?</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>여러 장의 강판을 겹쳐 만들어 대형 트럭 뒤축에 주로 쓴다</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>압축공기를 채운 고무 주머니로 차 높이를 조절한다</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>단위 무게당 에너지 흡수가 크고 승차감이 좋지만, 진동 감쇠 작용이 없어 쇽업소버를 함께 써야 한다</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>막대의 비틀림 탄성을 이용한다</t>
+        </is>
+      </c>
+      <c r="G290" t="n">
+        <v>3</v>
+      </c>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>코일 스프링은 강선을 나선형으로 감은 스프링으로 승용차 등에 많이 쓰이며, 판간 마찰이 없어 스스로 진동을 줄이지 못하므로 쇽업소버를 같이 쓴다. ①은 판스프링, ②는 공기 스프링, ④는 토션바 설명이다.</t>
+        </is>
+      </c>
+      <c r="I290" t="inlineStr">
+        <is>
+          <t>강선을 나선 모양으로 감은 구조와 판 사이 마찰이 없다는 점을 생각해 보세요.</t>
+        </is>
+      </c>
+      <c r="J290" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L290" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M290" t="n">
+        <v>3</v>
+      </c>
+      <c r="O290" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P290" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q290" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 교재 일반 내용(안전운행 - 현가장치 종류) 코일 스프링 특성. 기존 판·공기 스프링 문제와 다른 종류</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>SAFE-0290</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>화물차 타이어 옆면에 '295/80R22.5'라고 적혀 있다. 여기서 '80'이 뜻하는 것은?</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>타이어 단면 폭(밀리미터)</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>편평비(단면 높이를 단면 폭으로 나눈 백분율)</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>림 지름(인치)</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>최고 허용 속도(킬로미터/시)</t>
+        </is>
+      </c>
+      <c r="G291" t="n">
+        <v>2</v>
+      </c>
+      <c r="H291" t="inlineStr">
+        <is>
+          <t>295는 단면 폭(mm), 80은 편평비(%), R은 레이디얼 구조, 22.5는 림 지름(인치)을 뜻한다. 편평비가 작을수록 옆면이 낮은 타이어다.</t>
+        </is>
+      </c>
+      <c r="I291" t="inlineStr">
+        <is>
+          <t>빗금(/) 앞의 숫자와 비교되는 값이며, 단위 없이 비율로 나타냅니다.</t>
+        </is>
+      </c>
+      <c r="J291" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L291" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M291" t="n">
+        <v>2</v>
+      </c>
+      <c r="O291" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P291" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q291" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 타이어 규격 표기 일반(ISO 미터법 표기). 제조사 표기 안내와 일치하는 일반 지식</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>SAFE-0291</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>레이디얼 타이어의 특징으로 옳은 것은?</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>카커스 코드를 사선으로 엇갈리게 겹친 구조이다</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>트레드 강성이 낮아 고속 주행에 불리하다</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>접지 면적이 넓고 변형이 적어 고속 주행 시 발열과 스탠딩 웨이브가 적다</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>타이어 안에 튜브를 반드시 넣어야 한다</t>
+        </is>
+      </c>
+      <c r="G292" t="n">
+        <v>3</v>
+      </c>
+      <c r="H292" t="inlineStr">
+        <is>
+          <t>레이디얼 타이어는 카커스 코드를 원 둘레 방향과 직각(방사형)으로 배열하고 벨트로 보강해 접지면이 안정되고 고속 내구성이 좋다. 사선으로 엇갈린 구조는 바이어스 타이어다.</t>
+        </is>
+      </c>
+      <c r="I292" t="inlineStr">
+        <is>
+          <t>타이어 규격의 'R'이 무엇을 뜻하는지, 코드가 어느 방향으로 놓이는지 떠올려 보세요.</t>
+        </is>
+      </c>
+      <c r="J292" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L292" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M292" t="n">
+        <v>2</v>
+      </c>
+      <c r="O292" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P292" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q292" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 교재 일반 내용(안전운행 - 타이어의 종류) 바이어스·레이디얼 비교. 원문 미확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>SAFE-0292</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>뒷바퀴에 타이어 두 개를 나란히 끼운 복륜(복륜식) 타이어를 점검할 때 주의할 점으로 옳은 것은?</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>바깥쪽 타이어만 확인하면 된다</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>두 타이어의 공기압이 다르면 한쪽에 하중이 몰려 빨리 손상되므로 같게 맞추고, 사이에 낀 돌을 제거한다</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>안쪽 타이어는 공기압을 낮게 두는 것이 좋다</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>두 타이어는 서로 다른 크기를 쓰는 것이 좋다</t>
+        </is>
+      </c>
+      <c r="G293" t="n">
+        <v>2</v>
+      </c>
+      <c r="H293" t="inlineStr">
+        <is>
+          <t>복륜은 두 타이어가 하중을 나누어 지므로 공기압·크기·마모 상태가 같아야 한다. 타이어 사이에 돌이 끼면 옆면이 손상되므로 점검 때 제거한다.</t>
+        </is>
+      </c>
+      <c r="I293" t="inlineStr">
+        <is>
+          <t>두 타이어가 무게를 어떻게 나누어 받는지 생각해 보세요.</t>
+        </is>
+      </c>
+      <c r="J293" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L293" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M293" t="n">
+        <v>2</v>
+      </c>
+      <c r="O293" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P293" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q293" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 대형차 타이어 관리 일반 지식</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>SAFE-0293</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>타이어 옆면 DOT 표기의 끝에 '2524'라는 네 자리 숫자가 있다. 이 타이어의 제조 시기는?</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>2025년 24주차</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>2024년 25주차</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>2025년 2월 24일</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>2024년 2월 5일</t>
+        </is>
+      </c>
+      <c r="G294" t="n">
+        <v>2</v>
+      </c>
+      <c r="H294" t="inlineStr">
+        <is>
+          <t>DOT 표기 마지막 네 자리는 앞 두 자리가 제조 주(週), 뒤 두 자리가 제조 연도이다. 따라서 '2524'는 2024년 25주차에 만든 타이어다.</t>
+        </is>
+      </c>
+      <c r="I294" t="inlineStr">
+        <is>
+          <t>네 자리 중 연도를 나타내는 부분이 앞인지 뒤인지가 핵심입니다.</t>
+        </is>
+      </c>
+      <c r="J294" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L294" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M294" t="n">
+        <v>3</v>
+      </c>
+      <c r="O294" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P294" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q294" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 타이어 제조사 안내 https://lassa.com/how-to-read-tyre-dot-code (DOT 날짜 코드: 주 2자리+연도 2자리)</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>SAFE-0294</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>타이어 위치를 정기적으로 바꾸어 다는(로테이션) 주된 목적은?</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>타이어가 고르게 닳게 하여 수명을 늘리기 위해</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>타이어 공기압을 높이기 위해</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>엔진 출력을 높이기 위해</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>연료 탱크 용량을 늘리기 위해</t>
+        </is>
+      </c>
+      <c r="G295" t="n">
+        <v>1</v>
+      </c>
+      <c r="H295" t="inlineStr">
+        <is>
+          <t>앞·뒤, 좌·우 바퀴는 하중과 조향·구동 조건이 달라 닳는 정도가 다르므로, 일정 주행거리마다 위치를 바꾸면 마모가 고르게 되어 타이어 수명이 늘어난다.</t>
+        </is>
+      </c>
+      <c r="I295" t="inlineStr">
+        <is>
+          <t>바퀴마다 닳는 속도가 다르다는 점을 생각해 보세요.</t>
+        </is>
+      </c>
+      <c r="J295" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L295" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M295" t="n">
+        <v>1</v>
+      </c>
+      <c r="O295" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P295" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q295" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 타이어 관리 일반 지식</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>SAFE-0295</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>냉각장치의 서모스탯(정온기)의 역할로 옳은 것은?</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>냉각수의 어는점을 낮춘다</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>냉각수 온도에 따라 통로를 열고 닫아 엔진을 알맞은 온도로 유지한다</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>냉각수를 강제로 순환시키는 펌프 역할을 한다</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>라디에이터 안의 압력을 높인다</t>
+        </is>
+      </c>
+      <c r="G296" t="n">
+        <v>2</v>
+      </c>
+      <c r="H296" t="inlineStr">
+        <is>
+          <t>서모스탯은 엔진이 차가울 때는 라디에이터로 가는 통로를 닫아 빨리 데우고, 온도가 오르면 열어 냉각수를 식힌다. 열린 채 고장 나면 엔진이 잘 데워지지 않고, 닫힌 채 고장 나면 과열된다.</t>
+        </is>
+      </c>
+      <c r="I296" t="inlineStr">
+        <is>
+          <t>이름의 '정온(定溫)'이라는 말을 생각해 보세요.</t>
+        </is>
+      </c>
+      <c r="J296" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L296" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M296" t="n">
+        <v>2</v>
+      </c>
+      <c r="O296" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P296" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q296" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 자동차 구조 일반 이론. 기존 SAFE-0228은 겨울철 점검 항목으로 이름만 언급</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>SAFE-0296</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>압력식 라디에이터 캡의 역할로 옳은 것은?</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>냉각 계통에 압력을 가해 냉각수의 끓는점을 높인다</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>냉각수 색을 바꾸어 오염을 알린다</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>엔진오일이 냉각수에 섞이게 한다</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>냉각팬의 회전 속도를 조절한다</t>
+        </is>
+      </c>
+      <c r="G297" t="n">
+        <v>1</v>
+      </c>
+      <c r="H297" t="inlineStr">
+        <is>
+          <t>압력식 캡은 냉각 계통을 밀폐해 압력을 높임으로써 냉각수가 100℃보다 높은 온도에서도 끓지 않게 한다. 그래서 뜨거울 때 열면 냉각수가 뿜어져 위험하다.</t>
+        </is>
+      </c>
+      <c r="I297" t="inlineStr">
+        <is>
+          <t>압력솥에서 물이 끓는 온도가 어떻게 되는지 떠올려 보세요.</t>
+        </is>
+      </c>
+      <c r="J297" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L297" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M297" t="n">
+        <v>2</v>
+      </c>
+      <c r="O297" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P297" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q297" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 자동차 구조 일반 이론. 기존 SAFE-0070은 '뜨거울 때 열지 않기'만 물음</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>SAFE-0297</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>엔진오일의 역할로 보기 어려운 것은?</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>움직이는 부품 사이의 마찰과 마모를 줄인다</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>엔진 내부의 열을 식히고 이물질을 씻어 낸다</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>피스톤과 실린더 사이 틈을 막아 압축가스가 새는 것을 줄인다</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>연료를 실린더 안에 뿜어 넣는다</t>
+        </is>
+      </c>
+      <c r="G298" t="n">
+        <v>4</v>
+      </c>
+      <c r="H298" t="inlineStr">
+        <is>
+          <t>엔진오일은 윤활·냉각·세척·밀봉·방청 작용을 한다. 연료를 실린더에 뿜어 넣는 것은 연료 분사장치(인젝터)의 역할이다.</t>
+        </is>
+      </c>
+      <c r="I298" t="inlineStr">
+        <is>
+          <t>오일이 엔진 안을 돌며 하는 일과, 다른 장치가 맡는 일을 구분해 보세요.</t>
+        </is>
+      </c>
+      <c r="J298" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L298" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M298" t="n">
+        <v>1</v>
+      </c>
+      <c r="O298" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P298" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q298" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 자동차 구조 일반 이론(윤활유의 작용)</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>SAFE-0298</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>오일 게이지로 엔진오일을 확인했더니 오일이 우유처럼 뿌옇게 변해 있었다. 의심할 수 있는 원인은?</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>새 오일로 막 교환한 상태</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>냉각수가 엔진오일에 섞여 들어감(헤드 개스킷 손상 등)</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>오일 양이 너무 적음</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>연료 필터 막힘</t>
+        </is>
+      </c>
+      <c r="G299" t="n">
+        <v>2</v>
+      </c>
+      <c r="H299" t="inlineStr">
+        <is>
+          <t>오일이 우윳빛이면 물(냉각수)이 섞인 것으로, 실린더 헤드 개스킷 손상 등이 의심된다. 그대로 운행하면 윤활이 안 되어 엔진이 크게 손상될 수 있어 즉시 정비한다.</t>
+        </is>
+      </c>
+      <c r="I299" t="inlineStr">
+        <is>
+          <t>기름에 어떤 액체가 섞이면 뿌옇게 변하는지 생각해 보세요.</t>
+        </is>
+      </c>
+      <c r="J299" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L299" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M299" t="n">
+        <v>3</v>
+      </c>
+      <c r="O299" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P299" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q299" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 정비 일반 지식(유화된 엔진오일)</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>SAFE-0299</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>배터리 단자 주변에 하얀 가루 같은 부식물이 붙어 있을 때의 문제와 조치로 옳은 것은?</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>배터리 성능이 좋아진 신호이므로 그대로 둔다</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>접촉이 나빠져 시동 불량이 생길 수 있으므로 단자를 청소하고 단단히 조인다</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>냉각수를 부어 녹인다</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>엔진오일을 발라 둔다</t>
+        </is>
+      </c>
+      <c r="G300" t="n">
+        <v>2</v>
+      </c>
+      <c r="H300" t="inlineStr">
+        <is>
+          <t>단자 부식은 전기 흐름을 방해해 시동이 잘 안 걸리거나 충전이 약해지는 원인이 된다. 미지근한 물 등으로 닦아 내고 단자를 확실히 조인 뒤 보호제를 바른다.</t>
+        </is>
+      </c>
+      <c r="I300" t="inlineStr">
+        <is>
+          <t>전기가 흐르는 연결부에 이물질이 끼면 어떻게 될지 생각해 보세요.</t>
+        </is>
+      </c>
+      <c r="J300" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L300" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M300" t="n">
+        <v>1</v>
+      </c>
+      <c r="O300" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P300" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q300" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 정비 일반 지식(배터리 단자 관리)</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>SAFE-0300</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>배터리가 방전된 차를 다른 차의 배터리와 점프 케이블로 연결해 시동할 때의 방법으로 옳은 것은?</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>음극(-) 케이블부터 방전된 배터리에 연결한다</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>양극(+)끼리 먼저 연결하고, 음극(-)은 마지막에 방전 차의 엔진 블록 등 금속 부분에 연결한다</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>양극(+)과 음극(-)을 엇갈려 연결한다</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>두 차의 시동을 모두 끈 채로 연결한 뒤 방전된 차부터 시동한다</t>
+        </is>
+      </c>
+      <c r="G301" t="n">
+        <v>2</v>
+      </c>
+      <c r="H301" t="inlineStr">
+        <is>
+          <t>빨간 케이블로 두 배터리의 양극을 먼저 잇고, 검은 케이블은 정상 차 음극에서 방전 차의 차체 금속(접지)에 마지막으로 연결한다. 분리는 연결의 역순으로 한다.</t>
+        </is>
+      </c>
+      <c r="I301" t="inlineStr">
+        <is>
+          <t>불꽃이 생기기 쉬운 마지막 연결 지점을 배터리에서 멀리 두는 이유를 생각해 보세요.</t>
+        </is>
+      </c>
+      <c r="J301" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K301" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L301" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M301" t="n">
+        <v>3</v>
+      </c>
+      <c r="O301" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P301" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q301" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 차량 취급설명서 일반 절차(점프 스타트)</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>SAFE-0301</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>주행 중 계기판의 배터리 모양(충전) 경고등이 켜졌다. 의심할 수 있는 원인으로 가장 알맞은 것은?</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>발전기 고장이나 발전기를 돌리는 벨트가 끊어지거나 느슨해짐</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>타이어 공기압 부족</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>브레이크 라이닝 마모</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>연료 게이지 고장</t>
+        </is>
+      </c>
+      <c r="G302" t="n">
+        <v>1</v>
+      </c>
+      <c r="H302" t="inlineStr">
+        <is>
+          <t>충전 경고등은 발전기가 배터리를 충전하지 못할 때 켜진다. 발전기 고장, 구동 벨트 이상 등을 의심하고, 그대로 두면 배터리가 방전되어 차가 멈출 수 있다.</t>
+        </is>
+      </c>
+      <c r="I302" t="inlineStr">
+        <is>
+          <t>엔진이 도는 동안 전기를 만들어 배터리를 채워 주는 장치를 떠올려 보세요.</t>
+        </is>
+      </c>
+      <c r="J302" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L302" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M302" t="n">
+        <v>1</v>
+      </c>
+      <c r="O302" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P302" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q302" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 차량 취급설명서 일반 내용(충전 경고등)</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>SAFE-0302</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>전조등 퓨즈가 끊어져 교체할 때의 방법으로 옳은 것은?</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>더 오래 쓰도록 용량이 큰 퓨즈로 바꾼다</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>철사나 은박지로 이어 둔다</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>같은 용량의 퓨즈로 바꾸고, 자주 끊어지면 배선을 점검한다</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>퓨즈를 빼 둔 채로 운행한다</t>
+        </is>
+      </c>
+      <c r="G303" t="n">
+        <v>3</v>
+      </c>
+      <c r="H303" t="inlineStr">
+        <is>
+          <t>퓨즈는 과전류에서 회로를 보호하는 부품이므로 반드시 규정 용량으로 바꾼다. 더 큰 용량이나 철사로 대신하면 배선이 과열되어 화재가 날 수 있다.</t>
+        </is>
+      </c>
+      <c r="I303" t="inlineStr">
+        <is>
+          <t>퓨즈가 일부러 먼저 끊어지도록 만들어진 이유를 생각해 보세요.</t>
+        </is>
+      </c>
+      <c r="J303" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K303" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L303" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M303" t="n">
+        <v>1</v>
+      </c>
+      <c r="O303" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P303" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q303" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 전기 안전 일반 지식</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>SAFE-0303</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>방향지시등을 켰을 때 표시등이 평소보다 매우 빠르게 깜빡인다. 먼저 의심할 수 있는 원인은?</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>엔진오일 부족</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>좌우 앞바퀴 정렬 불량</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>냉각수 과열</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>해당 쪽 방향지시등 전구 중 하나가 끊어짐</t>
+        </is>
+      </c>
+      <c r="G304" t="n">
+        <v>4</v>
+      </c>
+      <c r="H304" t="inlineStr">
+        <is>
+          <t>방향지시등 회로의 전구 하나가 끊어지면 전류가 바뀌어 점멸 속도가 빨라진다. 앞·뒤·옆 전구를 확인하고 교체한다.</t>
+        </is>
+      </c>
+      <c r="I304" t="inlineStr">
+        <is>
+          <t>깜빡임을 만드는 회로에 연결된 부품 중 하나가 빠진 상황을 생각해 보세요.</t>
+        </is>
+      </c>
+      <c r="J304" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K304" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L304" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M304" t="n">
+        <v>2</v>
+      </c>
+      <c r="O304" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P304" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q304" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 자동차 전기장치 일반 지식(점멸 속도 변화)</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>SAFE-0304</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>겨울철 디젤 엔진 화물차의 시동을 도와주는 장치와 그 이유를 바르게 짝지은 것은?</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>점화플러그 – 불꽃으로 연료에 불을 붙이기 위해</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>예열플러그 – 연소실을 미리 데워 압축착화가 쉽게 일어나게 하기 위해</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>서모스탯 – 냉각수를 얼지 않게 하기 위해</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>배기 브레이크 – 배기 압력을 높이기 위해</t>
+        </is>
+      </c>
+      <c r="G305" t="n">
+        <v>2</v>
+      </c>
+      <c r="H305" t="inlineStr">
+        <is>
+          <t>디젤 엔진은 공기를 압축해 생긴 높은 열로 연료가 스스로 타는 방식이라, 추운 날에는 예열플러그로 연소실을 데운 뒤 시동한다. 점화플러그는 가솔린 엔진에 쓰인다.</t>
+        </is>
+      </c>
+      <c r="I305" t="inlineStr">
+        <is>
+          <t>디젤 엔진은 불꽃이 아니라 압축열로 연료를 태운다는 점을 떠올려 보세요.</t>
+        </is>
+      </c>
+      <c r="J305" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L305" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M305" t="n">
+        <v>2</v>
+      </c>
+      <c r="O305" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P305" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q305" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 자동차 구조 일반 이론(디젤 기관 예열장치)</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>SAFE-0305</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>요소수를 쓰는 선택적 환원 촉매장치(SCR)가 달린 디젤 화물차에 대한 설명으로 옳은 것은?</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>요소수는 연료 탱크에 경유와 섞어 넣는다</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr">
+        <is>
+          <t>요소수는 엔진오일 대신 쓸 수 있다</t>
+        </is>
+      </c>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>요소수가 떨어져도 배출가스와 차량 성능에는 아무 영향이 없다</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>요소수가 떨어지면 출력이 제한되거나 재시동이 안 될 수 있으므로 미리 보충한다</t>
+        </is>
+      </c>
+      <c r="G306" t="n">
+        <v>4</v>
+      </c>
+      <c r="H306" t="inlineStr">
+        <is>
+          <t>요소수는 배기가스 속 질소산화물을 줄이는 데 쓰이며 전용 탱크에 넣는다. 요소수가 바닥나면 배출가스 기준을 지키지 못하므로 출력 제한 등이 걸리도록 되어 있다.</t>
+        </is>
+      </c>
+      <c r="I306" t="inlineStr">
+        <is>
+          <t>이 장치는 배기가스를 깨끗하게 하기 위한 것이며, 전용 주입구가 따로 있습니다.</t>
+        </is>
+      </c>
+      <c r="J306" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L306" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M306" t="n">
+        <v>2</v>
+      </c>
+      <c r="O306" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P306" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q306" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 환경부·제조사 안내 일반 내용(요소수 부족 시 출력 제한). 2021년 요소수 품귀 보도 등에서 널리 알려진 사항</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>SAFE-0306</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>디젤 차량의 매연저감장치(DPF)에 대한 설명으로 옳은 것은?</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>배기가스 속 입자상 물질(매연)을 걸러 모은 뒤 높은 온도로 태워 없앤다</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr">
+        <is>
+          <t>엔진 냉각수 온도를 낮춘다</t>
+        </is>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>연료를 실린더에 분사한다</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>브레이크 마찰열을 식힌다</t>
+        </is>
+      </c>
+      <c r="G307" t="n">
+        <v>1</v>
+      </c>
+      <c r="H307" t="inlineStr">
+        <is>
+          <t>DPF는 필터로 매연 입자를 모았다가 배기 온도를 높여 태워 없애는(재생) 장치다. 짧은 거리만 반복 운행하면 재생이 잘 안 되어 필터가 막힐 수 있다.</t>
+        </is>
+      </c>
+      <c r="I307" t="inlineStr">
+        <is>
+          <t>이름에 '필터'가 들어간다는 점에서 역할을 떠올려 보세요.</t>
+        </is>
+      </c>
+      <c r="J307" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K307" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L307" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M307" t="n">
+        <v>2</v>
+      </c>
+      <c r="O307" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P307" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q307" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 배출가스 저감장치 일반 지식(Diesel Particulate Filter)</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>SAFE-0307</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>터보차저가 달린 화물차로 고속도로를 오래 달린 직후의 엔진 관리 방법으로 옳은 것은?</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>즉시 시동을 끄고 엔진 덮개를 연다</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr">
+        <is>
+          <t>가속 페달을 여러 번 세게 밟은 뒤 시동을 끈다</t>
+        </is>
+      </c>
+      <c r="E308" t="inlineStr">
+        <is>
+          <t>잠시 공회전하여 과열된 터보차저를 식힌 뒤 시동을 끈다</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>냉각수를 바로 추가로 부어 식힌다</t>
+        </is>
+      </c>
+      <c r="G308" t="n">
+        <v>3</v>
+      </c>
+      <c r="H308" t="inlineStr">
+        <is>
+          <t>고속 운행 직후 터보차저는 매우 뜨겁고 고속으로 회전하므로, 바로 시동을 끄면 윤활이 끊겨 베어링이 손상될 수 있다. 잠시 공회전으로 식힌 뒤 끈다.</t>
+        </is>
+      </c>
+      <c r="I308" t="inlineStr">
+        <is>
+          <t>배기가스로 빠르게 도는 부품이 기름을 공급받지 못하면 어떻게 될지 생각해 보세요.</t>
+        </is>
+      </c>
+      <c r="J308" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K308" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L308" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M308" t="n">
+        <v>3</v>
+      </c>
+      <c r="O308" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P308" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q308" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 차량 취급설명서 일반 내용(터보 차량 후냉각 공회전)</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>SAFE-0308</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>디젤 화물차가 연료가 바닥날 때까지 달려 멈춘 뒤, 연료를 넣었는데도 시동이 걸리지 않는다. 알맞은 조치는?</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>엔진오일을 보충한다</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>연료 계통에 들어간 공기를 빼낸(에어 빼기) 뒤 시동한다</t>
+        </is>
+      </c>
+      <c r="E309" t="inlineStr">
+        <is>
+          <t>냉각수를 모두 빼낸다</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>타이어 공기압을 높인다</t>
+        </is>
+      </c>
+      <c r="G309" t="n">
+        <v>2</v>
+      </c>
+      <c r="H309" t="inlineStr">
+        <is>
+          <t>디젤 엔진은 연료가 떨어지면 연료 계통에 공기가 차서 연료가 분사되지 않는다. 프라이밍 펌프 등으로 공기를 빼낸 뒤 시동해야 한다.</t>
+        </is>
+      </c>
+      <c r="I309" t="inlineStr">
+        <is>
+          <t>연료관에 연료 대신 무엇이 들어찼을지 생각해 보세요.</t>
+        </is>
+      </c>
+      <c r="J309" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L309" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M309" t="n">
+        <v>2</v>
+      </c>
+      <c r="O309" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P309" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q309" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 교재 일반 내용(안전운행 - 고장 유형별 조치) 엔진 시동 불량 항목과 정비 일반 지식</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>SAFE-0309</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>커브길을 돌 때 바깥쪽 바퀴가 안쪽 바퀴보다 더 많이 회전할 수 있도록 해 주는 장치는?</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>클러치</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>변속기</t>
+        </is>
+      </c>
+      <c r="E310" t="inlineStr">
+        <is>
+          <t>쇽업소버</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>차동장치</t>
+        </is>
+      </c>
+      <c r="G310" t="n">
+        <v>4</v>
+      </c>
+      <c r="H310" t="inlineStr">
+        <is>
+          <t>회전할 때 바깥쪽 바퀴는 안쪽보다 먼 거리를 가야 하므로, 차동장치가 좌우 구동 바퀴의 회전 차이를 허용해 미끄러짐 없이 돌게 한다.</t>
+        </is>
+      </c>
+      <c r="I310" t="inlineStr">
+        <is>
+          <t>커브에서는 바깥쪽 바퀴가 더 먼 거리를 돌아야 한다는 점을 떠올려 보세요.</t>
+        </is>
+      </c>
+      <c r="J310" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L310" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M310" t="n">
+        <v>1</v>
+      </c>
+      <c r="O310" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P310" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q310" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 자동차 구조 일반 이론(차동기어장치) · 교차 점검 반영</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>SAFE-0310</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>덤프트럭의 적재함이 올라가지 않을 때 먼저 점검할 사항으로 가장 알맞은 것은?</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>동력인출장치(PTO)의 작동 상태와 유압유 양</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr">
+        <is>
+          <t>전조등 전구</t>
+        </is>
+      </c>
+      <c r="E311" t="inlineStr">
+        <is>
+          <t>와이퍼 블레이드</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>타이어 트레드 깊이</t>
+        </is>
+      </c>
+      <c r="G311" t="n">
+        <v>1</v>
+      </c>
+      <c r="H311" t="inlineStr">
+        <is>
+          <t>덤프 적재함은 엔진 동력을 PTO로 꺼내 유압펌프를 돌려 올리므로, PTO 연결 상태와 유압유 양·누유, 유압 호스 등을 먼저 확인한다.</t>
+        </is>
+      </c>
+      <c r="I311" t="inlineStr">
+        <is>
+          <t>엔진의 힘을 주행 외의 작업 장치로 꺼내 쓰는 장치를 떠올려 보세요.</t>
+        </is>
+      </c>
+      <c r="J311" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L311" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M311" t="n">
+        <v>3</v>
+      </c>
+      <c r="O311" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P311" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q311" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 교재 일반 내용(안전운행 - 고장 유형별 조치) 덤프 작동 불량 항목 기억. 원문 미확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>SAFE-0311</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>운행 전 차의 바깥을 돌아보며 하는 외관 점검 항목으로 알맞은 것은?</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>휠 너트의 풀림, 판스프링 손상, 차 밑의 누유·누수 흔적</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr">
+        <is>
+          <t>엔진 피스톤 링의 마모량</t>
+        </is>
+      </c>
+      <c r="E312" t="inlineStr">
+        <is>
+          <t>변속기 내부 기어의 이 상태</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>연료 분사 시기</t>
+        </is>
+      </c>
+      <c r="G312" t="n">
+        <v>1</v>
+      </c>
+      <c r="H312" t="inlineStr">
+        <is>
+          <t>외관 점검에서는 타이어·휠 너트, 판스프링 연결부, 등화장치, 차 밑의 오일·냉각수 누설 흔적 등을 눈으로 확인한다. 엔진·변속기 내부는 정비업체가 분해해 점검한다.</t>
+        </is>
+      </c>
+      <c r="I312" t="inlineStr">
+        <is>
+          <t>공구로 분해하지 않고 차 주위를 돌며 눈으로 볼 수 있는 것을 고르세요.</t>
+        </is>
+      </c>
+      <c r="J312" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L312" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M312" t="n">
+        <v>1</v>
+      </c>
+      <c r="O312" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P312" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q312" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 교재 일반 내용(안전운행 - 운행 전 점검 - 외관). 기존 SAFE-0030(분해 측정 제외)·0185(운전석)와 다른 항목군</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>SAFE-0312</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>대형 화물차의 휠 너트 풀림을 운행 전 쉽게 확인하는 방법으로 옳은 것은?</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>타이어 공기압만 재면 알 수 있다</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr">
+        <is>
+          <t>너트와 볼트에 표시해 둔 선(또는 풀림 표시기)이 어긋나 있는지 본다</t>
+        </is>
+      </c>
+      <c r="E313" t="inlineStr">
+        <is>
+          <t>엔진 소리를 듣고 판단한다</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>차를 출발시킨 뒤 급제동해 본다</t>
+        </is>
+      </c>
+      <c r="G313" t="n">
+        <v>2</v>
+      </c>
+      <c r="H313" t="inlineStr">
+        <is>
+          <t>휠 너트에 일직선으로 표시를 하거나 풀림 표시기를 달아 두면 표시가 어긋난 너트를 바로 찾을 수 있다. 풀린 너트는 규정 토크로 다시 조인다.</t>
+        </is>
+      </c>
+      <c r="I313" t="inlineStr">
+        <is>
+          <t>눈으로 보고 바로 알아챌 수 있게 미리 해 두는 표시를 생각해 보세요.</t>
+        </is>
+      </c>
+      <c r="J313" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L313" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M313" t="n">
+        <v>2</v>
+      </c>
+      <c r="O313" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P313" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q313" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 대형차 안전점검 일반 지식(휠 너트 마킹·인디케이터)</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>SAFE-0313</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>바닷가 도로나 제설용 염화칼슘이 뿌려진 도로를 달린 뒤의 차량 관리로 옳은 것은?</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>차체 하부를 빨리 물로 씻어 염분을 없앤다</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr">
+        <is>
+          <t>타이어 공기압을 크게 낮춘다</t>
+        </is>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>엔진오일을 즉시 교환한다</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>세차를 하지 않고 그대로 말린다</t>
+        </is>
+      </c>
+      <c r="G314" t="n">
+        <v>1</v>
+      </c>
+      <c r="H314" t="inlineStr">
+        <is>
+          <t>염분과 염화칼슘은 차체 하부와 브레이크 배관 등을 녹슬게 하므로, 운행 뒤 가능한 한 빨리 하부까지 물로 씻어 낸다.</t>
+        </is>
+      </c>
+      <c r="I314" t="inlineStr">
+        <is>
+          <t>소금기가 금속에 오래 붙어 있으면 어떤 일이 생기는지 생각해 보세요.</t>
+        </is>
+      </c>
+      <c r="J314" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L314" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M314" t="n">
+        <v>1</v>
+      </c>
+      <c r="O314" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P314" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q314" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 교재 일반 내용(안전운행 - 자동차 관리 - 세차 시기). 기존 SAFE-0223(봄철 관리)과 다른 상황</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>SAFE-0314</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>교차로를 지날 때 앞차만 보고 따라 들어가는 운전이 위험한 이유로 가장 알맞은 것은?</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>앞차를 따라 진입하는 사이 신호가 바뀌어 교차 방향 차와 충돌할 수 있다</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr">
+        <is>
+          <t>앞차와의 거리가 넓어져 다른 차가 끼어들기 쉽다</t>
+        </is>
+      </c>
+      <c r="E315" t="inlineStr">
+        <is>
+          <t>엔진 회전수가 높아져 연료 소비가 늘어난다</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>앞차의 제동등이 잘 보이지 않아 공주거리가 짧아진다</t>
+        </is>
+      </c>
+      <c r="G315" t="n">
+        <v>1</v>
+      </c>
+      <c r="H315" t="inlineStr">
+        <is>
+          <t>앞차만 보고 따라가면 신호를 직접 확인하지 못해, 신호가 바뀐 뒤 교차로에 들어가 측면충돌을 일으키기 쉽다.</t>
+        </is>
+      </c>
+      <c r="I315" t="inlineStr">
+        <is>
+          <t>교차로에서 내 진행을 허락하는 것은 앞차가 아니라 무엇인지 생각해 보세요.</t>
+        </is>
+      </c>
+      <c r="J315" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L315" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M315" t="n">
+        <v>1</v>
+      </c>
+      <c r="O315" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P315" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q315" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 한국교통안전공단 화물운송종사 자격시험 교재 '안전운행' 단원의 일반 내용(교재 원문 미확인)</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>SAFE-0315</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>교차로 부근에서 많이 일어나는 사고 유형으로 보기 어려운 것은?</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>신호가 바뀌는 순간 무리하게 진입하여 일어나는 측면충돌</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr">
+        <is>
+          <t>우회전할 때 오른쪽의 보행자·이륜차를 치는 사고</t>
+        </is>
+      </c>
+      <c r="E316" t="inlineStr">
+        <is>
+          <t>긴 내리막길에서 브레이크 과열로 일어나는 단독사고</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>앞차의 급정지로 일어나는 추돌사고</t>
+        </is>
+      </c>
+      <c r="G316" t="n">
+        <v>3</v>
+      </c>
+      <c r="H316" t="inlineStr">
+        <is>
+          <t>교차로에서는 신호 전환 시 측면충돌, 우회전 말림사고, 신호 대기 중 추돌이 많다. 브레이크 과열 단독사고는 긴 내리막 구간의 특징이다.</t>
+        </is>
+      </c>
+      <c r="I316" t="inlineStr">
+        <is>
+          <t>교차로라는 장소의 특징(여러 방향의 흐름이 만남)과 관계없는 사고를 찾으세요.</t>
+        </is>
+      </c>
+      <c r="J316" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K316" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L316" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M316" t="n">
+        <v>1</v>
+      </c>
+      <c r="O316" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P316" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q316" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 한국교통안전공단 화물운송종사 자격시험 교재 '안전운행' 단원의 일반 내용(교재 원문 미확인)</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>SAFE-0316</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>회전교차로 중앙교통섬 둘레에 약간 높게 포장하여, 회전 반경이 큰 대형 차량의 뒷바퀴가 밟고 지나갈 수 있도록 만든 부분은?</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>분리 교통섬</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr">
+        <is>
+          <t>고원식 횡단보도</t>
+        </is>
+      </c>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>화물차 턱(트럭 에이프런)</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>가속차로</t>
+        </is>
+      </c>
+      <c r="G317" t="n">
+        <v>3</v>
+      </c>
+      <c r="H317" t="inlineStr">
+        <is>
+          <t>화물차 턱은 승용차는 밟지 않도록 약간 높이고, 대형차가 회전할 때 뒷바퀴가 올라탈 수 있게 만든 회전교차로의 시설이다.</t>
+        </is>
+      </c>
+      <c r="I317" t="inlineStr">
+        <is>
+          <t>대형차의 내륜차 때문에 안쪽 뒷바퀴가 어디를 지나게 되는지 떠올려 보세요.</t>
+        </is>
+      </c>
+      <c r="J317" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L317" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M317" t="n">
+        <v>3</v>
+      </c>
+      <c r="O317" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P317" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q317" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 국토교통부 회전교차로 설계지침의 일반 구성요소(화물차 턱) — 원문 미확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>SAFE-0317</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>회전교차로의 일반적인 특징으로 옳은 것은?</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>진입하려는 차가 이미 회전 중인 차보다 우선한다</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr">
+        <is>
+          <t>진입하는 차가 속도를 줄여야 하므로 사고가 나도 피해가 비교적 작다</t>
+        </is>
+      </c>
+      <c r="E318" t="inlineStr">
+        <is>
+          <t>신호 대기 시간이 길어 신호교차로보다 지체가 늘어난다</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>진입할 때 가속하여 회전 흐름에 빨리 끼어드는 것이 안전하다</t>
+        </is>
+      </c>
+      <c r="G318" t="n">
+        <v>2</v>
+      </c>
+      <c r="H318" t="inlineStr">
+        <is>
+          <t>회전교차로는 진입 차량이 감속하고 회전 차량에 양보하는 구조라 속도가 낮아져 충돌 시 피해가 줄어든다. 회전 중인 차가 우선이다.</t>
+        </is>
+      </c>
+      <c r="I318" t="inlineStr">
+        <is>
+          <t>원형 도로를 도는 동안 차가 빠르게 달릴 수 있는지 생각해 보세요.</t>
+        </is>
+      </c>
+      <c r="J318" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L318" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M318" t="n">
+        <v>2</v>
+      </c>
+      <c r="O318" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P318" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q318" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 한국교통안전공단 화물운송종사 자격시험 교재 '안전운행' 단원의 일반 내용(교재 원문 미확인)</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>SAFE-0318</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>교차로에서 좌회전하려고 반대편 직진 차가 지나가기를 기다릴 때 핸들 조작으로 옳은 것은?</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>좌회전 방향으로 핸들을 미리 꺾어 두고 기다린다</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr">
+        <is>
+          <t>오른쪽으로 핸들을 꺾어 두어 뒤차가 지나갈 공간을 만든다</t>
+        </is>
+      </c>
+      <c r="E319" t="inlineStr">
+        <is>
+          <t>핸들에서 손을 떼고 주차 브레이크만 채운 채 기다린다</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>앞바퀴가 곧게 향하도록 핸들을 바로 둔 채 기다린다</t>
+        </is>
+      </c>
+      <c r="G319" t="n">
+        <v>4</v>
+      </c>
+      <c r="H319" t="inlineStr">
+        <is>
+          <t>바퀴를 미리 왼쪽으로 꺾어 두면 뒤차에 추돌당했을 때 반대 차로로 밀려 들어가 정면충돌로 이어질 수 있다.</t>
+        </is>
+      </c>
+      <c r="I319" t="inlineStr">
+        <is>
+          <t>대기 중 뒤에서 차가 들이받았을 때 내 차가 어느 쪽으로 밀려 나갈지 생각해 보세요.</t>
+        </is>
+      </c>
+      <c r="J319" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K319" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L319" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M319" t="n">
+        <v>3</v>
+      </c>
+      <c r="O319" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P319" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q319" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 한국교통안전공단 화물운송종사 자격시험 교재 '안전운행' 단원의 일반 내용(교재 원문 미확인)</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>SAFE-0319</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>고속도로에서 나들목(인터체인지)으로 나갈 때의 운전 방법으로 옳은 것은?</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>본선에서 충분히 속도를 줄인 다음 감속차로로 들어간다</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr">
+        <is>
+          <t>미리 바깥쪽 차로로 옮겨 감속차로에 들어선 뒤 속도를 줄인다</t>
+        </is>
+      </c>
+      <c r="E320" t="inlineStr">
+        <is>
+          <t>진출로 바로 앞에서 여러 차로를 한꺼번에 가로질러 나간다</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>진출로 갈림목의 빗금 표시 구역을 가로질러 들어간다</t>
+        </is>
+      </c>
+      <c r="G320" t="n">
+        <v>2</v>
+      </c>
+      <c r="H320" t="inlineStr">
+        <is>
+          <t>감속은 본선이 아니라 감속차로에서 해야 뒤차의 추돌을 막을 수 있으며, 진출 차로는 미리 바꿔 두어야 한다.</t>
+        </is>
+      </c>
+      <c r="I320" t="inlineStr">
+        <is>
+          <t>본선은 빠른 흐름이 유지되는 곳입니다. 속도를 줄이는 전용 공간이 따로 있습니다.</t>
+        </is>
+      </c>
+      <c r="J320" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K320" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L320" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M320" t="n">
+        <v>2</v>
+      </c>
+      <c r="O320" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P320" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q320" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 한국교통안전공단 화물운송종사 자격시험 교재 '안전운행' 단원의 일반 내용(교재 원문 미확인)</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>SAFE-0320</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>고속도로 합류부에서 진입로의 차가 본선으로 들어오려 할 때 본선 주행 차량의 방어운전으로 옳은 것은?</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>진입 차가 끼어들지 못하도록 앞차에 바짝 붙는다</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr">
+        <is>
+          <t>합류부에서 급정지하여 진입 차를 먼저 보낸다</t>
+        </is>
+      </c>
+      <c r="E321" t="inlineStr">
+        <is>
+          <t>속도를 조절하거나 안전하면 왼쪽 차로로 옮겨 합류할 공간을 내준다</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>진입 차를 무시하고 가속하여 먼저 지나간다</t>
+        </is>
+      </c>
+      <c r="G321" t="n">
+        <v>3</v>
+      </c>
+      <c r="H321" t="inlineStr">
+        <is>
+          <t>합류부에서는 본선 차량도 진입 차량을 배려해 속도·차로를 조절해야 한다. 급정지는 뒤차 추돌을 부른다.</t>
+        </is>
+      </c>
+      <c r="I321" t="inlineStr">
+        <is>
+          <t>방어운전은 상대가 들어올 것을 예상하고 여유를 만드는 운전입니다.</t>
+        </is>
+      </c>
+      <c r="J321" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L321" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M321" t="n">
+        <v>1</v>
+      </c>
+      <c r="O321" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P321" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q321" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 한국교통안전공단 화물운송종사 자격시험 교재 '안전운행' 단원의 일반 내용(교재 원문 미확인)</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>SAFE-0321</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>화물자동차가 나들목 연결로(램프)를 지날 때 특히 주의할 점으로 옳은 것은?</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>곡선 반경이 작은 곳이 많아 진입 전에 충분히 감속하지 않으면 전도될 수 있다</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr">
+        <is>
+          <t>연결로는 본선보다 폭이 넓어 본선 속도를 유지해도 된다</t>
+        </is>
+      </c>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>연결로에서는 앞지르기로 빨리 빠져나가는 것이 안전하다</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>연결로에서는 엔진 브레이크를 쓰면 안 된다</t>
+        </is>
+      </c>
+      <c r="G322" t="n">
+        <v>1</v>
+      </c>
+      <c r="H322" t="inlineStr">
+        <is>
+          <t>연결로는 원형에 가깝게 급하게 굽은 경우가 많아, 무게중심이 높은 화물차가 속도를 줄이지 않으면 원심력으로 넘어질 수 있다.</t>
+        </is>
+      </c>
+      <c r="I322" t="inlineStr">
+        <is>
+          <t>빙 돌아 내려가는 연결로 모양과 원심력의 관계를 떠올려 보세요.</t>
+        </is>
+      </c>
+      <c r="J322" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L322" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M322" t="n">
+        <v>2</v>
+      </c>
+      <c r="O322" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P322" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q322" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 한국교통안전공단 화물운송종사 자격시험 교재 '안전운행' 단원의 일반 내용(교재 원문 미확인)</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>SAFE-0322</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>주택가 이면도로에서 길가에 주차된 차 옆을 지날 때의 방어운전으로 가장 알맞은 것은?</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>주차된 차에 바짝 붙어 반대편 차와의 간격을 최대한 넓힌다</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr">
+        <is>
+          <t>주차된 차에는 사람이 없으므로 평소 속도로 지나간다</t>
+        </is>
+      </c>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>경음기를 계속 울리면서 빠르게 지나간다</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>차 문이 갑자기 열리거나 차 사이로 사람이 나올 수 있으므로 옆 간격을 두고 서행한다</t>
+        </is>
+      </c>
+      <c r="G323" t="n">
+        <v>4</v>
+      </c>
+      <c r="H323" t="inlineStr">
+        <is>
+          <t>주차 차량 주변은 문 열림·보행자 돌출 위험이 크므로 간격을 확보하고 속도를 낮춘다.</t>
+        </is>
+      </c>
+      <c r="I323" t="inlineStr">
+        <is>
+          <t>세워 둔 차에서 갑자기 움직일 수 있는 것이 무엇인지 떠올려 보세요.</t>
+        </is>
+      </c>
+      <c r="J323" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K323" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L323" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M323" t="n">
+        <v>1</v>
+      </c>
+      <c r="O323" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P323" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q323" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 한국교통안전공단 화물운송종사 자격시험 교재 '안전운행' 단원의 일반 내용(교재 원문 미확인)</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>SAFE-0323</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>주택가·학교 앞 등에서 차량 속도를 낮추려고 설치하는 교통정온화 시설로 보기 어려운 것은?</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>가속차로</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr">
+        <is>
+          <t>과속방지턱</t>
+        </is>
+      </c>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>지그재그 형태의 차로(시케인)</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>차로 폭을 좁힌 구간(초커)</t>
+        </is>
+      </c>
+      <c r="G324" t="n">
+        <v>1</v>
+      </c>
+      <c r="H324" t="inlineStr">
+        <is>
+          <t>교통정온화 시설은 물리적으로 속도를 줄이게 하는 시설이다. 가속차로는 고속도로 진입 시 속도를 높이기 위한 차로다.</t>
+        </is>
+      </c>
+      <c r="I324" t="inlineStr">
+        <is>
+          <t>'정온화'는 교통을 조용하고 느리게 만든다는 뜻입니다.</t>
+        </is>
+      </c>
+      <c r="J324" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K324" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L324" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M324" t="n">
+        <v>3</v>
+      </c>
+      <c r="O324" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P324" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q324" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 국토교통부 교통정온화시설 설치·관리지침의 일반 내용(원문 미확인)</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>SAFE-0324</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>산악도로 급커브 구간 바깥쪽에 연속으로 설치되어 도로가 굽은 방향을 화살표 모양으로 알려 주는 시설은?</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>충격흡수시설</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr">
+        <is>
+          <t>도로반사경</t>
+        </is>
+      </c>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>과속방지턱</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>갈매기표지</t>
+        </is>
+      </c>
+      <c r="G325" t="n">
+        <v>4</v>
+      </c>
+      <c r="H325" t="inlineStr">
+        <is>
+          <t>갈매기표지는 시선유도시설의 하나로 급커브의 방향을 미리 알려 준다. 도로반사경은 보이지 않는 곳의 차를 비춰 보여 주는 거울이다.</t>
+        </is>
+      </c>
+      <c r="I325" t="inlineStr">
+        <is>
+          <t>시선유도시설의 하나로, 화살표처럼 생긴 표지가 커브 바깥쪽에 줄지어 서 있습니다.</t>
+        </is>
+      </c>
+      <c r="J325" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K325" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L325" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M325" t="n">
+        <v>2</v>
+      </c>
+      <c r="O325" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P325" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q325" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 국토교통부 도로안전시설 설치 및 관리지침(시선유도시설)의 일반 내용(원문 미확인) · 교차 점검 반영</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>SAFE-0325</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>산악도로 운전에 관한 설명으로 옳은 것은?</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>커브와 경사가 이어져 앞이 짧게 보이므로 커브 앞에서 감속하고 낙석·동물 출현에 대비한다</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr">
+        <is>
+          <t>오가는 차가 적으므로 중앙선을 넘어 커브를 직선처럼 달린다</t>
+        </is>
+      </c>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>내리막에서는 기어를 중립에 두어 연료를 아낀다</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>오르막에서는 앞차와 간격을 좁혀 뒤로 밀리지 않게 한다</t>
+        </is>
+      </c>
+      <c r="G326" t="n">
+        <v>1</v>
+      </c>
+      <c r="H326" t="inlineStr">
+        <is>
+          <t>산악도로는 시야가 짧고 경사·커브가 연속되므로 감속과 돌발 위험 대비가 기본이다. 중립 주행과 간격 좁히기는 위험하다.</t>
+        </is>
+      </c>
+      <c r="I326" t="inlineStr">
+        <is>
+          <t>굽고 가파른 길에서 운전자가 미리 보기 어려운 것이 무엇인지 생각해 보세요.</t>
+        </is>
+      </c>
+      <c r="J326" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K326" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L326" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M326" t="n">
+        <v>1</v>
+      </c>
+      <c r="O326" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P326" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q326" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 한국교통안전공단 화물운송종사 자격시험 교재 '안전운행' 단원의 일반 내용(교재 원문 미확인)</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>SAFE-0326</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>긴 내리막길 도중이나 끝부분에 설치되어, 브레이크가 고장 난 차량이 들어가 자갈 등의 저항으로 멈출 수 있게 만든 시설은?</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>오르막차로</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr">
+        <is>
+          <t>긴급제동시설</t>
+        </is>
+      </c>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>졸음쉼터</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>비상주차대</t>
+        </is>
+      </c>
+      <c r="G327" t="n">
+        <v>2</v>
+      </c>
+      <c r="H327" t="inlineStr">
+        <is>
+          <t>긴급제동시설은 제동 불능 차량이 진입해 바닥재 저항으로 감속·정지하도록 만든 비상 시설이다.</t>
+        </is>
+      </c>
+      <c r="I327" t="inlineStr">
+        <is>
+          <t>시설의 목적은 '쉼'이나 '주차'가 아니라 '멈추게 하는 것'입니다.</t>
+        </is>
+      </c>
+      <c r="J327" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K327" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L327" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M327" t="n">
+        <v>3</v>
+      </c>
+      <c r="O327" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P327" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q327" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 국토교통부 도로안전시설 설치 및 관리지침(긴급제동시설) 일반 내용(원문 미확인)</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>SAFE-0327</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>밤에 앞이 보이지 않는 산악도로 커브에 들어갈 때 자기 차의 접근을 반대편에 알리는 방법으로 알맞은 것은?</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>전조등을 끄고 반대편 불빛이 있는지 살핀다</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr">
+        <is>
+          <t>커브에 들어가기 전에 전조등을 상향과 하향으로 바꾸어 비춘다</t>
+        </is>
+      </c>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>커브 안쪽으로 붙어 중앙선을 넘어 빨리 돈다</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>경음기를 계속 울리며 속도를 높인다</t>
+        </is>
+      </c>
+      <c r="G328" t="n">
+        <v>2</v>
+      </c>
+      <c r="H328" t="inlineStr">
+        <is>
+          <t>야간 커브길에서는 전조등을 상·하향으로 바꿔 반대편 차에 내 차가 다가감을 알리고 감속한다.</t>
+        </is>
+      </c>
+      <c r="I328" t="inlineStr">
+        <is>
+          <t>밤에는 소리보다 빛이 멀리서도 눈에 잘 띕니다.</t>
+        </is>
+      </c>
+      <c r="J328" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K328" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L328" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M328" t="n">
+        <v>2</v>
+      </c>
+      <c r="O328" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P328" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q328" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 한국교통안전공단 화물운송종사 자격시험 교재 '안전운행' 단원의 일반 내용(교재 원문 미확인)</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>SAFE-0328</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>터널 안에서 화재가 나 걸어서 대피해야 할 때의 방법으로 옳은 것은?</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>연기가 흘러가는 방향을 따라 달려 나간다</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr">
+        <is>
+          <t>차 안에서 창문을 닫고 구조를 기다린다</t>
+        </is>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>터널 벽의 비상구 유도등을 따라 피난연결통로 등으로 대피한다</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>차를 돌려 반대 방향으로 몰고 나간다</t>
+        </is>
+      </c>
+      <c r="G329" t="n">
+        <v>3</v>
+      </c>
+      <c r="H329" t="inlineStr">
+        <is>
+          <t>터널에는 일정 간격으로 피난연결통로·비상구가 있으므로 유도등을 따라 대피한다. 연기 방향으로 가거나 차 안에 머무르면 위험하다.</t>
+        </is>
+      </c>
+      <c r="I329" t="inlineStr">
+        <is>
+          <t>터널 벽에 초록색으로 빛나는 표시가 무엇을 안내하는지 떠올려 보세요.</t>
+        </is>
+      </c>
+      <c r="J329" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K329" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L329" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M329" t="n">
+        <v>2</v>
+      </c>
+      <c r="O329" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P329" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q329" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 한국교통안전공단 화물운송종사 자격시험 교재 '안전운행' 단원의 일반 내용(교재 원문 미확인)</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>SAFE-0329</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>낮에 선글라스를 끼고 운전하다가 터널에 들어갈 때 바람직한 행동은?</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>터널 안이 더 밝게 보이도록 선글라스를 계속 낀다</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr">
+        <is>
+          <t>진입 전에 선글라스를 벗고 속도를 줄인다</t>
+        </is>
+      </c>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>터널 안에 들어간 뒤 운전하면서 선글라스를 찾아 벗는다</t>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>선글라스를 낀 채 전조등을 끄고 진입한다</t>
+        </is>
+      </c>
+      <c r="G330" t="n">
+        <v>2</v>
+      </c>
+      <c r="H330" t="inlineStr">
+        <is>
+          <t>선글라스를 낀 채 어두운 터널에 들어가면 시력이 크게 떨어지므로 진입 전에 벗고 감속한다.</t>
+        </is>
+      </c>
+      <c r="I330" t="inlineStr">
+        <is>
+          <t>어두운 곳에 들어가는데 빛을 줄이는 안경이 도움이 될지 생각해 보세요.</t>
+        </is>
+      </c>
+      <c r="J330" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K330" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L330" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M330" t="n">
+        <v>1</v>
+      </c>
+      <c r="O330" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P330" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q330" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 한국교통안전공단 화물운송종사 자격시험 교재 '안전운행' 단원의 일반 내용(교재 원문 미확인)</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>SAFE-0330</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>터널 입구 부근의 조명을 터널 안쪽보다 밝게 설치하는 주된 이유는?</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>운전자의 눈이 어둠에 서서히 적응하도록 하여 진입 직후 시력 저하를 줄이기 위해</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr">
+        <is>
+          <t>터널 안쪽 조명 전력을 아끼기 위해</t>
+        </is>
+      </c>
+      <c r="E331" t="inlineStr">
+        <is>
+          <t>터널 안에서 차량 속도를 높이도록 유도하기 위해</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>터널 밖에 있는 차가 터널 안을 들여다볼 수 있게 하기 위해</t>
+        </is>
+      </c>
+      <c r="G331" t="n">
+        <v>1</v>
+      </c>
+      <c r="H331" t="inlineStr">
+        <is>
+          <t>밝은 바깥에서 어두운 터널로 들어가면 눈이 바로 적응하지 못하므로, 입구부를 밝게 하고 안으로 갈수록 단계적으로 어둡게 한다.</t>
+        </is>
+      </c>
+      <c r="I331" t="inlineStr">
+        <is>
+          <t>밝기를 한꺼번에 바꾸지 않고 '단계적으로' 바꾸는 까닭을 떠올려 보세요.</t>
+        </is>
+      </c>
+      <c r="J331" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K331" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L331" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M331" t="n">
+        <v>3</v>
+      </c>
+      <c r="O331" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P331" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q331" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 도로조명 설계 일반 원리(터널 입구부 조명) — 원문 미확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>SAFE-0331</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>야간에 마주 오는 차와 엇갈릴 때 증발현상이 생기기 쉽다. 이에 대한 대처로 옳은 것은?</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>상향등을 켜서 마주 오는 차의 불빛을 이긴다</t>
+        </is>
+      </c>
+      <c r="D332" t="inlineStr">
+        <is>
+          <t>속도를 높여 마주 오는 차를 빨리 지나친다</t>
+        </is>
+      </c>
+      <c r="E332" t="inlineStr">
+        <is>
+          <t>엇갈리는 지점 부근에 보행자가 있을 수 있다고 보고 속도를 줄이며 주의 깊게 살핀다</t>
+        </is>
+      </c>
+      <c r="F332" t="inlineStr">
+        <is>
+          <t>눈을 잠시 감아 눈부심이 사라지기를 기다린다</t>
+        </is>
+      </c>
+      <c r="G332" t="n">
+        <v>3</v>
+      </c>
+      <c r="H332" t="inlineStr">
+        <is>
+          <t>증발현상은 두 차의 불빛이 겹치는 곳의 보행자가 사라진 것처럼 보이는 현상이므로 감속하며 그 지점을 경계해야 한다.</t>
+        </is>
+      </c>
+      <c r="I332" t="inlineStr">
+        <is>
+          <t>'보이지 않는다'는 것이 '없다'는 뜻은 아닙니다.</t>
+        </is>
+      </c>
+      <c r="J332" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K332" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L332" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M332" t="n">
+        <v>2</v>
+      </c>
+      <c r="O332" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P332" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q332" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 한국교통안전공단 화물운송종사 자격시험 교재 '안전운행' 단원의 일반 내용(교재 원문 미확인)</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>SAFE-0332</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>야간 운전 중 차 안의 실내등을 켜고 달리는 것이 좋지 않은 이유는?</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>차 안이 밝아져 바깥 물체를 알아보기 어려워진다</t>
+        </is>
+      </c>
+      <c r="D333" t="inlineStr">
+        <is>
+          <t>배터리가 과충전되어 고장 난다</t>
+        </is>
+      </c>
+      <c r="E333" t="inlineStr">
+        <is>
+          <t>다른 차의 전조등이 더 밝게 보이게 되어 눈부심이 줄어든다</t>
+        </is>
+      </c>
+      <c r="F333" t="inlineStr">
+        <is>
+          <t>계기판이 어두워져 속도를 알 수 없다</t>
+        </is>
+      </c>
+      <c r="G333" t="n">
+        <v>1</v>
+      </c>
+      <c r="H333" t="inlineStr">
+        <is>
+          <t>실내가 밝으면 앞유리에 빛이 비치고 눈이 밝기에 적응해 어두운 바깥이 더 안 보이게 된다.</t>
+        </is>
+      </c>
+      <c r="I333" t="inlineStr">
+        <is>
+          <t>밤에 불 켜진 방에서 바깥 창밖이 잘 보이는지 떠올려 보세요.</t>
+        </is>
+      </c>
+      <c r="J333" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K333" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L333" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M333" t="n">
+        <v>1</v>
+      </c>
+      <c r="O333" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P333" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q333" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 한국교통안전공단 화물운송종사 자격시험 교재 '안전운행' 단원의 일반 내용(교재 원문 미확인)</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>SAFE-0333</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>야간 주행 속도에 관한 설명으로 옳은 것은?</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>밤에는 차가 적으므로 낮보다 빠르게 달려도 된다</t>
+        </is>
+      </c>
+      <c r="D334" t="inlineStr">
+        <is>
+          <t>전조등을 상향으로 켜면 속도 제한 없이 달려도 된다</t>
+        </is>
+      </c>
+      <c r="E334" t="inlineStr">
+        <is>
+          <t>전조등이 비추는 거리 안에서 멈출 수 있는 속도로 달린다</t>
+        </is>
+      </c>
+      <c r="F334" t="inlineStr">
+        <is>
+          <t>앞차의 미등만 보고 같은 속도로 따라간다</t>
+        </is>
+      </c>
+      <c r="G334" t="n">
+        <v>3</v>
+      </c>
+      <c r="H334" t="inlineStr">
+        <is>
+          <t>야간에는 전조등 범위 밖의 위험을 볼 수 없으므로, 보이는 거리 안에서 정지할 수 있도록 속도를 낮춰야 한다.</t>
+        </is>
+      </c>
+      <c r="I334" t="inlineStr">
+        <is>
+          <t>정지거리와 '눈에 보이는 거리'를 비교해 보세요.</t>
+        </is>
+      </c>
+      <c r="J334" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K334" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L334" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M334" t="n">
+        <v>2</v>
+      </c>
+      <c r="O334" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P334" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q334" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 한국교통안전공단 화물운송종사 자격시험 교재 '안전운행' 단원의 일반 내용(교재 원문 미확인)</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>SAFE-0334</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>낮에 폭우가 쏟아질 때의 운전 방법으로 옳은 것은?</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>낮에는 전조등을 켜지 않고 비상등만 계속 켠 채 평소 속도로 달린다</t>
+        </is>
+      </c>
+      <c r="D335" t="inlineStr">
+        <is>
+          <t>와이퍼를 끄고 앞차의 물보라를 따라간다</t>
+        </is>
+      </c>
+      <c r="E335" t="inlineStr">
+        <is>
+          <t>물이 고인 곳은 빠르게 지나가 수막이 생기기 전에 벗어난다</t>
+        </is>
+      </c>
+      <c r="F335" t="inlineStr">
+        <is>
+          <t>낮이라도 전조등을 켜서 다른 운전자가 내 차를 알아보게 한다</t>
+        </is>
+      </c>
+      <c r="G335" t="n">
+        <v>4</v>
+      </c>
+      <c r="H335" t="inlineStr">
+        <is>
+          <t>폭우 때는 시야가 나빠 서로 잘 보이지 않으므로 전조등을 켜고 감속해야 한다.</t>
+        </is>
+      </c>
+      <c r="I335" t="inlineStr">
+        <is>
+          <t>비가 많이 오면 '내가 보는 것'만큼 '남에게 보이는 것'도 중요합니다.</t>
+        </is>
+      </c>
+      <c r="J335" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K335" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L335" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M335" t="n">
+        <v>1</v>
+      </c>
+      <c r="O335" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P335" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q335" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 한국교통안전공단 화물운송종사 자격시험 교재 '안전운행' 단원의 일반 내용(교재 원문 미확인)</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>SAFE-0335</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>짙은 안개로 앞이 거의 보이지 않아 운전을 계속하기 어려울 때 가장 알맞은 조치는?</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>비상점멸등을 켜고 휴게소 등 안전한 곳에 차를 세워 안개가 걷히기를 기다린다</t>
+        </is>
+      </c>
+      <c r="D336" t="inlineStr">
+        <is>
+          <t>고속도로 갓길에 차를 세우고 전조등을 끈 채 기다린다</t>
+        </is>
+      </c>
+      <c r="E336" t="inlineStr">
+        <is>
+          <t>차로 한가운데에 차를 세우고 경음기를 울린다</t>
+        </is>
+      </c>
+      <c r="F336" t="inlineStr">
+        <is>
+          <t>앞차의 미등이 보일 때까지 속도를 높여 따라붙는다</t>
+        </is>
+      </c>
+      <c r="G336" t="n">
+        <v>1</v>
+      </c>
+      <c r="H336" t="inlineStr">
+        <is>
+          <t>시계가 극히 나쁘면 무리하게 달리지 말고 안전한 장소로 대피해야 한다. 갓길·차로 정차는 2차 사고 위험이 크다.</t>
+        </is>
+      </c>
+      <c r="I336" t="inlineStr">
+        <is>
+          <t>멈추기로 했다면 '어디에' 멈추느냐가 안전을 좌우합니다.</t>
+        </is>
+      </c>
+      <c r="J336" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K336" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L336" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M336" t="n">
+        <v>2</v>
+      </c>
+      <c r="O336" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P336" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q336" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 한국교통안전공단 화물운송종사 자격시험 교재 '안전운행' 단원의 일반 내용(교재 원문 미확인)</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>SAFE-0336</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>다른 조건이 같을 때 강한 옆바람의 영향을 가장 크게 받기 쉬운 차량은?</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>화물을 가득 실은 낮은 평판형 화물자동차</t>
+        </is>
+      </c>
+      <c r="D337" t="inlineStr">
+        <is>
+          <t>차체가 낮은 소형 승용자동차</t>
+        </is>
+      </c>
+      <c r="E337" t="inlineStr">
+        <is>
+          <t>무거운 화물을 바닥에 고르게 실은 덤프트럭</t>
+        </is>
+      </c>
+      <c r="F337" t="inlineStr">
+        <is>
+          <t>적재함이 높고 비어 있는 박스형 화물자동차</t>
+        </is>
+      </c>
+      <c r="G337" t="n">
+        <v>4</v>
+      </c>
+      <c r="H337" t="inlineStr">
+        <is>
+          <t>옆면이 넓고 높아 바람을 받는 면적이 크며, 비어 있어 가벼운 차는 옆바람에 밀리거나 넘어지기 쉽다.</t>
+        </is>
+      </c>
+      <c r="I337" t="inlineStr">
+        <is>
+          <t>바람을 받는 면적과 차의 무게, 두 가지를 함께 생각해 보세요.</t>
+        </is>
+      </c>
+      <c r="J337" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K337" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L337" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M337" t="n">
+        <v>2</v>
+      </c>
+      <c r="O337" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P337" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q337" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 한국교통안전공단 화물운송종사 자격시험 교재 '안전운행' 단원의 일반 내용(교재 원문 미확인)</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>SAFE-0337</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>폭설로 도로에 고립되어 엔진을 켠 채 차 안에서 구조를 기다릴 때 반드시 주의할 점은?</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>창문을 꼭 닫고 히터를 최대로 켜 둔다</t>
+        </is>
+      </c>
+      <c r="D338" t="inlineStr">
+        <is>
+          <t>연료를 아끼려고 수시로 시동을 껐다 켜며 경음기를 울린다</t>
+        </is>
+      </c>
+      <c r="E338" t="inlineStr">
+        <is>
+          <t>차 밖으로 나가 도로를 따라 걸어서 이동한다</t>
+        </is>
+      </c>
+      <c r="F338" t="inlineStr">
+        <is>
+          <t>배기관 주변의 눈을 치우고 창문을 조금 열어 일산화탄소 중독을 막는다</t>
+        </is>
+      </c>
+      <c r="G338" t="n">
+        <v>4</v>
+      </c>
+      <c r="H338" t="inlineStr">
+        <is>
+          <t>배기관이 눈에 막히면 배기가스가 차 안으로 들어올 수 있어, 배기관 주변을 치우고 환기해야 한다.</t>
+        </is>
+      </c>
+      <c r="I338" t="inlineStr">
+        <is>
+          <t>엔진을 켜 두면 차 뒤쪽에서 나오는 것이 무엇인지 떠올려 보세요.</t>
+        </is>
+      </c>
+      <c r="J338" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K338" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L338" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M338" t="n">
+        <v>2</v>
+      </c>
+      <c r="O338" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P338" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q338" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 한국교통안전공단 화물운송종사 자격시험 교재 '안전운행' 단원의 일반 내용(교재 원문 미확인)</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>SAFE-0338</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>ABS가 없는 차로 빙판길에서 멈출 때의 제동 방법으로 옳은 것은?</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>브레이크 페달을 한 번에 끝까지 세게 밟는다</t>
+        </is>
+      </c>
+      <c r="D339" t="inlineStr">
+        <is>
+          <t>기어를 중립에 두고 주차 브레이크를 한 번에 당긴다</t>
+        </is>
+      </c>
+      <c r="E339" t="inlineStr">
+        <is>
+          <t>핸들을 좌우로 흔들어 바퀴의 마찰을 높인다</t>
+        </is>
+      </c>
+      <c r="F339" t="inlineStr">
+        <is>
+          <t>엔진 브레이크로 속도를 줄이면서 브레이크 페달을 여러 번 나누어 밟는다</t>
+        </is>
+      </c>
+      <c r="G339" t="n">
+        <v>4</v>
+      </c>
+      <c r="H339" t="inlineStr">
+        <is>
+          <t>빙판에서 한 번에 세게 밟으면 바퀴가 잠겨 미끄러지므로, 엔진 브레이크와 나누어 밟기로 서서히 감속한다.</t>
+        </is>
+      </c>
+      <c r="I339" t="inlineStr">
+        <is>
+          <t>바퀴가 '잠기는 것'을 막는 것이 핵심입니다.</t>
+        </is>
+      </c>
+      <c r="J339" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K339" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L339" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M339" t="n">
+        <v>2</v>
+      </c>
+      <c r="O339" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P339" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q339" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 한국교통안전공단 화물운송종사 자격시험 교재 '안전운행' 단원의 일반 내용(교재 원문 미확인)</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>SAFE-0339</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>빙판길에서 구동 바퀴가 헛돌아 차가 출발하지 못할 때의 조치로 옳은 것은?</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>가속 페달을 끝까지 밟아 바퀴를 세게 돌린다</t>
+        </is>
+      </c>
+      <c r="D340" t="inlineStr">
+        <is>
+          <t>타이어 공기를 모두 빼고 출발한다</t>
+        </is>
+      </c>
+      <c r="E340" t="inlineStr">
+        <is>
+          <t>바퀴 밑에 모래나 제설제를 뿌리거나 체인을 감아 마찰력을 높인다</t>
+        </is>
+      </c>
+      <c r="F340" t="inlineStr">
+        <is>
+          <t>핸들을 끝까지 꺾은 채 가속한다</t>
+        </is>
+      </c>
+      <c r="G340" t="n">
+        <v>3</v>
+      </c>
+      <c r="H340" t="inlineStr">
+        <is>
+          <t>헛돌 때 세게 가속하면 얼음이 더 매끈해져 빠져나오기 어렵다. 마찰력을 높여 주는 것이 바른 방법이다.</t>
+        </is>
+      </c>
+      <c r="I340" t="inlineStr">
+        <is>
+          <t>미끄러움의 반대 개념은 무엇일까요?</t>
+        </is>
+      </c>
+      <c r="J340" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K340" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L340" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M340" t="n">
+        <v>1</v>
+      </c>
+      <c r="O340" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P340" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q340" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 한국교통안전공단 화물운송종사 자격시험 교재 '안전운행' 단원의 일반 내용(교재 원문 미확인)</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>SAFE-0340</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>액체를 일부만 채운 유류 탱크로리를 운전할 때 주의할 점으로 옳은 것은?</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>액체가 적을수록 차가 안정되므로 커브길에서 속도를 높여도 된다</t>
+        </is>
+      </c>
+      <c r="D341" t="inlineStr">
+        <is>
+          <t>탱크 안 액체가 출렁이며 무게중심이 움직이므로 급제동·급가속을 피하고 커브 앞에서 미리 감속한다</t>
+        </is>
+      </c>
+      <c r="E341" t="inlineStr">
+        <is>
+          <t>출렁임을 없애려면 지그재그로 달려 액체를 흔들어 준다</t>
+        </is>
+      </c>
+      <c r="F341" t="inlineStr">
+        <is>
+          <t>정지할 때는 브레이크를 한 번에 세게 밟아 출렁임을 멈춘다</t>
+        </is>
+      </c>
+      <c r="G341" t="n">
+        <v>2</v>
+      </c>
+      <c r="H341" t="inlineStr">
+        <is>
+          <t>덜 채운 탱크는 액체가 앞뒤·좌우로 움직여 차를 밀거나 기울게 하므로 부드러운 가감속과 사전 감속이 필요하다.</t>
+        </is>
+      </c>
+      <c r="I341" t="inlineStr">
+        <is>
+          <t>물이 반쯤 든 통을 들고 걷다 갑자기 멈추면 어떻게 되는지 떠올려 보세요.</t>
+        </is>
+      </c>
+      <c r="J341" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K341" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L341" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M341" t="n">
+        <v>2</v>
+      </c>
+      <c r="O341" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P341" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q341" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 한국교통안전공단 화물운송종사 자격시험 교재 '안전운행' 단원의 일반 내용(교재 원문 미확인)</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>SAFE-0341</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>독성가스를 운반하는 차량이 누출 사고에 대비하여 갖추어야 할 것으로 옳은 것은?</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>누출된 가스를 태워 없애기 위한 점화 도구</t>
+        </is>
+      </c>
+      <c r="D342" t="inlineStr">
+        <is>
+          <t>방독면 등 보호구와 제독제, 응급조치용 공구</t>
+        </is>
+      </c>
+      <c r="E342" t="inlineStr">
+        <is>
+          <t>예비 연료를 담은 플라스틱 통</t>
+        </is>
+      </c>
+      <c r="F342" t="inlineStr">
+        <is>
+          <t>냄새를 가리기 위한 방향제</t>
+        </is>
+      </c>
+      <c r="G342" t="n">
+        <v>2</v>
+      </c>
+      <c r="H342" t="inlineStr">
+        <is>
+          <t>독성가스 운반 차량은 누출 시 사람을 보호하고 독성을 없앨 수 있도록 보호구·제독제·공구 등을 갖춘다.</t>
+        </is>
+      </c>
+      <c r="I342" t="inlineStr">
+        <is>
+          <t>누출된 독성가스로부터 '사람'을 지키고 '독'을 없애는 데 필요한 것을 고르세요.</t>
+        </is>
+      </c>
+      <c r="J342" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K342" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L342" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M342" t="n">
+        <v>2</v>
+      </c>
+      <c r="O342" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P342" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q342" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 고압가스 안전관리법 시행규칙(운반 기준: 보호구·제독제 휴대) 일반 내용(조문 원문 미확인)</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>SAFE-0342</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>LPG 등 가연성 가스를 싣고 가다 가스가 새는 냄새가 날 때의 조치로 옳은 것은?</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>새는 곳을 찾기 위해 라이터를 켜서 비춰 본다</t>
+        </is>
+      </c>
+      <c r="D343" t="inlineStr">
+        <is>
+          <t>환기를 위해 엔진을 켜 둔 채 전기 스위치를 여러 번 켠다</t>
+        </is>
+      </c>
+      <c r="E343" t="inlineStr">
+        <is>
+          <t>바람이 불어 가는 쪽으로 사람들을 대피시킨다</t>
+        </is>
+      </c>
+      <c r="F343" t="inlineStr">
+        <is>
+          <t>엔진을 끄고 불씨가 생기지 않게 하며 바람이 불어오는 쪽으로 사람을 대피시킨다</t>
+        </is>
+      </c>
+      <c r="G343" t="n">
+        <v>4</v>
+      </c>
+      <c r="H343" t="inlineStr">
+        <is>
+          <t>가연성 가스는 작은 불꽃에도 폭발할 수 있으므로 점화원을 없애고, 가스가 흘러가지 않는 바람 위쪽으로 대피한다.</t>
+        </is>
+      </c>
+      <c r="I343" t="inlineStr">
+        <is>
+          <t>가스는 바람을 따라 흘러갑니다.</t>
+        </is>
+      </c>
+      <c r="J343" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K343" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L343" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M343" t="n">
+        <v>1</v>
+      </c>
+      <c r="O343" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P343" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q343" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 한국교통안전공단 화물운송종사 자격시험 교재 '안전운행' 단원의 일반 내용(교재 원문 미확인)</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>SAFE-0343</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>유류를 실은 차량에 불이 났을 때의 초기 진화 방법으로 옳은 것은?</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>물을 세게 뿌려 불을 끈다</t>
+        </is>
+      </c>
+      <c r="D344" t="inlineStr">
+        <is>
+          <t>분말 소화기나 포 소화기를 사용한다</t>
+        </is>
+      </c>
+      <c r="E344" t="inlineStr">
+        <is>
+          <t>젖은 수건으로 불붙은 기름을 닦아 낸다</t>
+        </is>
+      </c>
+      <c r="F344" t="inlineStr">
+        <is>
+          <t>불붙은 기름을 흙탕물이 있는 배수로로 흘려보낸다</t>
+        </is>
+      </c>
+      <c r="G344" t="n">
+        <v>2</v>
+      </c>
+      <c r="H344" t="inlineStr">
+        <is>
+          <t>기름 화재에 물을 뿌리면 기름이 물 위에 떠서 불이 더 넓게 번질 수 있으므로 분말·포 소화기를 쓴다.</t>
+        </is>
+      </c>
+      <c r="I344" t="inlineStr">
+        <is>
+          <t>기름과 물은 섞이지 않고, 기름이 위로 뜹니다.</t>
+        </is>
+      </c>
+      <c r="J344" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K344" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L344" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M344" t="n">
+        <v>2</v>
+      </c>
+      <c r="O344" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P344" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q344" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 유류화재(B급) 소화 원리 — 소방 일반 상식(원문 미확인)</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>SAFE-0344</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>위험물을 싣고 출발하기 전에 운전자가 확인할 사항으로 가장 알맞은 것은?</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>용기를 적재함에 느슨하게 두어 충격을 흡수하게 한다</t>
+        </is>
+      </c>
+      <c r="D345" t="inlineStr">
+        <is>
+          <t>밸브를 조금 열어 두어 용기 안 압력을 낮춘다</t>
+        </is>
+      </c>
+      <c r="E345" t="inlineStr">
+        <is>
+          <t>용기가 움직이지 않게 고정되었는지, 밸브와 마개가 잠겼는지 확인한다</t>
+        </is>
+      </c>
+      <c r="F345" t="inlineStr">
+        <is>
+          <t>빨리 출발하기 위해 적재 상태는 도착 후에 확인한다</t>
+        </is>
+      </c>
+      <c r="G345" t="n">
+        <v>3</v>
+      </c>
+      <c r="H345" t="inlineStr">
+        <is>
+          <t>운행 중 용기가 구르거나 밸브가 열려 있으면 누출·폭발로 이어질 수 있으므로 고정과 밀폐를 출발 전에 확인한다.</t>
+        </is>
+      </c>
+      <c r="I345" t="inlineStr">
+        <is>
+          <t>운행 중 흔들림과 누출, 두 가지를 막는 것이 핵심입니다.</t>
+        </is>
+      </c>
+      <c r="J345" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K345" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L345" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M345" t="n">
+        <v>1</v>
+      </c>
+      <c r="O345" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P345" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q345" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 한국교통안전공단 화물운송종사 자격시험 교재 '안전운행' 단원의 일반 내용(교재 원문 미확인)</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>SAFE-0345</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>화물을 적재함 뒤쪽에 지나치게 몰아 실었을 때 생기기 쉬운 현상은?</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>앞바퀴 하중이 늘어나 핸들이 매우 무거워진다</t>
+        </is>
+      </c>
+      <c r="D346" t="inlineStr">
+        <is>
+          <t>무게중심이 낮아져 커브길에서 더 안정된다</t>
+        </is>
+      </c>
+      <c r="E346" t="inlineStr">
+        <is>
+          <t>앞바퀴에 걸리는 하중이 줄어 핸들 조작이 불안정해진다</t>
+        </is>
+      </c>
+      <c r="F346" t="inlineStr">
+        <is>
+          <t>뒷바퀴 하중이 줄어 뒷바퀴가 쉽게 미끄러진다</t>
+        </is>
+      </c>
+      <c r="G346" t="n">
+        <v>3</v>
+      </c>
+      <c r="H346" t="inlineStr">
+        <is>
+          <t>무게가 뒤로 쏠리면 앞바퀴가 들리듯 가벼워져 조향력이 떨어진다. 반대로 앞쪽에 몰면 앞바퀴에 과하중이 걸린다.</t>
+        </is>
+      </c>
+      <c r="I346" t="inlineStr">
+        <is>
+          <t>시소의 한쪽 끝에 무게를 실으면 반대쪽은 어떻게 되는지 떠올려 보세요.</t>
+        </is>
+      </c>
+      <c r="J346" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K346" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L346" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M346" t="n">
+        <v>3</v>
+      </c>
+      <c r="O346" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P346" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q346" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 한국교통안전공단 화물운송종사 자격시험 교재 '안전운행' 단원의 일반 내용(교재 원문 미확인)</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>SAFE-0346</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>적재함 뒤로 길게 튀어나온 철근 같은 화물을 실은 차가 회전할 때 주의할 점으로 옳은 것은?</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>튀어나온 화물은 회전 방향 쪽으로만 움직이므로 바깥쪽은 신경 쓰지 않아도 된다</t>
+        </is>
+      </c>
+      <c r="D347" t="inlineStr">
+        <is>
+          <t>회전할 때 빠르게 돌아야 화물 끝이 덜 움직인다</t>
+        </is>
+      </c>
+      <c r="E347" t="inlineStr">
+        <is>
+          <t>튀어나온 화물은 차체가 아니므로 접촉해도 사고가 아니다</t>
+        </is>
+      </c>
+      <c r="F347" t="inlineStr">
+        <is>
+          <t>튀어나온 화물 끝이 회전 방향과 반대쪽으로 크게 움직이므로 주변 차·보행자를 살피며 서행한다</t>
+        </is>
+      </c>
+      <c r="G347" t="n">
+        <v>4</v>
+      </c>
+      <c r="H347" t="inlineStr">
+        <is>
+          <t>뒤로 긴 화물은 회전할 때 끝부분이 바깥쪽으로 크게 휘둘려 옆 차로의 차나 보행자를 칠 수 있다.</t>
+        </is>
+      </c>
+      <c r="I347" t="inlineStr">
+        <is>
+          <t>긴 막대를 들고 몸을 돌릴 때 막대 뒤끝이 어디로 가는지 떠올려 보세요.</t>
+        </is>
+      </c>
+      <c r="J347" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K347" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L347" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M347" t="n">
+        <v>2</v>
+      </c>
+      <c r="O347" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P347" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q347" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 한국교통안전공단 화물운송종사 자격시험 교재 '안전운행' 단원의 일반 내용(교재 원문 미확인)</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>SAFE-0347</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>화물을 제대로 고정하지 않은 상태에서 급제동했을 때 일어날 수 있는 위험으로 가장 알맞은 것은?</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>화물이 앞으로 쏠려 운전석을 덮치거나 떨어져 다른 차를 위협한다</t>
+        </is>
+      </c>
+      <c r="D348" t="inlineStr">
+        <is>
+          <t>화물이 뒤로 밀려 제동거리가 짧아진다</t>
+        </is>
+      </c>
+      <c r="E348" t="inlineStr">
+        <is>
+          <t>화물이 무거울수록 제자리에 고정되어 안전하다</t>
+        </is>
+      </c>
+      <c r="F348" t="inlineStr">
+        <is>
+          <t>급제동하면 화물의 무게중심이 낮아진다</t>
+        </is>
+      </c>
+      <c r="G348" t="n">
+        <v>1</v>
+      </c>
+      <c r="H348" t="inlineStr">
+        <is>
+          <t>고정이 안 된 화물은 관성으로 앞으로 쏠리며 운전석 충돌·낙하 사고를 일으킨다.</t>
+        </is>
+      </c>
+      <c r="I348" t="inlineStr">
+        <is>
+          <t>달리던 물체는 차가 멈춰도 계속 앞으로 가려는 성질이 있습니다.</t>
+        </is>
+      </c>
+      <c r="J348" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K348" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L348" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M348" t="n">
+        <v>1</v>
+      </c>
+      <c r="O348" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P348" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q348" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 한국교통안전공단 화물운송종사 자격시험 교재 '안전운행' 단원의 일반 내용(교재 원문 미확인)</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>SAFE-0348</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>긴 내리막길을 내려온 뒤 바퀴 부근에서 연기와 타는 냄새가 날 때의 조치로 옳은 것은?</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>바람으로 식히기 위해 속도를 높여 계속 달린다</t>
+        </is>
+      </c>
+      <c r="D349" t="inlineStr">
+        <is>
+          <t>안전한 곳에 차를 세워 브레이크·타이어 과열을 확인하고, 불이 붙으면 소화기로 끈 뒤 차에서 떨어진다</t>
+        </is>
+      </c>
+      <c r="E349" t="inlineStr">
+        <is>
+          <t>브레이크를 더 세게 여러 번 밟아 열을 빼낸다</t>
+        </is>
+      </c>
+      <c r="F349" t="inlineStr">
+        <is>
+          <t>뜨거운 타이어 바로 옆에 붙어 서서 상태를 오래 지켜본다</t>
+        </is>
+      </c>
+      <c r="G349" t="n">
+        <v>2</v>
+      </c>
+      <c r="H349" t="inlineStr">
+        <is>
+          <t>내리막 연속 제동으로 브레이크·타이어가 과열되면 화재나 타이어 파열이 생길 수 있으므로 정차 후 확인·초기 진화하고 떨어져 있어야 한다.</t>
+        </is>
+      </c>
+      <c r="I349" t="inlineStr">
+        <is>
+          <t>과열의 원인이 된 행동을 계속하면 어떻게 될지 생각해 보세요.</t>
+        </is>
+      </c>
+      <c r="J349" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K349" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L349" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M349" t="n">
+        <v>3</v>
+      </c>
+      <c r="O349" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P349" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q349" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 한국교통안전공단 화물운송종사 자격시험 교재 '안전운행' 단원의 일반 내용(교재 원문 미확인)</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>SAFE-0349</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>집중호우로 앞쪽 지하차도나 도로가 물에 잠겨 깊이를 알 수 없을 때의 행동으로 옳은 것은?</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>들어가지 말고 다른 길로 돌아간다</t>
+        </is>
+      </c>
+      <c r="D350" t="inlineStr">
+        <is>
+          <t>대형차는 높으므로 속도를 높여 통과한다</t>
+        </is>
+      </c>
+      <c r="E350" t="inlineStr">
+        <is>
+          <t>앞차가 지나갔으면 따라 들어간다</t>
+        </is>
+      </c>
+      <c r="F350" t="inlineStr">
+        <is>
+          <t>물이 빠지길 기다리며 지하차도 안에 차를 세워 둔다</t>
+        </is>
+      </c>
+      <c r="G350" t="n">
+        <v>1</v>
+      </c>
+      <c r="H350" t="inlineStr">
+        <is>
+          <t>침수 깊이를 모르면 차가 멈추거나 떠내려갈 수 있으므로 진입하지 않고 우회한다.</t>
+        </is>
+      </c>
+      <c r="I350" t="inlineStr">
+        <is>
+          <t>보이지 않는 깊이는 언제든 예상보다 깊을 수 있습니다.</t>
+        </is>
+      </c>
+      <c r="J350" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K350" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L350" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M350" t="n">
+        <v>1</v>
+      </c>
+      <c r="O350" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P350" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q350" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 한국교통안전공단 화물운송종사 자격시험 교재 '안전운행' 단원의 일반 내용(교재 원문 미확인)</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>SAFE-0350</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>물이 고인 도로를 부득이하게 지나야 할 때의 방법으로 옳은 것은?</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>고단 기어로 빠르게 달려 물보라를 일으키며 지나간다</t>
+        </is>
+      </c>
+      <c r="D351" t="inlineStr">
+        <is>
+          <t>물 가운데에서 잠시 멈춰 앞쪽 깊이를 확인한다</t>
+        </is>
+      </c>
+      <c r="E351" t="inlineStr">
+        <is>
+          <t>물속에서 기어를 바꾸어 속도를 계속 바꾼다</t>
+        </is>
+      </c>
+      <c r="F351" t="inlineStr">
+        <is>
+          <t>저단 기어로 일정한 속도를 유지하며 중간에 멈추거나 변속하지 않고 통과한다</t>
+        </is>
+      </c>
+      <c r="G351" t="n">
+        <v>4</v>
+      </c>
+      <c r="H351" t="inlineStr">
+        <is>
+          <t>물속에서 멈추거나 변속하면 엔진이 꺼지거나 배기관으로 물이 들어갈 수 있어, 저단으로 천천히 한 번에 지난다.</t>
+        </is>
+      </c>
+      <c r="I351" t="inlineStr">
+        <is>
+          <t>물속에서 엔진이 꺼지지 않게 하는 것이 목표입니다.</t>
+        </is>
+      </c>
+      <c r="J351" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K351" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L351" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M351" t="n">
+        <v>2</v>
+      </c>
+      <c r="O351" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P351" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q351" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 한국교통안전공단 화물운송종사 자격시험 교재 '안전운행' 단원의 일반 내용(교재 원문 미확인)</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>SAFE-0351</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>차가 물에 잠겨 수압 때문에 문이 열리지 않을 때 탈출 방법으로 옳은 것은?</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>문이 열릴 때까지 계속 힘으로 밀며 기다린다</t>
+        </is>
+      </c>
+      <c r="D352" t="inlineStr">
+        <is>
+          <t>창문으로 먼저 탈출을 시도하고, 어려우면 차 안에 물이 차올라 안팎 수압 차이가 줄었을 때 문을 연다</t>
+        </is>
+      </c>
+      <c r="E352" t="inlineStr">
+        <is>
+          <t>안전띠를 맨 채 구조대가 올 때까지 움직이지 않는다</t>
+        </is>
+      </c>
+      <c r="F352" t="inlineStr">
+        <is>
+          <t>시동을 다시 걸어 차를 물 밖으로 몰고 나간다</t>
+        </is>
+      </c>
+      <c r="G352" t="n">
+        <v>2</v>
+      </c>
+      <c r="H352" t="inlineStr">
+        <is>
+          <t>물이 차오르기 시작하면 바깥 수압으로 문이 잘 열리지 않으므로 창문을 이용하고, 안팎 수위가 비슷해지면 문을 열 수 있다.</t>
+        </is>
+      </c>
+      <c r="I352" t="inlineStr">
+        <is>
+          <t>문을 바깥에서 누르는 힘이 언제 약해지는지 생각해 보세요.</t>
+        </is>
+      </c>
+      <c r="J352" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K352" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L352" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M352" t="n">
+        <v>3</v>
+      </c>
+      <c r="O352" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P352" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q352" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 행정안전부 국민재난안전포털 차량 침수 시 행동요령 일반 내용(원문 미확인) · 교차 점검 반영</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>SAFE-0352</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>침수되었던 차량을 다룰 때의 조치로 옳은 것은?</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>물기를 말리기 위해 바로 시동을 걸어 공회전시킨다</t>
+        </is>
+      </c>
+      <c r="D353" t="inlineStr">
+        <is>
+          <t>시동이 걸리면 바로 운행에 투입한다</t>
+        </is>
+      </c>
+      <c r="E353" t="inlineStr">
+        <is>
+          <t>엔진룸에 물을 더 뿌려 진흙을 씻어 낸 뒤 시동을 건다</t>
+        </is>
+      </c>
+      <c r="F353" t="inlineStr">
+        <is>
+          <t>시동을 걸지 말고 정비업체 등에 점검을 맡긴다</t>
+        </is>
+      </c>
+      <c r="G353" t="n">
+        <v>4</v>
+      </c>
+      <c r="H353" t="inlineStr">
+        <is>
+          <t>엔진에 물이 들어간 상태에서 시동을 걸면 엔진이 크게 손상될 수 있으므로 점검 전 시동을 걸지 않는다.</t>
+        </is>
+      </c>
+      <c r="I353" t="inlineStr">
+        <is>
+          <t>엔진 안으로 물이 들어갔다면 움직이는 순간 어떻게 될지 떠올려 보세요.</t>
+        </is>
+      </c>
+      <c r="J353" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K353" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L353" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M353" t="n">
+        <v>1</v>
+      </c>
+      <c r="O353" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P353" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q353" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 한국교통안전공단 화물운송종사 자격시험 교재 '안전운행' 단원의 일반 내용(교재 원문 미확인)</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>SAFE-0353</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>한국도로공사가 안내하는 고속도로 사고·고장 시 2차 사고 예방 행동요령의 순서로 옳은 것은?</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>트렁크 열기 → 비상등 켜기 → 스마트폰으로 신고 → 가드레일 밖으로 대피</t>
+        </is>
+      </c>
+      <c r="D354" t="inlineStr">
+        <is>
+          <t>스마트폰으로 신고 → 비상등 켜기 → 트렁크 열기 → 가드레일 밖으로 대피</t>
+        </is>
+      </c>
+      <c r="E354" t="inlineStr">
+        <is>
+          <t>가드레일 밖으로 대피 → 트렁크 열기 → 비상등 켜기 → 스마트폰으로 신고</t>
+        </is>
+      </c>
+      <c r="F354" t="inlineStr">
+        <is>
+          <t>비상등 켜기 → 트렁크 열기 → 가드레일 밖으로 대피 → 스마트폰으로 신고</t>
+        </is>
+      </c>
+      <c r="G354" t="n">
+        <v>4</v>
+      </c>
+      <c r="H354" t="inlineStr">
+        <is>
+          <t>캠페인 '비트밖스'는 비상등·트렁크로 뒤차에 알리고, 먼저 차로 밖 안전한 곳으로 대피한 뒤 신고하라는 뜻이다.</t>
+        </is>
+      </c>
+      <c r="I354" t="inlineStr">
+        <is>
+          <t>캠페인 이름은 각 행동의 첫 글자를 딴 네 글자이며, 신고는 몸이 안전해진 다음입니다.</t>
+        </is>
+      </c>
+      <c r="J354" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K354" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L354" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M354" t="n">
+        <v>2</v>
+      </c>
+      <c r="O354" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P354" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q354" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 한국도로공사 2차 사고 예방 캠페인 '비트밖스'(비상등-트렁크-밖으로 대피-스마트폰 신고), 2차 사고 치사율 54.3%(일반 사고 8.4%의 약 6.5배) — 전북일보 https://www.jjan.kr/articleAmp/20250901580341</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>SAFE-0354</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>고속도로 2차 사고의 특징으로 옳은 것은?</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>차가 멈춘 상태에서 일어나므로 피해가 대부분 가볍다</t>
+        </is>
+      </c>
+      <c r="D355" t="inlineStr">
+        <is>
+          <t>주로 낮 시간 맑은 날씨에만 일어난다</t>
+        </is>
+      </c>
+      <c r="E355" t="inlineStr">
+        <is>
+          <t>일반 교통사고보다 치사율이 몇 배나 높다</t>
+        </is>
+      </c>
+      <c r="F355" t="inlineStr">
+        <is>
+          <t>뒤차와 무관하게 사고 차량끼리만 다시 부딪치는 사고를 말한다</t>
+        </is>
+      </c>
+      <c r="G355" t="n">
+        <v>3</v>
+      </c>
+      <c r="H355" t="inlineStr">
+        <is>
+          <t>2차 사고는 멈춰 선 차량이나 사람을 뒤차가 고속으로 들이받는 경우가 많아 치사율이 일반 사고보다 훨씬 높다.</t>
+        </is>
+      </c>
+      <c r="I355" t="inlineStr">
+        <is>
+          <t>멈춰 선 사람과 빠르게 달려오는 뒤차를 함께 떠올려 보세요.</t>
+        </is>
+      </c>
+      <c r="J355" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K355" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L355" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M355" t="n">
+        <v>2</v>
+      </c>
+      <c r="O355" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P355" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q355" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 한국도로공사 2차 사고 예방 캠페인 '비트밖스'(비상등-트렁크-밖으로 대피-스마트폰 신고), 2차 사고 치사율 54.3%(일반 사고 8.4%의 약 6.5배) — 전북일보 https://www.jjan.kr/articleAmp/20250901580341</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>SAFE-0355</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>고속도로 2차 사고가 일어나기 쉬운 조건으로 가장 알맞은 것은?</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>차량 통행이 거의 없는 맑은 날 낮 시간</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>사고 차량이 비상등과 안전삼각대를 설치했을 때</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>사고 차량을 갓길 밖 안전지대로 옮겼을 때</t>
+        </is>
+      </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>시야가 나쁜 야간·새벽에 뒤차 운전자가 앞을 잘 살피지 않을 때</t>
+        </is>
+      </c>
+      <c r="G356" t="n">
+        <v>4</v>
+      </c>
+      <c r="H356" t="inlineStr">
+        <is>
+          <t>어두워 멈춘 차를 늦게 발견하거나 졸음·전방주시 태만이 겹칠 때 2차 사고가 많이 난다.</t>
+        </is>
+      </c>
+      <c r="I356" t="inlineStr">
+        <is>
+          <t>뒤차 운전자가 멈춘 차를 '늦게 발견하는' 상황을 고르세요.</t>
+        </is>
+      </c>
+      <c r="J356" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K356" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L356" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M356" t="n">
+        <v>2</v>
+      </c>
+      <c r="O356" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P356" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q356" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 한국도로공사 2차 사고 통계 보도 일반 내용(야간·졸음 비중) — 수치 원문 미확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>SAFE-0356</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>고속도로에서 반대편이나 옆 차로의 사고 현장을 지날 때 바람직하지 않은 행동은?</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>앞차와의 거리를 넉넉히 두고 앞쪽 흐름을 주시한다</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>속도를 줄여 사고 장면을 휴대전화로 촬영하며 지나간다</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>현장 근처의 사람이나 구조 차량에 주의하며 지나간다</t>
+        </is>
+      </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>필요하면 비상점멸등으로 뒤차에 감속을 알린다</t>
+        </is>
+      </c>
+      <c r="G357" t="n">
+        <v>2</v>
+      </c>
+      <c r="H357" t="inlineStr">
+        <is>
+          <t>사고 현장을 구경하거나 촬영하면 앞을 보지 못해 추돌 등 또 다른 사고를 일으킬 수 있다.</t>
+        </is>
+      </c>
+      <c r="I357" t="inlineStr">
+        <is>
+          <t>내 시선이 어디에 가 있어야 하는지 생각해 보세요.</t>
+        </is>
+      </c>
+      <c r="J357" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K357" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L357" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M357" t="n">
+        <v>1</v>
+      </c>
+      <c r="O357" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P357" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q357" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 한국교통안전공단 화물운송종사 자격시험 교재 '안전운행' 단원의 일반 내용(교재 원문 미확인)</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>SAFE-0357</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>고속도로에서 다친 사람이 없는 가벼운 접촉사고가 났을 때의 조치로 가장 알맞은 것은?</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>보험사 직원이 올 때까지 사고 위치에 차를 그대로 둔다</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>차로 위에 서서 상대 운전자와 과실을 따진다</t>
+        </is>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>사진 등으로 현장을 기록한 뒤 차를 갓길 등 안전한 곳으로 옮기고 사람은 안전지대로 대피한다</t>
+        </is>
+      </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>비상등을 끄고 차 안에서 상대가 내릴 때까지 기다린다</t>
+        </is>
+      </c>
+      <c r="G358" t="n">
+        <v>3</v>
+      </c>
+      <c r="H358" t="inlineStr">
+        <is>
+          <t>차로에 차와 사람이 머물면 뒤차에 의한 2차 사고 위험이 크므로, 기록 후 신속히 차를 옮기고 대피한다.</t>
+        </is>
+      </c>
+      <c r="I358" t="inlineStr">
+        <is>
+          <t>사고 처리보다 먼저 지켜야 할 것은 사람의 안전입니다.</t>
+        </is>
+      </c>
+      <c r="J358" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K358" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L358" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M358" t="n">
+        <v>2</v>
+      </c>
+      <c r="O358" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P358" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q358" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 한국교통안전공단 화물운송종사 자격시험 교재 '안전운행' 단원의 일반 내용(교재 원문 미확인)</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>SAFE-0358</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>성인에게 심폐소생술을 할 때 가슴압박의 깊이와 속도로 옳은 것은?</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>약 2cm 깊이로 분당 60~80회</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>약 5cm 깊이로 분당 100~120회</t>
+        </is>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>약 5cm 깊이로 분당 60~80회</t>
+        </is>
+      </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>약 10cm 깊이로 분당 150회 이상</t>
+        </is>
+      </c>
+      <c r="G359" t="n">
+        <v>2</v>
+      </c>
+      <c r="H359" t="inlineStr">
+        <is>
+          <t>현행 한국 심폐소생술 가이드라인은 성인 가슴압박을 약 5cm 깊이, 분당 100~120회 속도로 하도록 권고한다.</t>
+        </is>
+      </c>
+      <c r="I359" t="inlineStr">
+        <is>
+          <t>1초에 두 번 가까이 누르는 빠른 박자를 떠올려 보세요.</t>
+        </is>
+      </c>
+      <c r="J359" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K359" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L359" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M359" t="n">
+        <v>2</v>
+      </c>
+      <c r="O359" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P359" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q359" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 2025 한국 심폐소생술 가이드라인(질병관리청·대한심폐소생협회, 2026.1 발표: 전체 순서·방법 유지) / 금천구보건소 심폐소생술 안내 https://www.geumcheon.go.kr/health/contents.do?key=4540 (가슴뼈 아래 1/2, 약 5cm, 분당 100~120회, 30:2, 호흡 확인 10초 이내) / 경향신문 https://www.khan.co.kr/article/202601291431001/</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>SAFE-0359</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>성인 심폐소생술에서 가슴압박을 하는 위치로 옳은 것은?</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>가슴뼈(흉골)의 아래쪽 절반 부위</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>명치 끝 아래의 배 위쪽</t>
+        </is>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>왼쪽 젖꼭지 바깥쪽 갈비뼈 위</t>
+        </is>
+      </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>목 바로 아래 쇄골 사이</t>
+        </is>
+      </c>
+      <c r="G360" t="n">
+        <v>1</v>
+      </c>
+      <c r="H360" t="inlineStr">
+        <is>
+          <t>가슴압박은 가슴 한가운데 가슴뼈의 아래쪽 1/2 부위를 양팔을 곧게 펴고 체중을 실어 누른다.</t>
+        </is>
+      </c>
+      <c r="I360" t="inlineStr">
+        <is>
+          <t>심장은 가슴 한가운데 뼈의 뒤쪽에 있습니다.</t>
+        </is>
+      </c>
+      <c r="J360" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K360" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L360" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M360" t="n">
+        <v>2</v>
+      </c>
+      <c r="O360" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P360" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q360" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 2025 한국 심폐소생술 가이드라인(질병관리청·대한심폐소생협회, 2026.1 발표: 전체 순서·방법 유지) / 금천구보건소 심폐소생술 안내 https://www.geumcheon.go.kr/health/contents.do?key=4540 (가슴뼈 아래 1/2, 약 5cm, 분당 100~120회, 30:2, 호흡 확인 10초 이내) / 경향신문 https://www.khan.co.kr/article/202601291431001/</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>SAFE-0360</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>쓰러진 사람의 반응이 없을 때 심정지 여부를 판단하기 위해 호흡을 확인하는 시간으로 옳은 것은?</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>10초 이내</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>30초 이상 충분히</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>약 1분 동안</t>
+        </is>
+      </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>약 5분 동안</t>
+        </is>
+      </c>
+      <c r="G361" t="n">
+        <v>1</v>
+      </c>
+      <c r="H361" t="inlineStr">
+        <is>
+          <t>호흡 확인은 10초 이내로 얼굴과 가슴을 보며 하고, 호흡이 없거나 비정상이면 바로 가슴압박을 시작한다.</t>
+        </is>
+      </c>
+      <c r="I361" t="inlineStr">
+        <is>
+          <t>심정지는 1분 1초가 생존율을 좌우하므로 확인에 오래 머물러선 안 됩니다.</t>
+        </is>
+      </c>
+      <c r="J361" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K361" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L361" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M361" t="n">
+        <v>3</v>
+      </c>
+      <c r="O361" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P361" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q361" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 2025 한국 심폐소생술 가이드라인(질병관리청·대한심폐소생협회, 2026.1 발표: 전체 순서·방법 유지) / 금천구보건소 심폐소생술 안내 https://www.geumcheon.go.kr/health/contents.do?key=4540 (가슴뼈 아래 1/2, 약 5cm, 분당 100~120회, 30:2, 호흡 확인 10초 이내) / 경향신문 https://www.khan.co.kr/article/202601291431001/</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>SAFE-0361</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>교육을 받은 구조자가 인공호흡을 함께 할 때 가슴압박과 인공호흡의 비율로 옳은 것은?</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>15:1</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>30:2</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>5:1</t>
+        </is>
+      </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>2:30</t>
+        </is>
+      </c>
+      <c r="G362" t="n">
+        <v>2</v>
+      </c>
+      <c r="H362" t="inlineStr">
+        <is>
+          <t>가슴압박 30회 뒤 인공호흡 2회를 반복한다. 인공호흡이 어려운 일반인은 가슴압박만 계속해도 된다.</t>
+        </is>
+      </c>
+      <c r="I362" t="inlineStr">
+        <is>
+          <t>가슴압박 횟수가 인공호흡보다 훨씬 많습니다.</t>
+        </is>
+      </c>
+      <c r="J362" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K362" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L362" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M362" t="n">
+        <v>1</v>
+      </c>
+      <c r="O362" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P362" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q362" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 ○: 2025 한국 심폐소생술 가이드라인(질병관리청·대한심폐소생협회, 2026.1 발표: 전체 순서·방법 유지) / 금천구보건소 심폐소생술 안내 https://www.geumcheon.go.kr/health/contents.do?key=4540 (가슴뼈 아래 1/2, 약 5cm, 분당 100~120회, 30:2, 호흡 확인 10초 이내) / 경향신문 https://www.khan.co.kr/article/202601291431001/</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>SAFE-0362</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>자동심장충격기(AED)를 사용할 때의 방법으로 옳은 것은?</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>심장 리듬을 분석하는 동안에도 환자를 계속 붙잡고 있는다</t>
+        </is>
+      </c>
+      <c r="D363" t="inlineStr">
+        <is>
+          <t>패드는 옷 위에 붙여도 된다</t>
+        </is>
+      </c>
+      <c r="E363" t="inlineStr">
+        <is>
+          <t>충격을 한 번 주면 가슴압박은 더 하지 않는다</t>
+        </is>
+      </c>
+      <c r="F363" t="inlineStr">
+        <is>
+          <t>충격을 준 뒤에는 바로 가슴압박을 다시 시작한다</t>
+        </is>
+      </c>
+      <c r="G363" t="n">
+        <v>4</v>
+      </c>
+      <c r="H363" t="inlineStr">
+        <is>
+          <t>AED는 분석·충격 때 환자에게서 떨어져야 하며, 충격 후에는 즉시 가슴압박을 이어 가고 2분마다 다시 분석한다.</t>
+        </is>
+      </c>
+      <c r="I363" t="inlineStr">
+        <is>
+          <t>충격 한 번으로 끝나는 것이 아니라 심폐소생술과 번갈아 이어진다는 점을 떠올려 보세요.</t>
+        </is>
+      </c>
+      <c r="J363" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K363" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L363" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M363" t="n">
+        <v>2</v>
+      </c>
+      <c r="O363" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P363" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q363" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 한국 심폐소생술 가이드라인 AED 사용 순서 일반 내용(2025 개정: 여성 환자 브래지어 제거 불필요, 패드는 맨살에 부착) — 경향신문 https://www.khan.co.kr/article/202601291431001/</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>SAFE-0363</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>교통사고 부상자의 상처에서 피가 많이 날 때 가장 먼저 할 지혈 방법으로 옳은 것은?</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>상처에 흙이나 된장을 발라 피를 멈추게 한다</t>
+        </is>
+      </c>
+      <c r="D364" t="inlineStr">
+        <is>
+          <t>상처 부위를 심장보다 낮게 내려 둔다</t>
+        </is>
+      </c>
+      <c r="E364" t="inlineStr">
+        <is>
+          <t>깨끗한 거즈나 천을 상처에 대고 손으로 세게 눌러 압박한다</t>
+        </is>
+      </c>
+      <c r="F364" t="inlineStr">
+        <is>
+          <t>상처 위를 가볍게 문질러 피가 굳게 한다</t>
+        </is>
+      </c>
+      <c r="G364" t="n">
+        <v>3</v>
+      </c>
+      <c r="H364" t="inlineStr">
+        <is>
+          <t>출혈의 기본 처치는 직접 압박이며, 가능하면 상처 부위를 심장보다 높게 한다.</t>
+        </is>
+      </c>
+      <c r="I364" t="inlineStr">
+        <is>
+          <t>피가 나오는 곳을 '막는' 가장 단순한 방법을 생각해 보세요.</t>
+        </is>
+      </c>
+      <c r="J364" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K364" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L364" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M364" t="n">
+        <v>1</v>
+      </c>
+      <c r="O364" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P364" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q364" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 대한적십자사 응급처치 교육 일반 내용(직접 압박 지혈) — 원문 미확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>SAFE-0364</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>교통사고 부상자의 팔다리에 골절이 의심될 때의 응급처치로 옳은 것은?</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>어긋난 뼈를 손으로 잡아당겨 제자리에 맞춘다</t>
+        </is>
+      </c>
+      <c r="D365" t="inlineStr">
+        <is>
+          <t>통증을 확인하려고 다친 부위를 여러 번 움직여 본다</t>
+        </is>
+      </c>
+      <c r="E365" t="inlineStr">
+        <is>
+          <t>바로 맞추려 하지 말고 부목으로 다친 부위의 위아래 관절까지 고정한다</t>
+        </is>
+      </c>
+      <c r="F365" t="inlineStr">
+        <is>
+          <t>부목은 다친 곳 한 지점만 짧게 대어 묶는다</t>
+        </is>
+      </c>
+      <c r="G365" t="n">
+        <v>3</v>
+      </c>
+      <c r="H365" t="inlineStr">
+        <is>
+          <t>골절 부위를 움직이면 혈관·신경 손상이 커질 수 있으므로 있는 그대로 위아래 관절까지 고정한다.</t>
+        </is>
+      </c>
+      <c r="I365" t="inlineStr">
+        <is>
+          <t>고정의 목적은 '움직이지 않게' 하는 것입니다.</t>
+        </is>
+      </c>
+      <c r="J365" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K365" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L365" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M365" t="n">
+        <v>2</v>
+      </c>
+      <c r="O365" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P365" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q365" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 대한적십자사 응급처치 교육 일반 내용(골절 고정) — 원문 미확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>SAFE-0365</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>교통사고 부상자에게 나타나는 쇼크의 증상으로 옳은 것은?</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>얼굴이 창백하고 식은땀을 흘리며 맥박이 빠르고 약하다</t>
+        </is>
+      </c>
+      <c r="D366" t="inlineStr">
+        <is>
+          <t>얼굴이 붉어지고 피부가 뜨겁고 건조하며 맥박이 느리고 강하다</t>
+        </is>
+      </c>
+      <c r="E366" t="inlineStr">
+        <is>
+          <t>혈색이 좋아지고 호흡이 느리고 깊어진다</t>
+        </is>
+      </c>
+      <c r="F366" t="inlineStr">
+        <is>
+          <t>손발이 따뜻해지고 정신이 또렷해진다</t>
+        </is>
+      </c>
+      <c r="G366" t="n">
+        <v>1</v>
+      </c>
+      <c r="H366" t="inlineStr">
+        <is>
+          <t>쇼크는 몸에 혈액이 충분히 돌지 못하는 상태로, 창백함·식은땀·빠르고 약한 맥박·불안 등이 나타난다.</t>
+        </is>
+      </c>
+      <c r="I366" t="inlineStr">
+        <is>
+          <t>피가 부족해지면 피부색과 심장 박동이 어떻게 변할지 떠올려 보세요.</t>
+        </is>
+      </c>
+      <c r="J366" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K366" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L366" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M366" t="n">
+        <v>3</v>
+      </c>
+      <c r="O366" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P366" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q366" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 대한적십자사 응급처치 교육 일반 내용(쇼크 증상) — 원문 미확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>SAFE-0366</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>쇼크가 의심되는 부상자에 대한 응급처치로 옳지 않은 것은?</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>갈증을 호소하면 물을 충분히 마시게 한다</t>
+        </is>
+      </c>
+      <c r="D367" t="inlineStr">
+        <is>
+          <t>편안히 눕히고 담요 등으로 덮어 체온을 유지한다</t>
+        </is>
+      </c>
+      <c r="E367" t="inlineStr">
+        <is>
+          <t>119에 신고하고 상태를 계속 살핀다</t>
+        </is>
+      </c>
+      <c r="F367" t="inlineStr">
+        <is>
+          <t>출혈이 있으면 지혈을 한다</t>
+        </is>
+      </c>
+      <c r="G367" t="n">
+        <v>1</v>
+      </c>
+      <c r="H367" t="inlineStr">
+        <is>
+          <t>쇼크 환자는 구토로 기도가 막히거나 수술이 필요할 수 있어 먹을 것이나 마실 것을 주지 않는다.</t>
+        </is>
+      </c>
+      <c r="I367" t="inlineStr">
+        <is>
+          <t>나중에 병원에서 받을 처치와 구토 위험을 함께 생각해 보세요.</t>
+        </is>
+      </c>
+      <c r="J367" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K367" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L367" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M367" t="n">
+        <v>2</v>
+      </c>
+      <c r="O367" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P367" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q367" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 대한적십자사 응급처치 교육 일반 내용(쇼크 처치) — 원문 미확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>SAFE-0367</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>의식이 있는 성인이 음식물에 목이 막혀 말도 못 하고 기침도 하지 못할 때의 응급처치로 옳은 것은?</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>물을 마시게 하여 음식물을 넘기게 한다</t>
+        </is>
+      </c>
+      <c r="D368" t="inlineStr">
+        <is>
+          <t>바로 눕혀 가슴압박부터 시작한다</t>
+        </is>
+      </c>
+      <c r="E368" t="inlineStr">
+        <is>
+          <t>손가락을 목 안 깊숙이 넣어 보이지 않는 이물질을 더듬어 꺼낸다</t>
+        </is>
+      </c>
+      <c r="F368" t="inlineStr">
+        <is>
+          <t>뒤에서 감싸 안고 주먹 쥔 손으로 배꼽과 명치 사이를 위로 세게 밀어 올린다</t>
+        </is>
+      </c>
+      <c r="G368" t="n">
+        <v>4</v>
+      </c>
+      <c r="H368" t="inlineStr">
+        <is>
+          <t>기침을 못 하는 완전 기도폐쇄에는 등 두드리기 5회를 먼저 하고, 효과가 없으면 복부 밀어내기(하임리히법) 5회를 반복한다. 의식을 잃으면 그때 심폐소생술을 시작한다. 물을 마시게 하거나 손가락으로 더듬는 것은 위험하다.</t>
+        </is>
+      </c>
+      <c r="I368" t="inlineStr">
+        <is>
+          <t>폐 속 공기를 한꺼번에 밀어 올려 막힌 것을 빼내는 원리입니다.</t>
+        </is>
+      </c>
+      <c r="J368" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K368" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L368" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M368" t="n">
+        <v>2</v>
+      </c>
+      <c r="O368" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P368" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q368" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 한국 심폐소생술 가이드라인 성인 기도폐쇄 처치(복부 밀어내기) 일반 내용 — 원문 미확인 · 교차 점검 반영</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>SAFE-0368</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>경제운전을 위한 변속 방법으로 옳은 것은?</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>항상 저단 기어로 엔진 회전수를 높게 유지한다</t>
+        </is>
+      </c>
+      <c r="D369" t="inlineStr">
+        <is>
+          <t>속도에 맞게 가능한 한 높은 단 기어를 사용해 엔진 회전수를 낮게 유지한다</t>
+        </is>
+      </c>
+      <c r="E369" t="inlineStr">
+        <is>
+          <t>변속할 때마다 가속 페달을 끝까지 밟는다</t>
+        </is>
+      </c>
+      <c r="F369" t="inlineStr">
+        <is>
+          <t>평지 정속 주행 중에도 기어를 중립에 둔다</t>
+        </is>
+      </c>
+      <c r="G369" t="n">
+        <v>2</v>
+      </c>
+      <c r="H369" t="inlineStr">
+        <is>
+          <t>필요 이상으로 엔진 회전수를 높이면 연료가 많이 들므로, 속도에 맞는 높은 단으로 일찍 변속하는 것이 경제적이다.</t>
+        </is>
+      </c>
+      <c r="I369" t="inlineStr">
+        <is>
+          <t>엔진이 빠르게 돌수록 무엇을 더 많이 쓰는지 생각해 보세요.</t>
+        </is>
+      </c>
+      <c r="J369" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K369" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L369" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M369" t="n">
+        <v>2</v>
+      </c>
+      <c r="O369" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P369" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q369" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 한국교통안전공단 화물운송종사 자격시험 교재 '안전운행' 단원의 일반 내용(교재 원문 미확인)</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>SAFE-0369</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>고속 주행 중 창문을 활짝 열고 달릴 때에 대한 설명으로 옳은 것은?</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>공기 저항이 줄어 연료 소비가 크게 줄어든다</t>
+        </is>
+      </c>
+      <c r="D370" t="inlineStr">
+        <is>
+          <t>공기 저항이 커져 연료 소비가 늘어날 수 있다</t>
+        </is>
+      </c>
+      <c r="E370" t="inlineStr">
+        <is>
+          <t>차체가 가벼워져 제동거리가 짧아진다</t>
+        </is>
+      </c>
+      <c r="F370" t="inlineStr">
+        <is>
+          <t>엔진 출력이 높아져 가속이 좋아진다</t>
+        </is>
+      </c>
+      <c r="G370" t="n">
+        <v>2</v>
+      </c>
+      <c r="H370" t="inlineStr">
+        <is>
+          <t>속도가 높을수록 공기 저항의 영향이 커지는데, 창문을 열면 차의 모양이 흐트러져 저항이 더 커진다.</t>
+        </is>
+      </c>
+      <c r="I370" t="inlineStr">
+        <is>
+          <t>달리는 차 창밖으로 손을 내밀었을 때 느껴지는 힘을 떠올려 보세요.</t>
+        </is>
+      </c>
+      <c r="J370" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K370" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L370" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M370" t="n">
+        <v>2</v>
+      </c>
+      <c r="O370" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P370" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q370" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 한국교통안전공단 화물운송종사 자격시험 교재 '안전운행' 단원의 일반 내용(교재 원문 미확인)</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>SAFE-0370</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>정속 주행장치(크루즈 컨트롤) 사용에 관한 설명으로 옳은 것은?</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>미끄러운 눈길에서 쓰면 바퀴가 헛돌지 않아 더 안전하다</t>
+        </is>
+      </c>
+      <c r="D371" t="inlineStr">
+        <is>
+          <t>평탄한 고속도로에서는 일정 속도 유지에 도움이 되지만 빗길·눈길에서는 사용을 삼간다</t>
+        </is>
+      </c>
+      <c r="E371" t="inlineStr">
+        <is>
+          <t>시내 도로처럼 정지가 잦은 곳에서 연료 절약 효과가 가장 크다</t>
+        </is>
+      </c>
+      <c r="F371" t="inlineStr">
+        <is>
+          <t>정속 주행장치를 켜면 앞쪽을 살피지 않아도 된다</t>
+        </is>
+      </c>
+      <c r="G371" t="n">
+        <v>2</v>
+      </c>
+      <c r="H371" t="inlineStr">
+        <is>
+          <t>정속 주행장치는 가감속이 적은 곳에서 연비에 도움이 되나, 미끄러운 길에서는 접지력이 떨어질 때 대응이 늦어 위험하다.</t>
+        </is>
+      </c>
+      <c r="I371" t="inlineStr">
+        <is>
+          <t>장치가 노면의 미끄러움까지 판단해 주는지 생각해 보세요.</t>
+        </is>
+      </c>
+      <c r="J371" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K371" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L371" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M371" t="n">
+        <v>3</v>
+      </c>
+      <c r="O371" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P371" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q371" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 한국교통안전공단 화물운송종사 자격시험 교재 '안전운행' 단원의 일반 내용(교재 원문 미확인)</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>SAFE-0371</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>화물을 싣기 위해 오래 기다리며 정차해 있을 때 친환경 운전 방법으로 알맞은 것은?</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>엔진을 끄고 기다린다</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>엔진을 켜 둔 채 가속 페달을 가볍게 밟아 둔다</t>
+        </is>
+      </c>
+      <c r="E372" t="inlineStr">
+        <is>
+          <t>냉각을 위해 엔진을 켜 두고 보닛을 열어 둔다</t>
+        </is>
+      </c>
+      <c r="F372" t="inlineStr">
+        <is>
+          <t>다시 출발할 때 편하도록 계속 공회전시킨다</t>
+        </is>
+      </c>
+      <c r="G372" t="n">
+        <v>1</v>
+      </c>
+      <c r="H372" t="inlineStr">
+        <is>
+          <t>불필요한 공회전은 연료를 낭비하고 배출가스를 늘리므로 장시간 대기할 때는 시동을 끈다.</t>
+        </is>
+      </c>
+      <c r="I372" t="inlineStr">
+        <is>
+          <t>차가 움직이지 않는데도 연료가 타고 있다면 어떻게 해야 할까요?</t>
+        </is>
+      </c>
+      <c r="J372" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K372" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L372" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M372" t="n">
+        <v>1</v>
+      </c>
+      <c r="O372" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P372" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q372" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 한국교통안전공단 화물운송종사 자격시험 교재 '안전운행' 단원의 일반 내용(교재 원문 미확인)</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>SAFE-0372</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>폭우가 계속될 때 산을 깎아 만든 비탈면(절개지) 옆 도로를 지나는 방법으로 옳은 것은?</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>낙석이나 흘러내린 토사가 있을 수 있으므로 속도를 줄이고 노면 위 장애물을 살핀다</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>비탈면 쪽에 바짝 붙어 반대편 차와의 간격을 넓힌다</t>
+        </is>
+      </c>
+      <c r="E373" t="inlineStr">
+        <is>
+          <t>비탈면 구간은 빨리 벗어나야 하므로 속도를 높인다</t>
+        </is>
+      </c>
+      <c r="F373" t="inlineStr">
+        <is>
+          <t>비탈면 아래 갓길에 차를 세워 비가 그치길 기다린다</t>
+        </is>
+      </c>
+      <c r="G373" t="n">
+        <v>1</v>
+      </c>
+      <c r="H373" t="inlineStr">
+        <is>
+          <t>집중호우 때 절개지는 지반이 약해져 낙석·산사태가 생기기 쉬우므로 감속하며 장애물에 대비하고, 그 아래에 머무르지 않는다.</t>
+        </is>
+      </c>
+      <c r="I373" t="inlineStr">
+        <is>
+          <t>많은 비가 흙과 돌에 어떤 영향을 주는지 떠올려 보세요.</t>
+        </is>
+      </c>
+      <c r="J373" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K373" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L373" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M373" t="n">
+        <v>2</v>
+      </c>
+      <c r="O373" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P373" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q373" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 한국교통안전공단 화물운송종사 자격시험 교재 '안전운행' 단원의 일반 내용(교재 원문 미확인)</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>SAFE-0373</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>겨울철 아침 앞유리와 옆유리에 성에가 두껍게 끼어 있을 때 출발 전 조치로 옳은 것은?</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>운전석 정면 부분만 조금 긁어내고 출발한다</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>뜨거운 물을 유리에 부어 빨리 녹인다</t>
+        </is>
+      </c>
+      <c r="E374" t="inlineStr">
+        <is>
+          <t>와이퍼를 작동시켜 성에를 긁어낸다</t>
+        </is>
+      </c>
+      <c r="F374" t="inlineStr">
+        <is>
+          <t>앞·옆·뒤 유리와 사이드미러의 성에와 눈을 모두 제거한 뒤 출발한다</t>
+        </is>
+      </c>
+      <c r="G374" t="n">
+        <v>4</v>
+      </c>
+      <c r="H374" t="inlineStr">
+        <is>
+          <t>운전에 필요한 시야는 정면뿐 아니라 옆·뒤와 사이드미러까지 포함하므로 모두 제거한 뒤 출발해야 한다. 뜨거운 물은 급격한 온도 차로 유리가 깨질 수 있고, 와이퍼로 긁으면 고무날이 상한다.</t>
+        </is>
+      </c>
+      <c r="I374" t="inlineStr">
+        <is>
+          <t>운전에 필요한 시야는 정면만이 아닙니다. 차선 변경과 후진 때를 떠올려 보세요.</t>
+        </is>
+      </c>
+      <c r="J374" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K374" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L374" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M374" t="n">
+        <v>1</v>
+      </c>
+      <c r="O374" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P374" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q374" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 겨울철 안전운전 일반 내용(교재 계절별 운전 단원 취지). 법정 수치 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>SAFE-0374</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>자동변속기 차량에서 변속 레버를 D(주행)에 둔 채 브레이크 페달에서 발을 떼면 가속 페달을 밟지 않아도 차가 천천히 움직이는 현상은?</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>킥다운</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>크리프 현상</t>
+        </is>
+      </c>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>베이퍼 록</t>
+        </is>
+      </c>
+      <c r="F375" t="inlineStr">
+        <is>
+          <t>스탠딩 웨이브</t>
+        </is>
+      </c>
+      <c r="G375" t="n">
+        <v>2</v>
+      </c>
+      <c r="H375" t="inlineStr">
+        <is>
+          <t>크리프 현상은 자동변속기 차량이 D·R 위치에서 엔진 공회전만으로 천천히 움직이는 현상이다. 정차 중에는 브레이크를 확실히 밟고, 차에서 내릴 때는 P에 두고 주차 브레이크를 채워야 한다. 킥다운은 가속 페달을 깊게 밟아 낮은 단으로 바뀌는 것이다.</t>
+        </is>
+      </c>
+      <c r="I375" t="inlineStr">
+        <is>
+          <t>브레이크에서 발을 떼면 엔진의 힘이 변속기를 거쳐 바퀴로 조금씩 전달되기 때문에 생깁니다. 주차장·정체 구간에서 특히 주의해야 합니다.</t>
+        </is>
+      </c>
+      <c r="J375" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K375" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L375" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M375" t="n">
+        <v>2</v>
+      </c>
+      <c r="O375" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P375" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q375" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 자동차 구조 일반 내용(자동변속기 특성). 법정 수치 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>SAFE-0375</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>자갈이 깔린 비포장도로를 화물자동차로 달릴 때의 운전 방법으로 옳은 것은?</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>바퀴가 헛돌지 않도록 속도를 높여 빨리 통과한다</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>앞차 바퀴 자국을 따라가기 위해 앞차에 바짝 붙어 달린다</t>
+        </is>
+      </c>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>미끄러지면 브레이크를 세게 밟아 즉시 멈춘다</t>
+        </is>
+      </c>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>저속으로 일정하게 달리고 급핸들·급제동을 피하며 앞차와 거리를 충분히 둔다</t>
+        </is>
+      </c>
+      <c r="G376" t="n">
+        <v>4</v>
+      </c>
+      <c r="H376" t="inlineStr">
+        <is>
+          <t>자갈길은 노면 마찰이 고르지 않아 미끄러지기 쉽고 앞차 바퀴에서 돌이 튈 수 있으므로, 저속으로 일정하게 달리며 급조작을 피하고 차간거리를 넉넉히 둔다. 급제동은 오히려 미끄러짐을 키운다.</t>
+        </is>
+      </c>
+      <c r="I376" t="inlineStr">
+        <is>
+          <t>노면이 고르지 않아 바퀴가 쉽게 미끄러지고, 앞차 바퀴에서 돌이 튈 수 있다는 점을 생각해 보세요.</t>
+        </is>
+      </c>
+      <c r="J376" t="inlineStr">
+        <is>
+          <t>교재 일반 내용</t>
+        </is>
+      </c>
+      <c r="K376" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="L376" t="inlineStr">
+        <is>
+          <t>자체 작성</t>
+        </is>
+      </c>
+      <c r="M376" t="n">
+        <v>2</v>
+      </c>
+      <c r="O376" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="P376" t="inlineStr">
+        <is>
+          <t>1등 / 2026-10-22</t>
+        </is>
+      </c>
+      <c r="Q376" t="inlineStr">
+        <is>
+          <t>AI 4차 초안(2026-10-21) · 근거 확인 △: 교통안전 일반 내용(노면 상태별 운전). 법정 수치 없음</t>
         </is>
       </c>
     </row>
